--- a/00-日語文型整理.xlsx
+++ b/00-日語文型整理.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://guandamachine-my.sharepoint.com/personal/ec03_gd_guandamachine_com_tw/Documents/Fly/日語/日語練習網站/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECF5CC43-C76B-4CDA-9C3B-E732C9080A60}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65329EAD-A39C-4205-9A99-4F3A0D911256}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{0F3A2E6B-B5D2-4B57-9A1E-3E6BF54CF7A6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0F3A2E6B-B5D2-4B57-9A1E-3E6BF54CF7A6}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="712">
   <si>
     <t>わたしわ マイク・ミラーです</t>
   </si>
@@ -2148,6 +2148,165 @@
   </si>
   <si>
     <t>がつに きょうとで おまつりが あるでしょう?</t>
+  </si>
+  <si>
+    <t>*第13課文型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>わたしは パソコンが ほしいです</t>
+  </si>
+  <si>
+    <t>わたしは てんぷらを たべたいです</t>
+  </si>
+  <si>
+    <t>わたしは フランスヘ りょうり を ならいに いきます</t>
+  </si>
+  <si>
+    <t>我想要一台電腦</t>
+  </si>
+  <si>
+    <t>我想吃天婦羅</t>
+  </si>
+  <si>
+    <t>我要去法國學烹飪</t>
+  </si>
+  <si>
+    <t>私は パソコンが 欲しいです</t>
+  </si>
+  <si>
+    <t>私は てんぷらを 食べたいです</t>
+  </si>
+  <si>
+    <t>私は フランスヘ 料理を 習いに 行きます</t>
+  </si>
+  <si>
+    <t>いまなにが いちばん ほしいですか</t>
+  </si>
+  <si>
+    <t>今 何が いちばん 欲しいですか</t>
+  </si>
+  <si>
+    <t>うちが ほしいです</t>
+  </si>
+  <si>
+    <t>うちが 欲しいです</t>
+  </si>
+  <si>
+    <t>你現在最想要什麼?</t>
+  </si>
+  <si>
+    <t>我想要一棟房子</t>
+  </si>
+  <si>
+    <t>なつやすみに どこへ いきたいですか</t>
+  </si>
+  <si>
+    <t>夏休みに どこへ 行きたいですか</t>
+  </si>
+  <si>
+    <t>おきなわへ いきたいです</t>
+  </si>
+  <si>
+    <t>沖縄へ 行きたいです</t>
+  </si>
+  <si>
+    <t>きょうは つかれましたから、なにも したくないです</t>
+  </si>
+  <si>
+    <t>きょうは 疲れましたから、何も したくないです</t>
+  </si>
+  <si>
+    <t>そうですね。きょうの かいぎは たい へんでしたね</t>
+  </si>
+  <si>
+    <t>そうですね きょうの 会議は 大変でしたね</t>
+  </si>
+  <si>
+    <t>この しゅうまつは なにを しますか</t>
+  </si>
+  <si>
+    <t>この 週末は 何を しますか</t>
+  </si>
+  <si>
+    <t>こどもと こうべへ ふね を みに いきます</t>
+  </si>
+  <si>
+    <t>子どもと 神戸へ 船を 見に 行きます</t>
+  </si>
+  <si>
+    <t>日本へ 何の 勉強に 来ましたか</t>
+  </si>
+  <si>
+    <t>けいざいの べんきょうに きました</t>
+  </si>
+  <si>
+    <t>経済の 勉強に 来ました</t>
+  </si>
+  <si>
+    <t>にほんへ なんの べんきょうに きましたか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暑假想去哪裡</t>
+  </si>
+  <si>
+    <t>我想去沖繩</t>
+  </si>
+  <si>
+    <t>我今天很累,什麼都不想做</t>
+  </si>
+  <si>
+    <t>是啊,今天的會議很累,對吧</t>
+  </si>
+  <si>
+    <t>你這個週末有什麼安排</t>
+  </si>
+  <si>
+    <t>我要帶孩子去神戶看船</t>
+  </si>
+  <si>
+    <t>你來日本學什麼專業</t>
+  </si>
+  <si>
+    <t>我來學習經濟學</t>
+  </si>
+  <si>
+    <t>ふゆやすみは どこか いきましたか</t>
+  </si>
+  <si>
+    <t>冬休みは どこか 行きましたか</t>
+  </si>
+  <si>
+    <t>ええ、いきました</t>
+  </si>
+  <si>
+    <t>ええ、行きました</t>
+  </si>
+  <si>
+    <t>どこへ いきましたか</t>
+  </si>
+  <si>
+    <t>どこへ 行きましたか。</t>
+  </si>
+  <si>
+    <t>ほっかいどうへ スキーに いきました</t>
+  </si>
+  <si>
+    <t>北海道へスキーに行きました</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒假期間你出去玩了嗎?</t>
+  </si>
+  <si>
+    <t>去了</t>
+  </si>
+  <si>
+    <t>你去哪裡了?</t>
+  </si>
+  <si>
+    <t>我去北海道滑雪了</t>
   </si>
 </sst>
 </file>
@@ -2234,9 +2393,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2274,7 +2433,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2380,7 +2539,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2522,7 +2681,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2530,15 +2689,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B91EE72-412B-4BEC-A7E9-A97446845EE1}">
-  <dimension ref="A1:C248"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:C266"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="57.26953125" customWidth="1"/>
-    <col min="2" max="2" width="45.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.08984375" customWidth="1"/>
+    <col min="1" max="1" width="57.21875" customWidth="1"/>
+    <col min="2" max="2" width="45.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -2549,12 +2708,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -2565,7 +2724,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -2573,7 +2732,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -2584,7 +2743,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -2595,7 +2754,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -2604,7 +2763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
@@ -2615,7 +2774,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -2626,7 +2785,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -2637,7 +2796,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -2648,7 +2807,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
@@ -2659,7 +2818,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -2670,7 +2829,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -2681,7 +2840,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2692,7 +2851,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -2703,7 +2862,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2714,7 +2873,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -2725,7 +2884,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -2736,7 +2895,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -2747,12 +2906,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -2763,7 +2922,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2774,7 +2933,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -2785,7 +2944,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>67</v>
       </c>
@@ -2796,7 +2955,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -2807,7 +2966,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -2815,7 +2974,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -2823,7 +2982,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>75</v>
       </c>
@@ -2831,7 +2990,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>77</v>
       </c>
@@ -2842,7 +3001,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>80</v>
       </c>
@@ -2853,7 +3012,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -2864,7 +3023,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>109</v>
       </c>
@@ -2875,7 +3034,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>111</v>
       </c>
@@ -2886,7 +3045,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -2897,7 +3056,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>89</v>
       </c>
@@ -2908,7 +3067,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>92</v>
       </c>
@@ -2919,7 +3078,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>95</v>
       </c>
@@ -2930,7 +3089,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>96</v>
       </c>
@@ -2938,7 +3097,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>98</v>
       </c>
@@ -2949,7 +3108,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>99</v>
       </c>
@@ -2960,7 +3119,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>102</v>
       </c>
@@ -2971,12 +3130,12 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>116</v>
       </c>
@@ -2987,7 +3146,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>119</v>
       </c>
@@ -2998,7 +3157,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>120</v>
       </c>
@@ -3006,7 +3165,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>122</v>
       </c>
@@ -3014,7 +3173,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>124</v>
       </c>
@@ -3022,7 +3181,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>126</v>
       </c>
@@ -3033,7 +3192,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>127</v>
       </c>
@@ -3041,7 +3200,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>129</v>
       </c>
@@ -3049,7 +3208,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>127</v>
       </c>
@@ -3057,7 +3216,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>131</v>
       </c>
@@ -3068,7 +3227,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>134</v>
       </c>
@@ -3079,7 +3238,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>137</v>
       </c>
@@ -3087,7 +3246,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>138</v>
       </c>
@@ -3098,7 +3257,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>141</v>
       </c>
@@ -3109,7 +3268,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>144</v>
       </c>
@@ -3120,7 +3279,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>147</v>
       </c>
@@ -3128,7 +3287,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>154</v>
       </c>
@@ -3139,7 +3298,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>157</v>
       </c>
@@ -3147,7 +3306,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>159</v>
       </c>
@@ -3158,7 +3317,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>160</v>
       </c>
@@ -3166,7 +3325,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>162</v>
       </c>
@@ -3177,7 +3336,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>165</v>
       </c>
@@ -3188,12 +3347,12 @@
         <v>167</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>284</v>
       </c>
@@ -3204,7 +3363,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>285</v>
       </c>
@@ -3215,7 +3374,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>288</v>
       </c>
@@ -3226,7 +3385,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>291</v>
       </c>
@@ -3237,7 +3396,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>294</v>
       </c>
@@ -3248,7 +3407,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>297</v>
       </c>
@@ -3259,7 +3418,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>300</v>
       </c>
@@ -3270,7 +3429,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>303</v>
       </c>
@@ -3281,7 +3440,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>304</v>
       </c>
@@ -3292,7 +3451,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>307</v>
       </c>
@@ -3303,7 +3462,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>310</v>
       </c>
@@ -3314,7 +3473,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>313</v>
       </c>
@@ -3325,7 +3484,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>316</v>
       </c>
@@ -3336,7 +3495,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>319</v>
       </c>
@@ -3347,7 +3506,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>322</v>
       </c>
@@ -3358,7 +3517,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>325</v>
       </c>
@@ -3369,7 +3528,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>328</v>
       </c>
@@ -3380,7 +3539,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>331</v>
       </c>
@@ -3391,7 +3550,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>334</v>
       </c>
@@ -3402,12 +3561,12 @@
         <v>336</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>342</v>
       </c>
@@ -3418,7 +3577,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>355</v>
       </c>
@@ -3426,7 +3585,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>345</v>
       </c>
@@ -3437,7 +3596,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>348</v>
       </c>
@@ -3445,7 +3604,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>349</v>
       </c>
@@ -3456,7 +3615,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>352</v>
       </c>
@@ -3467,1578 +3626,1770 @@
         <v>354</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>661</v>
+      </c>
+      <c r="B94" t="s">
+        <v>667</v>
+      </c>
+      <c r="C94" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>662</v>
+      </c>
+      <c r="B95" t="s">
+        <v>668</v>
+      </c>
+      <c r="C95" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>663</v>
+      </c>
+      <c r="B96" t="s">
+        <v>669</v>
+      </c>
+      <c r="C96" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>670</v>
+      </c>
+      <c r="B97" t="s">
+        <v>671</v>
+      </c>
+      <c r="C97" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>672</v>
+      </c>
+      <c r="B98" t="s">
+        <v>673</v>
+      </c>
+      <c r="C98" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>676</v>
+      </c>
+      <c r="B99" t="s">
+        <v>677</v>
+      </c>
+      <c r="C99" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>678</v>
+      </c>
+      <c r="B100" t="s">
+        <v>679</v>
+      </c>
+      <c r="C100" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>680</v>
+      </c>
+      <c r="B101" t="s">
+        <v>681</v>
+      </c>
+      <c r="C101" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>682</v>
+      </c>
+      <c r="B102" t="s">
+        <v>683</v>
+      </c>
+      <c r="C102" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>684</v>
+      </c>
+      <c r="B103" t="s">
+        <v>685</v>
+      </c>
+      <c r="C103" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>686</v>
+      </c>
+      <c r="B104" t="s">
+        <v>687</v>
+      </c>
+      <c r="C104" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>691</v>
+      </c>
+      <c r="B105" t="s">
+        <v>688</v>
+      </c>
+      <c r="C105" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>689</v>
+      </c>
+      <c r="B106" t="s">
+        <v>690</v>
+      </c>
+      <c r="C106" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>700</v>
+      </c>
+      <c r="B107" t="s">
+        <v>701</v>
+      </c>
+      <c r="C107" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>702</v>
+      </c>
+      <c r="B108" t="s">
+        <v>703</v>
+      </c>
+      <c r="C108" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>704</v>
+      </c>
+      <c r="B109" t="s">
+        <v>705</v>
+      </c>
+      <c r="C109" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>706</v>
+      </c>
+      <c r="B110" t="s">
+        <v>707</v>
+      </c>
+      <c r="C110" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A94" t="s">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>171</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C112" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A95" t="s">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>173</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B113" t="s">
         <v>174</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C113" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A96" t="s">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>176</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C114" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A97" t="s">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>178</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B115" t="s">
         <v>179</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C115" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A98" t="s">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>176</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B116" t="s">
         <v>181</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C116" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A99" t="s">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
         <v>182</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B117" t="s">
         <v>183</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C117" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A100" t="s">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
         <v>184</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C118" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A101" t="s">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
         <v>186</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B119" t="s">
         <v>187</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C119" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A102" t="s">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
         <v>189</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B120" t="s">
         <v>190</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C120" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A103" t="s">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>192</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B121" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A104" t="s">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
         <v>194</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B122" t="s">
         <v>195</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C122" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A105" t="s">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
         <v>197</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B123" t="s">
         <v>198</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C123" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A106" t="s">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
         <v>200</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B124" t="s">
         <v>202</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C124" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A107" t="s">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
         <v>203</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B125" t="s">
         <v>204</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C125" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A108" t="s">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
         <v>206</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B126" t="s">
         <v>207</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C126" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A109" t="s">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
         <v>209</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B127" t="s">
         <v>210</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C127" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A110" t="s">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
         <v>212</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B128" t="s">
         <v>213</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C128" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A111" t="s">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
         <v>215</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B129" t="s">
         <v>216</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C129" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A112" t="s">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
         <v>218</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B130" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A113" t="s">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A114" t="s">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
         <v>413</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C132" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A115" t="s">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
         <v>414</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B133" t="s">
         <v>410</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C133" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A116" t="s">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
         <v>411</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C134" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A117" t="s">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
         <v>374</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B135" t="s">
         <v>359</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C135" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A118" t="s">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
         <v>415</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C136" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A119" t="s">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
         <v>430</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B137" t="s">
         <v>429</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C137" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="20" x14ac:dyDescent="0.4">
-      <c r="A120" t="s">
+    <row r="138" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
         <v>431</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B138" t="s">
         <v>428</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C138" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A121" t="s">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
         <v>421</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B139" t="s">
         <v>422</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C139" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A122" t="s">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
         <v>362</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B140" t="s">
         <v>363</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C140" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A123" t="s">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
         <v>419</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B141" t="s">
         <v>418</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C141" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A124" t="s">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
         <v>424</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B142" t="s">
         <v>423</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C142" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A125" t="s">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
         <v>434</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B143" t="s">
         <v>435</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C143" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A126" t="s">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
         <v>427</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B144" t="s">
         <v>426</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C144" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A127" t="s">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
         <v>364</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C145" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A128" t="s">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
         <v>366</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B146" t="s">
         <v>367</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C146" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A129" t="s">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
         <v>369</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B147" t="s">
         <v>370</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C147" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A130" t="s">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
         <v>372</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C148" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A131" t="s">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
         <v>376</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B149" t="s">
         <v>377</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C149" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A132" t="s">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
         <v>379</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B150" t="s">
         <v>380</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C150" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A133" t="s">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
         <v>382</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B151" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A134" t="s">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
         <v>407</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B152" t="s">
         <v>408</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C152" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A135" t="s">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
         <v>384</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B153" t="s">
         <v>385</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C153" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A136" t="s">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
         <v>387</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B154" t="s">
         <v>388</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C154" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A137" t="s">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
         <v>390</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B155" t="s">
         <v>409</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C155" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A138" t="s">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
         <v>391</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B156" t="s">
         <v>392</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C156" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A139" t="s">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
         <v>394</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B157" t="s">
         <v>395</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C157" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A140" t="s">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
         <v>397</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C158" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A141" t="s">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
         <v>399</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B159" t="s">
         <v>400</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C159" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A142" t="s">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
         <v>402</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B160" t="s">
         <v>403</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C160" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A143" t="s">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A144" t="s">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
         <v>488</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B162" t="s">
         <v>439</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C162" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="20" x14ac:dyDescent="0.4">
-      <c r="A145" t="s">
+    <row r="163" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
         <v>492</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B163" t="s">
         <v>489</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C163" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A146" t="s">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
         <v>445</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B164" t="s">
         <v>446</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C164" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A147" t="s">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
         <v>494</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B165" t="s">
         <v>493</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C165" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A148" t="s">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
         <v>442</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B166" t="s">
         <v>443</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C166" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A149" t="s">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
         <v>447</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B167" t="s">
         <v>448</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C167" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A150" t="s">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
         <v>450</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B168" t="s">
         <v>451</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C168" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A151" t="s">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
         <v>453</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B169" t="s">
         <v>454</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C169" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A152" t="s">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
         <v>456</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B170" t="s">
         <v>457</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C170" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A153" t="s">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
         <v>459</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B171" t="s">
         <v>460</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C171" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A154" t="s">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
         <v>464</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B172" t="s">
         <v>462</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C172" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A155" t="s">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
         <v>465</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B173" t="s">
         <v>466</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C173" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A156" t="s">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
         <v>468</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B174" t="s">
         <v>469</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C174" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A157" t="s">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
         <v>471</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B175" t="s">
         <v>472</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C175" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A158" t="s">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
         <v>474</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C176" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A159" t="s">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
         <v>476</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B177" t="s">
         <v>477</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C177" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A160" t="s">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
         <v>479</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B178" t="s">
         <v>480</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C178" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A161" t="s">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
         <v>482</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B179" t="s">
         <v>483</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C179" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A162" t="s">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
         <v>486</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B180" t="s">
         <v>487</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C180" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A163" t="s">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A164" t="s">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
         <v>553</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B182" t="s">
         <v>554</v>
       </c>
-      <c r="C164" t="s">
+      <c r="C182" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A165" t="s">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
         <v>556</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B183" t="s">
         <v>557</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C183" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A166" t="s">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
         <v>559</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B184" t="s">
         <v>560</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C184" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A167" t="s">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
         <v>562</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B185" t="s">
         <v>563</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C185" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A168" t="s">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
         <v>565</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B186" t="s">
         <v>566</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C186" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A169" t="s">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
         <v>568</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C187" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A170" t="s">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
         <v>570</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C188" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A171" t="s">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
         <v>572</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C189" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A172" t="s">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
         <v>574</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B190" t="s">
         <v>575</v>
       </c>
-      <c r="C172" t="s">
+      <c r="C190" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A173" t="s">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
         <v>577</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B191" t="s">
         <v>578</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C191" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A174" t="s">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
         <v>580</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B192" t="s">
         <v>581</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C192" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A175" t="s">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
         <v>583</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C193" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A176" t="s">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
         <v>585</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C194" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A177" t="s">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
         <v>587</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B195" t="s">
         <v>588</v>
       </c>
-      <c r="C177" t="s">
+      <c r="C195" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A178" t="s">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
         <v>590</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B196" t="s">
         <v>591</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C196" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A179" t="s">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
         <v>593</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B197" t="s">
         <v>601</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C197" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A180" t="s">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
         <v>595</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B198" t="s">
         <v>602</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C198" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A181" t="s">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
         <v>596</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B199" t="s">
         <v>597</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C199" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A182" t="s">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
         <v>598</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B200" t="s">
         <v>599</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C200" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A183" t="s">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A184" t="s">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
         <v>605</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B202" t="s">
         <v>606</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C202" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A185" t="s">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
         <v>608</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B203" t="s">
         <v>610</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C203" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A186" t="s">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
         <v>611</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B204" t="s">
         <v>622</v>
       </c>
-      <c r="C186" t="s">
+      <c r="C204" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A187" t="s">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
         <v>613</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B205" t="s">
         <v>614</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C205" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A188" t="s">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
         <v>616</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B206" t="s">
         <v>617</v>
       </c>
-      <c r="C188" t="s">
+      <c r="C206" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A189" t="s">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
         <v>619</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B207" t="s">
         <v>620</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C207" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A190" t="s">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
         <v>623</v>
       </c>
-      <c r="C190" t="s">
+      <c r="C208" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A191" t="s">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
         <v>625</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B209" t="s">
         <v>626</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C209" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A192" t="s">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
         <v>628</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B210" t="s">
         <v>629</v>
       </c>
-      <c r="C192" t="s">
+      <c r="C210" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A193" t="s">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
         <v>636</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B211" t="s">
         <v>631</v>
       </c>
-      <c r="C193" t="s">
+      <c r="C211" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A194" t="s">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
         <v>633</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B212" t="s">
         <v>634</v>
       </c>
-      <c r="C194" t="s">
+      <c r="C212" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A195" t="s">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
         <v>637</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B213" t="s">
         <v>638</v>
       </c>
-      <c r="C195" t="s">
+      <c r="C213" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A196" t="s">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
         <v>642</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B214" t="s">
         <v>640</v>
       </c>
-      <c r="C196" t="s">
+      <c r="C214" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A197" t="s">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
         <v>643</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B215" t="s">
         <v>644</v>
       </c>
-      <c r="C197" t="s">
+      <c r="C215" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A198" t="s">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
         <v>646</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B216" t="s">
         <v>647</v>
       </c>
-      <c r="C198" t="s">
+      <c r="C216" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A199" t="s">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
         <v>649</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B217" t="s">
         <v>650</v>
       </c>
-      <c r="C199" t="s">
+      <c r="C217" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A200" t="s">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
         <v>652</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B218" t="s">
         <v>653</v>
       </c>
-      <c r="C200" t="s">
+      <c r="C218" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A201" t="s">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
         <v>659</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B219" t="s">
         <v>655</v>
       </c>
-      <c r="C201" t="s">
+      <c r="C219" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A202" t="s">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
         <v>657</v>
       </c>
-      <c r="C202" t="s">
+      <c r="C220" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A203" t="s">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A204" t="s">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
         <v>496</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B222" t="s">
         <v>497</v>
       </c>
-      <c r="C204" t="s">
+      <c r="C222" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A205" t="s">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
         <v>499</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B223" t="s">
         <v>500</v>
       </c>
-      <c r="C205" t="s">
+      <c r="C223" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A206" t="s">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
         <v>502</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B224" t="s">
         <v>503</v>
       </c>
-      <c r="C206" t="s">
+      <c r="C224" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A207" t="s">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
         <v>505</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B225" t="s">
         <v>506</v>
       </c>
-      <c r="C207" t="s">
+      <c r="C225" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A208" t="s">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
         <v>508</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B226" t="s">
         <v>509</v>
       </c>
-      <c r="C208" t="s">
+      <c r="C226" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A209" t="s">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
         <v>511</v>
       </c>
-      <c r="C209" t="s">
+      <c r="C227" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A210" t="s">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
         <v>513</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B228" t="s">
         <v>514</v>
       </c>
-      <c r="C210" t="s">
+      <c r="C228" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A211" t="s">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
         <v>516</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B229" t="s">
         <v>517</v>
       </c>
-      <c r="C211" t="s">
+      <c r="C229" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A212" t="s">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
         <v>519</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B230" t="s">
         <v>520</v>
       </c>
-      <c r="C212" t="s">
+      <c r="C230" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A213" t="s">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
         <v>522</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B231" t="s">
         <v>523</v>
       </c>
-      <c r="C213" t="s">
+      <c r="C231" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A214" t="s">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
         <v>525</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B232" t="s">
         <v>526</v>
       </c>
-      <c r="C214" t="s">
+      <c r="C232" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A215" t="s">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
         <v>528</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B233" t="s">
         <v>529</v>
       </c>
-      <c r="C215" t="s">
+      <c r="C233" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A216" t="s">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
         <v>531</v>
       </c>
-      <c r="B216" t="s">
+      <c r="B234" t="s">
         <v>540</v>
       </c>
-      <c r="C216" t="s">
+      <c r="C234" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A217" t="s">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
         <v>533</v>
       </c>
-      <c r="C217" t="s">
+      <c r="C235" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A218" t="s">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
         <v>535</v>
       </c>
-      <c r="C218" t="s">
+      <c r="C236" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A219" t="s">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
         <v>537</v>
       </c>
-      <c r="B219" t="s">
+      <c r="B237" t="s">
         <v>538</v>
       </c>
-      <c r="C219" t="s">
+      <c r="C237" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A220" t="s">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
         <v>541</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B238" t="s">
         <v>542</v>
       </c>
-      <c r="C220" t="s">
+      <c r="C238" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A221" t="s">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
         <v>544</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B239" t="s">
         <v>550</v>
       </c>
-      <c r="C221" t="s">
+      <c r="C239" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A222" t="s">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
         <v>197</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B240" t="s">
         <v>198</v>
       </c>
-      <c r="C222" t="s">
+      <c r="C240" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A223" t="s">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
         <v>547</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B241" t="s">
         <v>548</v>
       </c>
-      <c r="C223" t="s">
+      <c r="C241" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A224" t="s">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A225" t="s">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
         <v>221</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B243" t="s">
         <v>222</v>
       </c>
-      <c r="C225" t="s">
+      <c r="C243" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A226" t="s">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
         <v>275</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B244" t="s">
         <v>276</v>
       </c>
-      <c r="C226" t="s">
+      <c r="C244" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A227" t="s">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
         <v>225</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B245" t="s">
         <v>277</v>
       </c>
-      <c r="C227" t="s">
+      <c r="C245" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A228" t="s">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
         <v>278</v>
       </c>
-      <c r="B228" t="s">
+      <c r="B246" t="s">
         <v>279</v>
       </c>
-      <c r="C228" t="s">
+      <c r="C246" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A229" t="s">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
         <v>228</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B247" t="s">
         <v>280</v>
       </c>
-      <c r="C229" t="s">
+      <c r="C247" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A230" t="s">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
         <v>229</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B248" t="s">
         <v>282</v>
       </c>
-      <c r="C230" t="s">
+      <c r="C248" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A231" t="s">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
         <v>231</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B249" t="s">
         <v>232</v>
       </c>
-      <c r="C231" t="s">
+      <c r="C249" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A232" t="s">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
         <v>234</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B250" t="s">
         <v>235</v>
       </c>
-      <c r="C232" t="s">
+      <c r="C250" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A233" t="s">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
         <v>237</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B251" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A234" t="s">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A235" t="s">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
         <v>240</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B253" t="s">
         <v>241</v>
       </c>
-      <c r="C235" t="s">
+      <c r="C253" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A236" t="s">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
         <v>243</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B254" t="s">
         <v>244</v>
       </c>
-      <c r="C236" t="s">
+      <c r="C254" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A237" t="s">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
         <v>246</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B255" t="s">
         <v>247</v>
       </c>
-      <c r="C237" t="s">
+      <c r="C255" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A238" t="s">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A239" t="s">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
         <v>250</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B257" t="s">
         <v>251</v>
       </c>
-      <c r="C239" t="s">
+      <c r="C257" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A240" t="s">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
         <v>253</v>
       </c>
-      <c r="B240" t="s">
+      <c r="B258" t="s">
         <v>254</v>
       </c>
-      <c r="C240" t="s">
+      <c r="C258" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A241" t="s">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
         <v>256</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B259" t="s">
         <v>257</v>
       </c>
-      <c r="C241" t="s">
+      <c r="C259" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A242" t="s">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
         <v>259</v>
       </c>
-      <c r="B242" t="s">
+      <c r="B260" t="s">
         <v>260</v>
       </c>
-      <c r="C242" t="s">
+      <c r="C260" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A243" t="s">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
         <v>262</v>
       </c>
-      <c r="B243" t="s">
+      <c r="B261" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A244" t="s">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A245" t="s">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
         <v>265</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B263" t="s">
         <v>266</v>
       </c>
-      <c r="C245" t="s">
+      <c r="C263" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A246" t="s">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A247" t="s">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
         <v>269</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B265" t="s">
         <v>270</v>
       </c>
-      <c r="C247" t="s">
+      <c r="C265" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A248" t="s">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
         <v>272</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B266" t="s">
         <v>273</v>
       </c>
-      <c r="C248" t="s">
+      <c r="C266" t="s">
         <v>274</v>
       </c>
     </row>

--- a/00-日語文型整理.xlsx
+++ b/00-日語文型整理.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://guandamachine-my.sharepoint.com/personal/ec03_gd_guandamachine_com_tw/Documents/Fly/日語/日語練習網站/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65329EAD-A39C-4205-9A99-4F3A0D911256}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D006D79-9A02-456C-AFF5-61ADEC482D29}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0F3A2E6B-B5D2-4B57-9A1E-3E6BF54CF7A6}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{0F3A2E6B-B5D2-4B57-9A1E-3E6BF54CF7A6}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="865">
   <si>
     <t>わたしわ マイク・ミラーです</t>
   </si>
@@ -721,9 +721,6 @@
   </si>
   <si>
     <t>金曜日(きんようび)までに 出(だ)して ください。  (報告最遲請在星期五交)</t>
-  </si>
-  <si>
-    <t>*ない形 變化 I</t>
   </si>
   <si>
     <t>第一類動詞 V+ウ段音</t>
@@ -2307,6 +2304,470 @@
   </si>
   <si>
     <t>我去北海道滑雪了</t>
+  </si>
+  <si>
+    <t>*第23課文型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>としょかんで ほんを かりる とき、カードが いります</t>
+  </si>
+  <si>
+    <t>從圖書館借書需要藉書證</t>
+  </si>
+  <si>
+    <t>この　ボタンを　おすと、おつりが　でます</t>
+  </si>
+  <si>
+    <t>按這個按鈕找的零錢就會出來</t>
+  </si>
+  <si>
+    <t>よく テレビを みますか</t>
+  </si>
+  <si>
+    <t>よく テレビを 見ますか</t>
+  </si>
+  <si>
+    <t>你常看電視嗎？</t>
+  </si>
+  <si>
+    <t>そうですね. やきゅうの しあいが ある とき、みます</t>
+  </si>
+  <si>
+    <t>そうですね. 野球の 試合が ある とき、見ます</t>
+  </si>
+  <si>
+    <t>是的,有棒球比賽的時候我會去看</t>
+  </si>
+  <si>
+    <t>れいぞうこに なにも ない とき、どう しますか</t>
+  </si>
+  <si>
+    <t>冷蔵庫に 何も ない とき、どう しますか</t>
+  </si>
+  <si>
+    <t>冰箱裡沒東西的時候你會怎麼做?</t>
+  </si>
+  <si>
+    <t>ちかくの レストランへ なにか たべに いきます</t>
+  </si>
+  <si>
+    <t>近くの レストランへ 何か 食べに 行きます</t>
+  </si>
+  <si>
+    <t>我會去附近的餐廳吃點東西</t>
+  </si>
+  <si>
+    <t>図書館で 本を 借りる とき、カードが 要ります</t>
+  </si>
+  <si>
+    <t>この　ボタンを　押すと、お釣りが 出ます</t>
+  </si>
+  <si>
+    <t>かいぎしつを でる とき、エアコンを けしましたか。</t>
+  </si>
+  <si>
+    <t>你離開會議室時關掉冷氣了嗎？</t>
+  </si>
+  <si>
+    <t>すみません, わすれました。</t>
+  </si>
+  <si>
+    <t>すみません, 忘れました。</t>
+  </si>
+  <si>
+    <t>抱歉，我忘了。</t>
+  </si>
+  <si>
+    <t>サントスさんは どこで ふくや くつを かいますか。</t>
+  </si>
+  <si>
+    <t>サントスさんは どこで 服や 靴を 買いますか。</t>
+  </si>
+  <si>
+    <t>桑托斯先生在哪裡買衣服和鞋子？</t>
+  </si>
+  <si>
+    <t>なつやすみや おしょうがつに くにへ かえった とき、かいます。</t>
+  </si>
+  <si>
+    <t>夏休みや お正月に 国へ 帰った とき、買います。</t>
+  </si>
+  <si>
+    <t>他會在暑假或新年回國的時候買。</t>
+  </si>
+  <si>
+    <t>にほんのは ちいさいですから。</t>
+  </si>
+  <si>
+    <t>因為日本的鞋子很小。</t>
+  </si>
+  <si>
+    <t>それは なんですか。</t>
+  </si>
+  <si>
+    <t>それは 何ですか。</t>
+  </si>
+  <si>
+    <t>那是什麼？</t>
+  </si>
+  <si>
+    <t>「げんきちゃ」です。 からだの ちょうしが わるい とき、のみます。</t>
+  </si>
+  <si>
+    <t>那是「元氣茶」。我身體不舒服的時候就喝。</t>
+  </si>
+  <si>
+    <t>ひまな とき、うちへ あそびに きませんか。</t>
+  </si>
+  <si>
+    <t>有空的時候想來我家玩嗎？</t>
+  </si>
+  <si>
+    <t>ええ、ありがとう ございます。</t>
+  </si>
+  <si>
+    <t>是的，非常感謝。</t>
+  </si>
+  <si>
+    <t>がくせいの とき、アルバイトを しましたか。</t>
+  </si>
+  <si>
+    <t>学生の とき、アルバイトを しましたか。</t>
+  </si>
+  <si>
+    <t>你讀書的時候有打工嗎？</t>
+  </si>
+  <si>
+    <t>ええ、とき どき しました。</t>
+  </si>
+  <si>
+    <t>ええ、時々 しました。</t>
+  </si>
+  <si>
+    <t>是的，偶爾會做。</t>
+  </si>
+  <si>
+    <t>おとが ちいさいですね。</t>
+  </si>
+  <si>
+    <t>音が 小さいですね。</t>
+  </si>
+  <si>
+    <t>聲音很小，是嗎？</t>
+  </si>
+  <si>
+    <t>この つまみを みぎへ まわすと、おおきく なります。</t>
+  </si>
+  <si>
+    <t>この つまみを 右へ 回すと、大きく なります。</t>
+  </si>
+  <si>
+    <t>把這個旋鈕向右轉就能調大音量。</t>
+  </si>
+  <si>
+    <t>すみません。 しやくしょは どこですか。</t>
+  </si>
+  <si>
+    <t>すみません。 市役所は どこですか。</t>
+  </si>
+  <si>
+    <t>請問，市政廳在哪裡？</t>
+  </si>
+  <si>
+    <t>この みちを まっすぐ いくと、ひだりに あります。</t>
+  </si>
+  <si>
+    <t>この 道を まっすぐ 行くと、左に あります。</t>
+  </si>
+  <si>
+    <t>沿著這條路直走，它就在你的左邊。</t>
+  </si>
+  <si>
+    <t>会議室を 出る とき、エアコンを 消しましたか。</t>
+  </si>
+  <si>
+    <t>日本のは 小さいですから。</t>
+  </si>
+  <si>
+    <t>「元気茶」です。 体の 調子が 悪い とき、飲みます。</t>
+  </si>
+  <si>
+    <t>暇な とき、うちへ 遊びに 来ませんか。</t>
+  </si>
+  <si>
+    <t>*第6課文型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>あした どこへ いきますか。</t>
+  </si>
+  <si>
+    <t>あした どこへ 行きますか。</t>
+  </si>
+  <si>
+    <t>你明天要去哪裡？</t>
+  </si>
+  <si>
+    <t>ならへ いきます。</t>
+  </si>
+  <si>
+    <t>奈良へ 行きます。</t>
+  </si>
+  <si>
+    <t>我要去奈良。</t>
+  </si>
+  <si>
+    <t>にちようび どこへ いきましたか。</t>
+  </si>
+  <si>
+    <t>日曜日 どこへ 行きましたか。</t>
+  </si>
+  <si>
+    <t>你星期天去哪了？</t>
+  </si>
+  <si>
+    <t>我哪裡也沒去。</t>
+  </si>
+  <si>
+    <t>なんで とうきょうへ いきますか。</t>
+  </si>
+  <si>
+    <t>何で 東京へ 行きますか。</t>
+  </si>
+  <si>
+    <t>如何去東京？</t>
+  </si>
+  <si>
+    <t>しんかんせんで いきます。</t>
+  </si>
+  <si>
+    <t>新幹線で 行きます。</t>
+  </si>
+  <si>
+    <t>我要坐新幹線去。</t>
+  </si>
+  <si>
+    <t>だれと とうきょうへ いきますか。</t>
+  </si>
+  <si>
+    <t>だれと 東京へ 行きますか。</t>
+  </si>
+  <si>
+    <t>你和誰一起去東京？</t>
+  </si>
+  <si>
+    <t>やまださんと いきます。</t>
+  </si>
+  <si>
+    <t>我和山田先生一起去。</t>
+  </si>
+  <si>
+    <t>いつ にほんへ きましたか。</t>
+  </si>
+  <si>
+    <t>いつ 日本へ 来ましたか。</t>
+  </si>
+  <si>
+    <t>你什麼時候來日本的？</t>
+  </si>
+  <si>
+    <t>3がつ25にちに きました。</t>
+  </si>
+  <si>
+    <t>3月25日に 来ました。</t>
+  </si>
+  <si>
+    <t>我3月25日來的。</t>
+  </si>
+  <si>
+    <t>たんじょうびは いつですか。</t>
+  </si>
+  <si>
+    <t>你的生日是什麼時候？</t>
+  </si>
+  <si>
+    <t>6がつ13にちです。</t>
+  </si>
+  <si>
+    <t>6月13日です。</t>
+  </si>
+  <si>
+    <t>是6月13日。</t>
+  </si>
+  <si>
+    <t>どこ[へ]も いきませんでした。</t>
+  </si>
+  <si>
+    <t>どこ[へ]も 行きませんでした。</t>
+  </si>
+  <si>
+    <t>山田さんと 行きます。</t>
+  </si>
+  <si>
+    <t>誕生日は いつですか。</t>
+  </si>
+  <si>
+    <t>わたしは ジュースを のみます。</t>
+  </si>
+  <si>
+    <t>わたしは ジュースを 飲みます。</t>
+  </si>
+  <si>
+    <t>我喝果汁。</t>
+  </si>
+  <si>
+    <t>わたしは えきで しん ぶんを かいます。</t>
+  </si>
+  <si>
+    <t>わたしは 駅で 新聞を 買います。</t>
+  </si>
+  <si>
+    <t>我在車站買的報紙。</t>
+  </si>
+  <si>
+    <t>いっしょに こうべへ いきませんか。</t>
+  </si>
+  <si>
+    <t>いっしょに 神戸へ 行きませんか。</t>
+  </si>
+  <si>
+    <t>要不要一起去神戶呢？</t>
+  </si>
+  <si>
+    <t>ちょっと やすみましょう。</t>
+  </si>
+  <si>
+    <t>ちょっと 休みましょう。</t>
+  </si>
+  <si>
+    <t>我們稍作休息吧。</t>
+  </si>
+  <si>
+    <t>たばこを すいますか。</t>
+  </si>
+  <si>
+    <t>たばこを 吸いますか。</t>
+  </si>
+  <si>
+    <t>你抽煙嗎？</t>
+  </si>
+  <si>
+    <t>いいえ、すいません。</t>
+  </si>
+  <si>
+    <t>いいえ、吸いません。</t>
+  </si>
+  <si>
+    <t>不，我不抽煙。</t>
+  </si>
+  <si>
+    <t>まいあさ なにを たべますか。</t>
+  </si>
+  <si>
+    <t>你每天早上吃什麼？</t>
+  </si>
+  <si>
+    <t>パンと たまごを たべます。</t>
+  </si>
+  <si>
+    <t>パンと 卵を 食べます。</t>
+  </si>
+  <si>
+    <t>我吃麵包和雞蛋。</t>
+  </si>
+  <si>
+    <t>けさ なにを たべましたか。</t>
+  </si>
+  <si>
+    <t>けさ 何を 食べましたか。</t>
+  </si>
+  <si>
+    <t>你今天早上吃了什麼？</t>
+  </si>
+  <si>
+    <t>なにも たべませんでした。</t>
+  </si>
+  <si>
+    <t>何も 食べませんでした。</t>
+  </si>
+  <si>
+    <t>我什麼都沒吃。</t>
+  </si>
+  <si>
+    <t>どようび なにを しましたか。</t>
+  </si>
+  <si>
+    <t>土曜日 何を しましたか。</t>
+  </si>
+  <si>
+    <t>你星期六做了什麼？</t>
+  </si>
+  <si>
+    <t>にほんごを べんきょうしました。 それから えいがを みました。</t>
+  </si>
+  <si>
+    <t>日本語を 勉強しました。 それから 映画を 見ました。</t>
+  </si>
+  <si>
+    <t>我學習了日語，然後看了一部電影。</t>
+  </si>
+  <si>
+    <t>にちようびは なにを しましたか。</t>
+  </si>
+  <si>
+    <t>日曜日は 何を しましたか。</t>
+  </si>
+  <si>
+    <t>你星期天做了什麼？</t>
+  </si>
+  <si>
+    <t>友達と 奈良へ 行きました。</t>
+  </si>
+  <si>
+    <t>我和朋友們去了奈良。</t>
+  </si>
+  <si>
+    <t>你的包包在哪裡買的？</t>
+  </si>
+  <si>
+    <t>我在墨西哥買的。</t>
+  </si>
+  <si>
+    <t>いっしょに ビールを のみませんか。</t>
+  </si>
+  <si>
+    <t>いっしょに ビールを 飲みませんか。</t>
+  </si>
+  <si>
+    <t>我們一起喝杯啤酒吧？</t>
+  </si>
+  <si>
+    <t>ええ、のみましょう。</t>
+  </si>
+  <si>
+    <t>ええ、飲みましょう。</t>
+  </si>
+  <si>
+    <t>好啊，喝一杯去。</t>
+  </si>
+  <si>
+    <t>毎朝 何を 食べますか。</t>
+  </si>
+  <si>
+    <t>メキシコで かいました。</t>
+  </si>
+  <si>
+    <t>メキシコで 買いました。</t>
+  </si>
+  <si>
+    <t>ともだちと ならへ いきました。</t>
+  </si>
+  <si>
+    <t>どこで その かばんを かいましたか。</t>
+  </si>
+  <si>
+    <t>どこで その かばんを 買いましたか。</t>
   </si>
 </sst>
 </file>
@@ -2386,10 +2847,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2689,7 +3146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B91EE72-412B-4BEC-A7E9-A97446845EE1}">
-  <dimension ref="A1:C266"/>
+  <dimension ref="A1:C318"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="57.21875" customWidth="1"/>
@@ -3349,2048 +3806,2611 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B67" t="s">
+        <v>338</v>
+      </c>
+      <c r="C67" t="s">
         <v>339</v>
-      </c>
-      <c r="C67" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>284</v>
+      </c>
+      <c r="B68" t="s">
         <v>285</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>286</v>
-      </c>
-      <c r="C68" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>287</v>
+      </c>
+      <c r="B69" t="s">
         <v>288</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>289</v>
-      </c>
-      <c r="C69" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>290</v>
+      </c>
+      <c r="B70" t="s">
         <v>291</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>292</v>
-      </c>
-      <c r="C70" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>293</v>
+      </c>
+      <c r="B71" t="s">
         <v>294</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>295</v>
-      </c>
-      <c r="C71" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>296</v>
+      </c>
+      <c r="B72" t="s">
         <v>297</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>298</v>
-      </c>
-      <c r="C72" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>299</v>
+      </c>
+      <c r="B73" t="s">
         <v>300</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>301</v>
-      </c>
-      <c r="C73" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B74" t="s">
+        <v>336</v>
+      </c>
+      <c r="C74" t="s">
         <v>337</v>
-      </c>
-      <c r="C74" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>303</v>
+      </c>
+      <c r="B75" t="s">
         <v>304</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>305</v>
-      </c>
-      <c r="C75" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>306</v>
+      </c>
+      <c r="B76" t="s">
         <v>307</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>308</v>
-      </c>
-      <c r="C76" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>309</v>
+      </c>
+      <c r="B77" t="s">
         <v>310</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>311</v>
-      </c>
-      <c r="C77" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>312</v>
+      </c>
+      <c r="B78" t="s">
         <v>313</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>314</v>
-      </c>
-      <c r="C78" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>315</v>
+      </c>
+      <c r="B79" t="s">
         <v>316</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>317</v>
-      </c>
-      <c r="C79" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>318</v>
+      </c>
+      <c r="B80" t="s">
         <v>319</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>320</v>
-      </c>
-      <c r="C80" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>321</v>
+      </c>
+      <c r="B81" t="s">
         <v>322</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>323</v>
-      </c>
-      <c r="C81" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>324</v>
+      </c>
+      <c r="B82" t="s">
         <v>325</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>326</v>
-      </c>
-      <c r="C82" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>327</v>
+      </c>
+      <c r="B83" t="s">
         <v>328</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>329</v>
-      </c>
-      <c r="C83" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>330</v>
+      </c>
+      <c r="B84" t="s">
         <v>331</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>332</v>
-      </c>
-      <c r="C84" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>333</v>
+      </c>
+      <c r="B85" t="s">
         <v>334</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>335</v>
-      </c>
-      <c r="C85" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>341</v>
+      </c>
+      <c r="B87" t="s">
         <v>342</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>343</v>
-      </c>
-      <c r="C87" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>354</v>
+      </c>
+      <c r="C88" t="s">
         <v>355</v>
-      </c>
-      <c r="C88" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>344</v>
+      </c>
+      <c r="B89" t="s">
         <v>345</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>346</v>
-      </c>
-      <c r="C89" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C90" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>348</v>
+      </c>
+      <c r="B91" t="s">
         <v>349</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>350</v>
-      </c>
-      <c r="C91" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>351</v>
+      </c>
+      <c r="B92" t="s">
         <v>352</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>353</v>
-      </c>
-      <c r="C92" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>660</v>
+        <v>775</v>
+      </c>
+      <c r="B93" t="s">
+        <v>776</v>
+      </c>
+      <c r="C93" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>661</v>
+        <v>778</v>
       </c>
       <c r="B94" t="s">
-        <v>667</v>
+        <v>779</v>
       </c>
       <c r="C94" t="s">
-        <v>664</v>
+        <v>780</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>662</v>
+        <v>781</v>
       </c>
       <c r="B95" t="s">
-        <v>668</v>
+        <v>782</v>
       </c>
       <c r="C95" t="s">
-        <v>665</v>
+        <v>783</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>663</v>
+        <v>807</v>
       </c>
       <c r="B96" t="s">
-        <v>669</v>
+        <v>808</v>
       </c>
       <c r="C96" t="s">
-        <v>666</v>
+        <v>784</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>670</v>
+        <v>785</v>
       </c>
       <c r="B97" t="s">
-        <v>671</v>
+        <v>786</v>
       </c>
       <c r="C97" t="s">
-        <v>674</v>
+        <v>787</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>672</v>
+        <v>788</v>
       </c>
       <c r="B98" t="s">
-        <v>673</v>
+        <v>789</v>
       </c>
       <c r="C98" t="s">
-        <v>675</v>
+        <v>790</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>676</v>
+        <v>791</v>
       </c>
       <c r="B99" t="s">
-        <v>677</v>
+        <v>792</v>
       </c>
       <c r="C99" t="s">
-        <v>692</v>
+        <v>793</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>678</v>
+        <v>794</v>
       </c>
       <c r="B100" t="s">
-        <v>679</v>
+        <v>809</v>
       </c>
       <c r="C100" t="s">
-        <v>693</v>
+        <v>795</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>680</v>
+        <v>796</v>
       </c>
       <c r="B101" t="s">
-        <v>681</v>
+        <v>797</v>
       </c>
       <c r="C101" t="s">
-        <v>694</v>
+        <v>798</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>682</v>
+        <v>799</v>
       </c>
       <c r="B102" t="s">
-        <v>683</v>
+        <v>800</v>
       </c>
       <c r="C102" t="s">
-        <v>695</v>
+        <v>801</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>684</v>
+        <v>802</v>
       </c>
       <c r="B103" t="s">
-        <v>685</v>
+        <v>810</v>
       </c>
       <c r="C103" t="s">
-        <v>696</v>
+        <v>803</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>686</v>
+        <v>804</v>
       </c>
       <c r="B104" t="s">
-        <v>687</v>
+        <v>805</v>
       </c>
       <c r="C104" t="s">
-        <v>697</v>
+        <v>806</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>691</v>
-      </c>
-      <c r="B105" t="s">
-        <v>688</v>
-      </c>
-      <c r="C105" t="s">
-        <v>698</v>
+        <v>774</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>689</v>
+        <v>811</v>
       </c>
       <c r="B106" t="s">
-        <v>690</v>
+        <v>812</v>
       </c>
       <c r="C106" t="s">
-        <v>699</v>
+        <v>813</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>700</v>
+        <v>814</v>
       </c>
       <c r="B107" t="s">
-        <v>701</v>
+        <v>815</v>
       </c>
       <c r="C107" t="s">
-        <v>708</v>
+        <v>816</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>702</v>
+        <v>817</v>
       </c>
       <c r="B108" t="s">
-        <v>703</v>
+        <v>818</v>
       </c>
       <c r="C108" t="s">
-        <v>709</v>
+        <v>819</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>704</v>
+        <v>820</v>
       </c>
       <c r="B109" t="s">
-        <v>705</v>
+        <v>821</v>
       </c>
       <c r="C109" t="s">
-        <v>710</v>
+        <v>822</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>706</v>
+        <v>823</v>
       </c>
       <c r="B110" t="s">
-        <v>707</v>
+        <v>824</v>
       </c>
       <c r="C110" t="s">
-        <v>711</v>
+        <v>825</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>170</v>
+        <v>826</v>
+      </c>
+      <c r="B111" t="s">
+        <v>827</v>
+      </c>
+      <c r="C111" t="s">
+        <v>828</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>171</v>
+        <v>829</v>
+      </c>
+      <c r="B112" t="s">
+        <v>859</v>
       </c>
       <c r="C112" t="s">
-        <v>172</v>
+        <v>830</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>173</v>
+        <v>831</v>
       </c>
       <c r="B113" t="s">
-        <v>174</v>
+        <v>832</v>
       </c>
       <c r="C113" t="s">
-        <v>175</v>
+        <v>833</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>176</v>
+        <v>834</v>
+      </c>
+      <c r="B114" t="s">
+        <v>835</v>
       </c>
       <c r="C114" t="s">
-        <v>177</v>
+        <v>836</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>178</v>
+        <v>837</v>
       </c>
       <c r="B115" t="s">
-        <v>179</v>
+        <v>838</v>
       </c>
       <c r="C115" t="s">
-        <v>180</v>
+        <v>839</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>176</v>
+        <v>840</v>
       </c>
       <c r="B116" t="s">
-        <v>181</v>
+        <v>841</v>
       </c>
       <c r="C116" t="s">
-        <v>177</v>
+        <v>842</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>182</v>
+        <v>843</v>
       </c>
       <c r="B117" t="s">
-        <v>183</v>
+        <v>844</v>
       </c>
       <c r="C117" t="s">
-        <v>180</v>
+        <v>845</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>184</v>
+        <v>846</v>
+      </c>
+      <c r="B118" t="s">
+        <v>847</v>
       </c>
       <c r="C118" t="s">
-        <v>185</v>
+        <v>848</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>186</v>
+        <v>862</v>
       </c>
       <c r="B119" t="s">
-        <v>187</v>
+        <v>849</v>
       </c>
       <c r="C119" t="s">
-        <v>188</v>
+        <v>850</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>189</v>
+        <v>863</v>
       </c>
       <c r="B120" t="s">
-        <v>190</v>
+        <v>864</v>
       </c>
       <c r="C120" t="s">
-        <v>191</v>
+        <v>851</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>192</v>
+        <v>860</v>
       </c>
       <c r="B121" t="s">
-        <v>193</v>
+        <v>861</v>
+      </c>
+      <c r="C121" t="s">
+        <v>852</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>194</v>
+        <v>853</v>
       </c>
       <c r="B122" t="s">
-        <v>195</v>
+        <v>854</v>
       </c>
       <c r="C122" t="s">
-        <v>196</v>
+        <v>855</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>197</v>
+        <v>856</v>
       </c>
       <c r="B123" t="s">
-        <v>198</v>
+        <v>857</v>
       </c>
       <c r="C123" t="s">
-        <v>199</v>
+        <v>858</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>200</v>
-      </c>
-      <c r="B124" t="s">
-        <v>202</v>
-      </c>
-      <c r="C124" t="s">
-        <v>201</v>
+        <v>659</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>203</v>
+        <v>660</v>
       </c>
       <c r="B125" t="s">
-        <v>204</v>
+        <v>666</v>
       </c>
       <c r="C125" t="s">
-        <v>205</v>
+        <v>663</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>206</v>
+        <v>661</v>
       </c>
       <c r="B126" t="s">
-        <v>207</v>
+        <v>667</v>
       </c>
       <c r="C126" t="s">
-        <v>208</v>
+        <v>664</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>209</v>
+        <v>662</v>
       </c>
       <c r="B127" t="s">
-        <v>210</v>
+        <v>668</v>
       </c>
       <c r="C127" t="s">
-        <v>211</v>
+        <v>665</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>212</v>
+        <v>669</v>
       </c>
       <c r="B128" t="s">
-        <v>213</v>
+        <v>670</v>
       </c>
       <c r="C128" t="s">
-        <v>214</v>
+        <v>673</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>215</v>
+        <v>671</v>
       </c>
       <c r="B129" t="s">
-        <v>216</v>
+        <v>672</v>
       </c>
       <c r="C129" t="s">
-        <v>217</v>
+        <v>674</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>218</v>
+        <v>675</v>
       </c>
       <c r="B130" t="s">
-        <v>219</v>
+        <v>676</v>
+      </c>
+      <c r="C130" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>358</v>
+        <v>677</v>
+      </c>
+      <c r="B131" t="s">
+        <v>678</v>
+      </c>
+      <c r="C131" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>413</v>
+        <v>679</v>
+      </c>
+      <c r="B132" t="s">
+        <v>680</v>
       </c>
       <c r="C132" t="s">
-        <v>375</v>
+        <v>693</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>414</v>
+        <v>681</v>
       </c>
       <c r="B133" t="s">
-        <v>410</v>
+        <v>682</v>
       </c>
       <c r="C133" t="s">
-        <v>375</v>
+        <v>694</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>411</v>
+        <v>683</v>
+      </c>
+      <c r="B134" t="s">
+        <v>684</v>
       </c>
       <c r="C134" t="s">
-        <v>412</v>
+        <v>695</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>374</v>
+        <v>685</v>
       </c>
       <c r="B135" t="s">
-        <v>359</v>
+        <v>686</v>
       </c>
       <c r="C135" t="s">
-        <v>360</v>
+        <v>696</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>415</v>
+        <v>690</v>
+      </c>
+      <c r="B136" t="s">
+        <v>687</v>
       </c>
       <c r="C136" t="s">
-        <v>416</v>
+        <v>697</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>430</v>
+        <v>688</v>
       </c>
       <c r="B137" t="s">
-        <v>429</v>
+        <v>689</v>
       </c>
       <c r="C137" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>431</v>
+        <v>699</v>
       </c>
       <c r="B138" t="s">
-        <v>428</v>
+        <v>700</v>
       </c>
       <c r="C138" t="s">
-        <v>432</v>
+        <v>707</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>421</v>
+        <v>701</v>
       </c>
       <c r="B139" t="s">
-        <v>422</v>
+        <v>702</v>
       </c>
       <c r="C139" t="s">
-        <v>417</v>
+        <v>708</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>362</v>
+        <v>703</v>
       </c>
       <c r="B140" t="s">
-        <v>363</v>
+        <v>704</v>
       </c>
       <c r="C140" t="s">
-        <v>433</v>
+        <v>709</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>419</v>
+        <v>705</v>
       </c>
       <c r="B141" t="s">
-        <v>418</v>
+        <v>706</v>
       </c>
       <c r="C141" t="s">
-        <v>420</v>
+        <v>710</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>424</v>
-      </c>
-      <c r="B142" t="s">
-        <v>423</v>
-      </c>
-      <c r="C142" t="s">
-        <v>425</v>
+        <v>170</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>434</v>
-      </c>
-      <c r="B143" t="s">
-        <v>435</v>
+        <v>171</v>
       </c>
       <c r="C143" t="s">
-        <v>436</v>
+        <v>172</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>427</v>
+        <v>173</v>
       </c>
       <c r="B144" t="s">
-        <v>426</v>
+        <v>174</v>
       </c>
       <c r="C144" t="s">
-        <v>437</v>
+        <v>175</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>364</v>
+        <v>176</v>
       </c>
       <c r="C145" t="s">
-        <v>365</v>
+        <v>177</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>366</v>
+        <v>178</v>
       </c>
       <c r="B146" t="s">
-        <v>367</v>
+        <v>179</v>
       </c>
       <c r="C146" t="s">
-        <v>368</v>
+        <v>180</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>369</v>
+        <v>176</v>
       </c>
       <c r="B147" t="s">
-        <v>370</v>
+        <v>181</v>
       </c>
       <c r="C147" t="s">
-        <v>371</v>
+        <v>177</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>372</v>
+        <v>182</v>
+      </c>
+      <c r="B148" t="s">
+        <v>183</v>
       </c>
       <c r="C148" t="s">
-        <v>373</v>
+        <v>180</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>376</v>
-      </c>
-      <c r="B149" t="s">
-        <v>377</v>
+        <v>184</v>
       </c>
       <c r="C149" t="s">
-        <v>378</v>
+        <v>185</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>379</v>
+        <v>186</v>
       </c>
       <c r="B150" t="s">
-        <v>380</v>
+        <v>187</v>
       </c>
       <c r="C150" t="s">
-        <v>381</v>
+        <v>188</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>382</v>
+        <v>189</v>
       </c>
       <c r="B151" t="s">
-        <v>383</v>
+        <v>190</v>
+      </c>
+      <c r="C151" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>407</v>
+        <v>192</v>
       </c>
       <c r="B152" t="s">
-        <v>408</v>
-      </c>
-      <c r="C152" t="s">
-        <v>406</v>
+        <v>193</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>384</v>
+        <v>194</v>
       </c>
       <c r="B153" t="s">
-        <v>385</v>
+        <v>195</v>
       </c>
       <c r="C153" t="s">
-        <v>386</v>
+        <v>196</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>387</v>
+        <v>197</v>
       </c>
       <c r="B154" t="s">
-        <v>388</v>
+        <v>198</v>
       </c>
       <c r="C154" t="s">
-        <v>389</v>
+        <v>199</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>390</v>
+        <v>200</v>
       </c>
       <c r="B155" t="s">
-        <v>409</v>
+        <v>202</v>
       </c>
       <c r="C155" t="s">
-        <v>405</v>
+        <v>201</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>391</v>
+        <v>203</v>
       </c>
       <c r="B156" t="s">
-        <v>392</v>
+        <v>204</v>
       </c>
       <c r="C156" t="s">
-        <v>393</v>
+        <v>205</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>394</v>
+        <v>206</v>
       </c>
       <c r="B157" t="s">
-        <v>395</v>
+        <v>207</v>
       </c>
       <c r="C157" t="s">
-        <v>396</v>
+        <v>208</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>397</v>
+        <v>209</v>
+      </c>
+      <c r="B158" t="s">
+        <v>210</v>
       </c>
       <c r="C158" t="s">
-        <v>398</v>
+        <v>211</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>399</v>
+        <v>212</v>
       </c>
       <c r="B159" t="s">
-        <v>400</v>
+        <v>213</v>
       </c>
       <c r="C159" t="s">
-        <v>401</v>
+        <v>214</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>402</v>
+        <v>215</v>
       </c>
       <c r="B160" t="s">
-        <v>403</v>
+        <v>216</v>
       </c>
       <c r="C160" t="s">
-        <v>404</v>
+        <v>217</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>438</v>
+        <v>218</v>
+      </c>
+      <c r="B161" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>488</v>
-      </c>
-      <c r="B162" t="s">
-        <v>439</v>
-      </c>
-      <c r="C162" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>492</v>
-      </c>
-      <c r="B163" t="s">
-        <v>489</v>
+        <v>412</v>
       </c>
       <c r="C163" t="s">
-        <v>490</v>
+        <v>374</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>445</v>
+        <v>413</v>
       </c>
       <c r="B164" t="s">
-        <v>446</v>
+        <v>409</v>
       </c>
       <c r="C164" t="s">
-        <v>441</v>
+        <v>374</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>494</v>
-      </c>
-      <c r="B165" t="s">
-        <v>493</v>
+        <v>410</v>
       </c>
       <c r="C165" t="s">
-        <v>491</v>
+        <v>411</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>442</v>
+        <v>373</v>
       </c>
       <c r="B166" t="s">
-        <v>443</v>
+        <v>358</v>
       </c>
       <c r="C166" t="s">
-        <v>444</v>
+        <v>359</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>447</v>
-      </c>
-      <c r="B167" t="s">
-        <v>448</v>
+        <v>414</v>
       </c>
       <c r="C167" t="s">
-        <v>449</v>
+        <v>415</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="B168" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="C168" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="B169" t="s">
-        <v>454</v>
+        <v>427</v>
       </c>
       <c r="C169" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>456</v>
+        <v>420</v>
       </c>
       <c r="B170" t="s">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="C170" t="s">
-        <v>458</v>
+        <v>416</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>459</v>
+        <v>361</v>
       </c>
       <c r="B171" t="s">
-        <v>460</v>
+        <v>362</v>
       </c>
       <c r="C171" t="s">
-        <v>461</v>
+        <v>432</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>464</v>
+        <v>418</v>
       </c>
       <c r="B172" t="s">
-        <v>462</v>
+        <v>417</v>
       </c>
       <c r="C172" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>465</v>
+        <v>423</v>
       </c>
       <c r="B173" t="s">
-        <v>466</v>
+        <v>422</v>
       </c>
       <c r="C173" t="s">
-        <v>467</v>
+        <v>424</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>468</v>
+        <v>433</v>
       </c>
       <c r="B174" t="s">
-        <v>469</v>
+        <v>434</v>
       </c>
       <c r="C174" t="s">
-        <v>470</v>
+        <v>435</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="B175" t="s">
-        <v>472</v>
+        <v>425</v>
       </c>
       <c r="C175" t="s">
-        <v>473</v>
+        <v>436</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>474</v>
+        <v>363</v>
       </c>
       <c r="C176" t="s">
-        <v>475</v>
+        <v>364</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>476</v>
+        <v>365</v>
       </c>
       <c r="B177" t="s">
-        <v>477</v>
+        <v>366</v>
       </c>
       <c r="C177" t="s">
-        <v>478</v>
+        <v>367</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>479</v>
+        <v>368</v>
       </c>
       <c r="B178" t="s">
-        <v>480</v>
+        <v>369</v>
       </c>
       <c r="C178" t="s">
-        <v>481</v>
+        <v>370</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>482</v>
-      </c>
-      <c r="B179" t="s">
-        <v>483</v>
+        <v>371</v>
       </c>
       <c r="C179" t="s">
-        <v>484</v>
+        <v>372</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>486</v>
+        <v>375</v>
       </c>
       <c r="B180" t="s">
-        <v>487</v>
+        <v>376</v>
       </c>
       <c r="C180" t="s">
-        <v>485</v>
+        <v>377</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>551</v>
+        <v>378</v>
+      </c>
+      <c r="B181" t="s">
+        <v>379</v>
+      </c>
+      <c r="C181" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>553</v>
+        <v>381</v>
       </c>
       <c r="B182" t="s">
-        <v>554</v>
-      </c>
-      <c r="C182" t="s">
-        <v>555</v>
+        <v>382</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>556</v>
+        <v>406</v>
       </c>
       <c r="B183" t="s">
-        <v>557</v>
+        <v>407</v>
       </c>
       <c r="C183" t="s">
-        <v>558</v>
+        <v>405</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>559</v>
+        <v>383</v>
       </c>
       <c r="B184" t="s">
-        <v>560</v>
+        <v>384</v>
       </c>
       <c r="C184" t="s">
-        <v>561</v>
+        <v>385</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>562</v>
+        <v>386</v>
       </c>
       <c r="B185" t="s">
-        <v>563</v>
+        <v>387</v>
       </c>
       <c r="C185" t="s">
-        <v>564</v>
+        <v>388</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>565</v>
+        <v>389</v>
       </c>
       <c r="B186" t="s">
-        <v>566</v>
+        <v>408</v>
       </c>
       <c r="C186" t="s">
-        <v>567</v>
+        <v>404</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>568</v>
+        <v>390</v>
+      </c>
+      <c r="B187" t="s">
+        <v>391</v>
       </c>
       <c r="C187" t="s">
-        <v>569</v>
+        <v>392</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>570</v>
+        <v>393</v>
+      </c>
+      <c r="B188" t="s">
+        <v>394</v>
       </c>
       <c r="C188" t="s">
-        <v>571</v>
+        <v>395</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>572</v>
+        <v>396</v>
       </c>
       <c r="C189" t="s">
-        <v>573</v>
+        <v>397</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>574</v>
+        <v>398</v>
       </c>
       <c r="B190" t="s">
-        <v>575</v>
+        <v>399</v>
       </c>
       <c r="C190" t="s">
-        <v>576</v>
+        <v>400</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>577</v>
+        <v>401</v>
       </c>
       <c r="B191" t="s">
-        <v>578</v>
+        <v>402</v>
       </c>
       <c r="C191" t="s">
-        <v>579</v>
+        <v>403</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>580</v>
-      </c>
-      <c r="B192" t="s">
-        <v>581</v>
-      </c>
-      <c r="C192" t="s">
-        <v>582</v>
+        <v>437</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>583</v>
+        <v>487</v>
+      </c>
+      <c r="B193" t="s">
+        <v>438</v>
       </c>
       <c r="C193" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>585</v>
+        <v>491</v>
+      </c>
+      <c r="B194" t="s">
+        <v>488</v>
       </c>
       <c r="C194" t="s">
-        <v>586</v>
+        <v>489</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>587</v>
+        <v>444</v>
       </c>
       <c r="B195" t="s">
-        <v>588</v>
+        <v>445</v>
       </c>
       <c r="C195" t="s">
-        <v>589</v>
+        <v>440</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>590</v>
+        <v>493</v>
       </c>
       <c r="B196" t="s">
-        <v>591</v>
+        <v>492</v>
       </c>
       <c r="C196" t="s">
-        <v>592</v>
+        <v>490</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>593</v>
+        <v>441</v>
       </c>
       <c r="B197" t="s">
-        <v>601</v>
+        <v>442</v>
       </c>
       <c r="C197" t="s">
-        <v>594</v>
+        <v>443</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>595</v>
+        <v>446</v>
       </c>
       <c r="B198" t="s">
-        <v>602</v>
+        <v>447</v>
       </c>
       <c r="C198" t="s">
-        <v>603</v>
+        <v>448</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>596</v>
+        <v>449</v>
       </c>
       <c r="B199" t="s">
-        <v>597</v>
+        <v>450</v>
       </c>
       <c r="C199" t="s">
-        <v>604</v>
+        <v>451</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>598</v>
+        <v>452</v>
       </c>
       <c r="B200" t="s">
-        <v>599</v>
+        <v>453</v>
       </c>
       <c r="C200" t="s">
-        <v>600</v>
+        <v>454</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>552</v>
+        <v>455</v>
+      </c>
+      <c r="B201" t="s">
+        <v>456</v>
+      </c>
+      <c r="C201" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>605</v>
+        <v>458</v>
       </c>
       <c r="B202" t="s">
-        <v>606</v>
+        <v>459</v>
       </c>
       <c r="C202" t="s">
-        <v>607</v>
+        <v>460</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>608</v>
+        <v>463</v>
       </c>
       <c r="B203" t="s">
-        <v>610</v>
+        <v>461</v>
       </c>
       <c r="C203" t="s">
-        <v>609</v>
+        <v>462</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>611</v>
+        <v>464</v>
       </c>
       <c r="B204" t="s">
-        <v>622</v>
+        <v>465</v>
       </c>
       <c r="C204" t="s">
-        <v>612</v>
+        <v>466</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>613</v>
+        <v>467</v>
       </c>
       <c r="B205" t="s">
-        <v>614</v>
+        <v>468</v>
       </c>
       <c r="C205" t="s">
-        <v>615</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>616</v>
+        <v>470</v>
       </c>
       <c r="B206" t="s">
-        <v>617</v>
+        <v>471</v>
       </c>
       <c r="C206" t="s">
-        <v>618</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>619</v>
-      </c>
-      <c r="B207" t="s">
-        <v>620</v>
+        <v>473</v>
       </c>
       <c r="C207" t="s">
-        <v>621</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>623</v>
+        <v>475</v>
+      </c>
+      <c r="B208" t="s">
+        <v>476</v>
       </c>
       <c r="C208" t="s">
-        <v>624</v>
+        <v>477</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>625</v>
+        <v>478</v>
       </c>
       <c r="B209" t="s">
-        <v>626</v>
+        <v>479</v>
       </c>
       <c r="C209" t="s">
-        <v>627</v>
+        <v>480</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>628</v>
+        <v>481</v>
       </c>
       <c r="B210" t="s">
-        <v>629</v>
+        <v>482</v>
       </c>
       <c r="C210" t="s">
-        <v>630</v>
+        <v>483</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>636</v>
+        <v>485</v>
       </c>
       <c r="B211" t="s">
-        <v>631</v>
+        <v>486</v>
       </c>
       <c r="C211" t="s">
-        <v>632</v>
+        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>633</v>
-      </c>
-      <c r="B212" t="s">
-        <v>634</v>
-      </c>
-      <c r="C212" t="s">
-        <v>635</v>
+        <v>550</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>637</v>
+        <v>552</v>
       </c>
       <c r="B213" t="s">
-        <v>638</v>
+        <v>553</v>
       </c>
       <c r="C213" t="s">
-        <v>639</v>
+        <v>554</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>642</v>
+        <v>555</v>
       </c>
       <c r="B214" t="s">
-        <v>640</v>
+        <v>556</v>
       </c>
       <c r="C214" t="s">
-        <v>641</v>
+        <v>557</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>643</v>
+        <v>558</v>
       </c>
       <c r="B215" t="s">
-        <v>644</v>
+        <v>559</v>
       </c>
       <c r="C215" t="s">
-        <v>645</v>
+        <v>560</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>646</v>
+        <v>561</v>
       </c>
       <c r="B216" t="s">
-        <v>647</v>
+        <v>562</v>
       </c>
       <c r="C216" t="s">
-        <v>648</v>
+        <v>563</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>649</v>
+        <v>564</v>
       </c>
       <c r="B217" t="s">
-        <v>650</v>
+        <v>565</v>
       </c>
       <c r="C217" t="s">
-        <v>651</v>
+        <v>566</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>652</v>
-      </c>
-      <c r="B218" t="s">
-        <v>653</v>
+        <v>567</v>
       </c>
       <c r="C218" t="s">
-        <v>654</v>
+        <v>568</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>659</v>
-      </c>
-      <c r="B219" t="s">
-        <v>655</v>
+        <v>569</v>
       </c>
       <c r="C219" t="s">
-        <v>656</v>
+        <v>570</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>657</v>
+        <v>571</v>
       </c>
       <c r="C220" t="s">
-        <v>658</v>
+        <v>572</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>495</v>
+        <v>573</v>
+      </c>
+      <c r="B221" t="s">
+        <v>574</v>
+      </c>
+      <c r="C221" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>496</v>
+        <v>576</v>
       </c>
       <c r="B222" t="s">
-        <v>497</v>
+        <v>577</v>
       </c>
       <c r="C222" t="s">
-        <v>498</v>
+        <v>578</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>499</v>
+        <v>579</v>
       </c>
       <c r="B223" t="s">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="C223" t="s">
-        <v>501</v>
+        <v>581</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>502</v>
-      </c>
-      <c r="B224" t="s">
-        <v>503</v>
+        <v>582</v>
       </c>
       <c r="C224" t="s">
-        <v>504</v>
+        <v>583</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>505</v>
-      </c>
-      <c r="B225" t="s">
-        <v>506</v>
+        <v>584</v>
       </c>
       <c r="C225" t="s">
-        <v>507</v>
+        <v>585</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>508</v>
+        <v>586</v>
       </c>
       <c r="B226" t="s">
-        <v>509</v>
+        <v>587</v>
       </c>
       <c r="C226" t="s">
-        <v>510</v>
+        <v>588</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>511</v>
+        <v>589</v>
+      </c>
+      <c r="B227" t="s">
+        <v>590</v>
       </c>
       <c r="C227" t="s">
-        <v>512</v>
+        <v>591</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>513</v>
+        <v>592</v>
       </c>
       <c r="B228" t="s">
-        <v>514</v>
+        <v>600</v>
       </c>
       <c r="C228" t="s">
-        <v>515</v>
+        <v>593</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>516</v>
+        <v>594</v>
       </c>
       <c r="B229" t="s">
-        <v>517</v>
+        <v>601</v>
       </c>
       <c r="C229" t="s">
-        <v>518</v>
+        <v>602</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>519</v>
+        <v>595</v>
       </c>
       <c r="B230" t="s">
-        <v>520</v>
+        <v>596</v>
       </c>
       <c r="C230" t="s">
-        <v>521</v>
+        <v>603</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>522</v>
+        <v>597</v>
       </c>
       <c r="B231" t="s">
-        <v>523</v>
+        <v>598</v>
       </c>
       <c r="C231" t="s">
-        <v>524</v>
+        <v>599</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>525</v>
-      </c>
-      <c r="B232" t="s">
-        <v>526</v>
-      </c>
-      <c r="C232" t="s">
-        <v>527</v>
+        <v>551</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>528</v>
+        <v>604</v>
       </c>
       <c r="B233" t="s">
-        <v>529</v>
+        <v>605</v>
       </c>
       <c r="C233" t="s">
-        <v>530</v>
+        <v>606</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>531</v>
+        <v>607</v>
       </c>
       <c r="B234" t="s">
-        <v>540</v>
+        <v>609</v>
       </c>
       <c r="C234" t="s">
-        <v>532</v>
+        <v>608</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>533</v>
+        <v>610</v>
+      </c>
+      <c r="B235" t="s">
+        <v>621</v>
       </c>
       <c r="C235" t="s">
-        <v>534</v>
+        <v>611</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>535</v>
+        <v>612</v>
+      </c>
+      <c r="B236" t="s">
+        <v>613</v>
       </c>
       <c r="C236" t="s">
-        <v>536</v>
+        <v>614</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>537</v>
+        <v>615</v>
       </c>
       <c r="B237" t="s">
-        <v>538</v>
+        <v>616</v>
       </c>
       <c r="C237" t="s">
-        <v>539</v>
+        <v>617</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>541</v>
+        <v>618</v>
       </c>
       <c r="B238" t="s">
-        <v>542</v>
+        <v>619</v>
       </c>
       <c r="C238" t="s">
-        <v>543</v>
+        <v>620</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>544</v>
-      </c>
-      <c r="B239" t="s">
-        <v>550</v>
+        <v>622</v>
       </c>
       <c r="C239" t="s">
-        <v>545</v>
+        <v>623</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>197</v>
+        <v>624</v>
       </c>
       <c r="B240" t="s">
-        <v>198</v>
+        <v>625</v>
       </c>
       <c r="C240" t="s">
-        <v>546</v>
+        <v>626</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>547</v>
+        <v>627</v>
       </c>
       <c r="B241" t="s">
-        <v>548</v>
+        <v>628</v>
       </c>
       <c r="C241" t="s">
-        <v>549</v>
+        <v>629</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>220</v>
+        <v>635</v>
+      </c>
+      <c r="B242" t="s">
+        <v>630</v>
+      </c>
+      <c r="C242" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>221</v>
+        <v>632</v>
       </c>
       <c r="B243" t="s">
-        <v>222</v>
+        <v>633</v>
       </c>
       <c r="C243" t="s">
-        <v>223</v>
+        <v>634</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>275</v>
+        <v>636</v>
       </c>
       <c r="B244" t="s">
-        <v>276</v>
+        <v>637</v>
       </c>
       <c r="C244" t="s">
-        <v>224</v>
+        <v>638</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>225</v>
+        <v>641</v>
       </c>
       <c r="B245" t="s">
-        <v>277</v>
+        <v>639</v>
       </c>
       <c r="C245" t="s">
-        <v>226</v>
+        <v>640</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>278</v>
+        <v>642</v>
       </c>
       <c r="B246" t="s">
-        <v>279</v>
+        <v>643</v>
       </c>
       <c r="C246" t="s">
-        <v>227</v>
+        <v>644</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>228</v>
+        <v>645</v>
       </c>
       <c r="B247" t="s">
-        <v>280</v>
+        <v>646</v>
       </c>
       <c r="C247" t="s">
-        <v>281</v>
+        <v>647</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>229</v>
+        <v>648</v>
       </c>
       <c r="B248" t="s">
-        <v>282</v>
+        <v>649</v>
       </c>
       <c r="C248" t="s">
-        <v>230</v>
+        <v>650</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>231</v>
+        <v>651</v>
       </c>
       <c r="B249" t="s">
-        <v>232</v>
+        <v>652</v>
       </c>
       <c r="C249" t="s">
-        <v>233</v>
+        <v>653</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>234</v>
+        <v>658</v>
       </c>
       <c r="B250" t="s">
-        <v>235</v>
+        <v>654</v>
       </c>
       <c r="C250" t="s">
-        <v>236</v>
+        <v>655</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>237</v>
-      </c>
-      <c r="B251" t="s">
-        <v>238</v>
+        <v>656</v>
+      </c>
+      <c r="C251" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>239</v>
+        <v>494</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>240</v>
+        <v>495</v>
       </c>
       <c r="B253" t="s">
-        <v>241</v>
+        <v>496</v>
       </c>
       <c r="C253" t="s">
-        <v>242</v>
+        <v>497</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>243</v>
+        <v>498</v>
       </c>
       <c r="B254" t="s">
-        <v>244</v>
+        <v>499</v>
       </c>
       <c r="C254" t="s">
-        <v>245</v>
+        <v>500</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>246</v>
+        <v>501</v>
       </c>
       <c r="B255" t="s">
-        <v>247</v>
+        <v>502</v>
       </c>
       <c r="C255" t="s">
-        <v>248</v>
+        <v>503</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>249</v>
+        <v>504</v>
+      </c>
+      <c r="B256" t="s">
+        <v>505</v>
+      </c>
+      <c r="C256" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>250</v>
+        <v>507</v>
       </c>
       <c r="B257" t="s">
-        <v>251</v>
+        <v>508</v>
       </c>
       <c r="C257" t="s">
-        <v>252</v>
+        <v>509</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>253</v>
-      </c>
-      <c r="B258" t="s">
-        <v>254</v>
+        <v>510</v>
       </c>
       <c r="C258" t="s">
-        <v>255</v>
+        <v>511</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="B259" t="s">
-        <v>257</v>
+        <v>513</v>
       </c>
       <c r="C259" t="s">
-        <v>258</v>
+        <v>514</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>259</v>
+        <v>515</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>516</v>
       </c>
       <c r="C260" t="s">
-        <v>261</v>
+        <v>517</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>262</v>
+        <v>518</v>
       </c>
       <c r="B261" t="s">
-        <v>263</v>
+        <v>519</v>
+      </c>
+      <c r="C261" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>264</v>
+        <v>521</v>
+      </c>
+      <c r="B262" t="s">
+        <v>522</v>
+      </c>
+      <c r="C262" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>265</v>
+        <v>524</v>
       </c>
       <c r="B263" t="s">
-        <v>266</v>
+        <v>525</v>
       </c>
       <c r="C263" t="s">
-        <v>267</v>
+        <v>526</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>268</v>
+        <v>527</v>
+      </c>
+      <c r="B264" t="s">
+        <v>528</v>
+      </c>
+      <c r="C264" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>269</v>
+        <v>530</v>
       </c>
       <c r="B265" t="s">
-        <v>270</v>
+        <v>539</v>
       </c>
       <c r="C265" t="s">
-        <v>271</v>
+        <v>531</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
+        <v>532</v>
+      </c>
+      <c r="C266" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>534</v>
+      </c>
+      <c r="C267" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>536</v>
+      </c>
+      <c r="B268" t="s">
+        <v>537</v>
+      </c>
+      <c r="C268" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>540</v>
+      </c>
+      <c r="B269" t="s">
+        <v>541</v>
+      </c>
+      <c r="C269" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>543</v>
+      </c>
+      <c r="B270" t="s">
+        <v>549</v>
+      </c>
+      <c r="C270" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>197</v>
+      </c>
+      <c r="B271" t="s">
+        <v>198</v>
+      </c>
+      <c r="C271" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>546</v>
+      </c>
+      <c r="B272" t="s">
+        <v>547</v>
+      </c>
+      <c r="C272" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>712</v>
+      </c>
+      <c r="B274" t="s">
+        <v>728</v>
+      </c>
+      <c r="C274" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>714</v>
+      </c>
+      <c r="B275" t="s">
+        <v>729</v>
+      </c>
+      <c r="C275" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>716</v>
+      </c>
+      <c r="B276" t="s">
+        <v>717</v>
+      </c>
+      <c r="C276" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>719</v>
+      </c>
+      <c r="B277" t="s">
+        <v>720</v>
+      </c>
+      <c r="C277" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>722</v>
+      </c>
+      <c r="B278" t="s">
+        <v>723</v>
+      </c>
+      <c r="C278" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>725</v>
+      </c>
+      <c r="B279" t="s">
+        <v>726</v>
+      </c>
+      <c r="C279" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>730</v>
+      </c>
+      <c r="B280" t="s">
+        <v>770</v>
+      </c>
+      <c r="C280" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>732</v>
+      </c>
+      <c r="B281" t="s">
+        <v>733</v>
+      </c>
+      <c r="C281" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>735</v>
+      </c>
+      <c r="B282" t="s">
+        <v>736</v>
+      </c>
+      <c r="C282" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>738</v>
+      </c>
+      <c r="B283" t="s">
+        <v>739</v>
+      </c>
+      <c r="C283" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>741</v>
+      </c>
+      <c r="B284" t="s">
+        <v>771</v>
+      </c>
+      <c r="C284" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>743</v>
+      </c>
+      <c r="B285" t="s">
+        <v>744</v>
+      </c>
+      <c r="C285" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>746</v>
+      </c>
+      <c r="B286" t="s">
+        <v>772</v>
+      </c>
+      <c r="C286" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>748</v>
+      </c>
+      <c r="B287" t="s">
+        <v>773</v>
+      </c>
+      <c r="C287" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>750</v>
+      </c>
+      <c r="C288" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>752</v>
+      </c>
+      <c r="B289" t="s">
+        <v>753</v>
+      </c>
+      <c r="C289" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>755</v>
+      </c>
+      <c r="B290" t="s">
+        <v>756</v>
+      </c>
+      <c r="C290" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>758</v>
+      </c>
+      <c r="B291" t="s">
+        <v>759</v>
+      </c>
+      <c r="C291" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>761</v>
+      </c>
+      <c r="B292" t="s">
+        <v>762</v>
+      </c>
+      <c r="C292" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>764</v>
+      </c>
+      <c r="B293" t="s">
+        <v>765</v>
+      </c>
+      <c r="C293" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>767</v>
+      </c>
+      <c r="B294" t="s">
+        <v>768</v>
+      </c>
+      <c r="C294" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>220</v>
+      </c>
+      <c r="B295" t="s">
+        <v>221</v>
+      </c>
+      <c r="C295" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>274</v>
+      </c>
+      <c r="B296" t="s">
+        <v>275</v>
+      </c>
+      <c r="C296" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>224</v>
+      </c>
+      <c r="B297" t="s">
+        <v>276</v>
+      </c>
+      <c r="C297" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>277</v>
+      </c>
+      <c r="B298" t="s">
+        <v>278</v>
+      </c>
+      <c r="C298" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>227</v>
+      </c>
+      <c r="B299" t="s">
+        <v>279</v>
+      </c>
+      <c r="C299" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>228</v>
+      </c>
+      <c r="B300" t="s">
+        <v>281</v>
+      </c>
+      <c r="C300" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>230</v>
+      </c>
+      <c r="B301" t="s">
+        <v>231</v>
+      </c>
+      <c r="C301" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>233</v>
+      </c>
+      <c r="B302" t="s">
+        <v>234</v>
+      </c>
+      <c r="C302" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>236</v>
+      </c>
+      <c r="B303" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>239</v>
+      </c>
+      <c r="B305" t="s">
+        <v>240</v>
+      </c>
+      <c r="C305" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>242</v>
+      </c>
+      <c r="B306" t="s">
+        <v>243</v>
+      </c>
+      <c r="C306" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>245</v>
+      </c>
+      <c r="B307" t="s">
+        <v>246</v>
+      </c>
+      <c r="C307" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>249</v>
+      </c>
+      <c r="B309" t="s">
+        <v>250</v>
+      </c>
+      <c r="C309" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>252</v>
+      </c>
+      <c r="B310" t="s">
+        <v>253</v>
+      </c>
+      <c r="C310" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>255</v>
+      </c>
+      <c r="B311" t="s">
+        <v>256</v>
+      </c>
+      <c r="C311" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>258</v>
+      </c>
+      <c r="B312" t="s">
+        <v>259</v>
+      </c>
+      <c r="C312" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>261</v>
+      </c>
+      <c r="B313" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>264</v>
+      </c>
+      <c r="B315" t="s">
+        <v>265</v>
+      </c>
+      <c r="C315" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>268</v>
+      </c>
+      <c r="B317" t="s">
+        <v>269</v>
+      </c>
+      <c r="C317" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>271</v>
+      </c>
+      <c r="B318" t="s">
         <v>272</v>
       </c>
-      <c r="B266" t="s">
+      <c r="C318" t="s">
         <v>273</v>
-      </c>
-      <c r="C266" t="s">
-        <v>274</v>
       </c>
     </row>
   </sheetData>

--- a/00-日語文型整理.xlsx
+++ b/00-日語文型整理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://guandamachine-my.sharepoint.com/personal/ec03_gd_guandamachine_com_tw/Documents/Fly/日語/日語練習網站/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D006D79-9A02-456C-AFF5-61ADEC482D29}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D0ED304-CB8C-4E80-ADCE-8FE909AAD359}"/>
   <bookViews>
     <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{0F3A2E6B-B5D2-4B57-9A1E-3E6BF54CF7A6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="1091">
   <si>
     <t>わたしわ マイク・ミラーです</t>
   </si>
@@ -2768,6 +2768,790 @@
   </si>
   <si>
     <t>どこで その かばんを 買いましたか。</t>
+  </si>
+  <si>
+    <t>*第7課文型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>わたしは ワープロで てがみを かきます。</t>
+  </si>
+  <si>
+    <t>我用文書軟體(Word Processor)軟體寫信。</t>
+  </si>
+  <si>
+    <t>わたしは きむらさんに はなを あげます。</t>
+  </si>
+  <si>
+    <t>我送花給木村女士。</t>
+  </si>
+  <si>
+    <t>わたしは カリナさんに チョコレートを もらいました。</t>
+  </si>
+  <si>
+    <t>我收到了卡琳娜女士送的巧克力。</t>
+  </si>
+  <si>
+    <t>私は ワープロで 手紙を 書きます。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>私は 木村さんに 花を あげます。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>テレビで にほんごを べんきょうしましたか。</t>
+  </si>
+  <si>
+    <t>テレビで 日本語を 勉強しましたか。</t>
+  </si>
+  <si>
+    <t>你是透過電視學日語的嗎？</t>
+  </si>
+  <si>
+    <t>いいえ、ラジオで べんきょうしました。</t>
+  </si>
+  <si>
+    <t>いいえ、ラジオで 勉強しました。</t>
+  </si>
+  <si>
+    <t>不，我是聽廣播學的。</t>
+  </si>
+  <si>
+    <t>にほんごで レポートを か書きますか。</t>
+  </si>
+  <si>
+    <t>日本語で レポートを 書きますか。</t>
+  </si>
+  <si>
+    <t>你用日文寫報告嗎？</t>
+  </si>
+  <si>
+    <t>いいえ、えいごで かきます。</t>
+  </si>
+  <si>
+    <t>いいえ、英語で 書きます。</t>
+  </si>
+  <si>
+    <t>不，我用英文寫。</t>
+  </si>
+  <si>
+    <t>Goodbyeは にほんごで なんですか。</t>
+  </si>
+  <si>
+    <t>Goodbyeは 日本語で 何ですか。</t>
+  </si>
+  <si>
+    <t>日文的「再見」怎麼說？</t>
+  </si>
+  <si>
+    <t>「さようなら」です。</t>
+  </si>
+  <si>
+    <t>是「Sayonara」。</t>
+  </si>
+  <si>
+    <t>だれに クリスマスカードを かきますか。</t>
+  </si>
+  <si>
+    <t>だれに クリスマスカードを 書きますか。</t>
+  </si>
+  <si>
+    <t>你在寫聖誕卡給誰？</t>
+  </si>
+  <si>
+    <t>かぞくと ともだちに かきます。</t>
+  </si>
+  <si>
+    <t>家族と 友達に 書きます。</t>
+  </si>
+  <si>
+    <t>我寫給我的家人和朋友。</t>
+  </si>
+  <si>
+    <t>てちょうです。 やまださんに もらいました。</t>
+  </si>
+  <si>
+    <t>手帳です。 山田さんに もらいました。</t>
+  </si>
+  <si>
+    <t>那是筆記本。山田先生給我的。</t>
+  </si>
+  <si>
+    <t>もう しんかんせんの きっぷを かいましたか。</t>
+  </si>
+  <si>
+    <t>もう 新幹線の 切符を 買いましたか。</t>
+  </si>
+  <si>
+    <t>你已經買好新幹線車票了嗎？</t>
+  </si>
+  <si>
+    <t>はい、もう かいました。</t>
+  </si>
+  <si>
+    <t>はい、もう 買いました。</t>
+  </si>
+  <si>
+    <t>是的，我已經買了。</t>
+  </si>
+  <si>
+    <t>もう ひるごはんを たべましたか。</t>
+  </si>
+  <si>
+    <t>もう 昼ごはんを 食べましたか。</t>
+  </si>
+  <si>
+    <t>你吃過午餐了嗎？</t>
+  </si>
+  <si>
+    <t>いいえ、まだです。 これから たべます。</t>
+  </si>
+  <si>
+    <t>いいえ、まだです。 これから 食べます。</t>
+  </si>
+  <si>
+    <t>還沒有。我現在就去吃。</t>
+  </si>
+  <si>
+    <t>*第8課文型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さくらは きれいです。</t>
+  </si>
+  <si>
+    <t>桜は きれいです。</t>
+  </si>
+  <si>
+    <t>櫻花真美。</t>
+  </si>
+  <si>
+    <t>ふじさんは たかいです。</t>
+  </si>
+  <si>
+    <t>富士山は 高いです。</t>
+  </si>
+  <si>
+    <t>富士山很高。</t>
+  </si>
+  <si>
+    <t>さくらは きれいな はなです。</t>
+  </si>
+  <si>
+    <t>桜は きれいな 花です。</t>
+  </si>
+  <si>
+    <t>櫻花是美麗的花朵。</t>
+  </si>
+  <si>
+    <t>ふじさんは たかい やまです。</t>
+  </si>
+  <si>
+    <t>富士山是一座高山。</t>
+  </si>
+  <si>
+    <t>富士山は 高い 山です。</t>
+  </si>
+  <si>
+    <t>おおさかは にぎやかですか。</t>
+  </si>
+  <si>
+    <t>大阪は にぎやかですか。</t>
+  </si>
+  <si>
+    <t>大阪熱鬧嗎？</t>
+  </si>
+  <si>
+    <t>はい、にぎやかです。</t>
+  </si>
+  <si>
+    <t>是的,很熱鬧。</t>
+  </si>
+  <si>
+    <t>びわこの みずは きれいですか。</t>
+  </si>
+  <si>
+    <t>琵琶湖の 水は きれいですか。</t>
+  </si>
+  <si>
+    <t>琵琶湖的水乾淨嗎？</t>
+  </si>
+  <si>
+    <t>いいえ、あまり きれいじゃ(では) ありません。</t>
+  </si>
+  <si>
+    <t>不,不太乾淨。</t>
+  </si>
+  <si>
+    <t>ペキンは いま さむいですか。</t>
+  </si>
+  <si>
+    <t>ペキンは 今 寒いですか。</t>
+  </si>
+  <si>
+    <t>北京現在冷嗎？</t>
+  </si>
+  <si>
+    <t>はい、とても さむいです。</t>
+  </si>
+  <si>
+    <t>はい、とても 寒いです。</t>
+  </si>
+  <si>
+    <t>是的,很冷。</t>
+  </si>
+  <si>
+    <t>シャンハイも さむいですか。</t>
+  </si>
+  <si>
+    <t>シャンハイも 寒いですか。</t>
+  </si>
+  <si>
+    <t>上海也冷嗎？</t>
+  </si>
+  <si>
+    <t>いいえ、あまり さむくないです。</t>
+  </si>
+  <si>
+    <t>いいえ、あまり 寒くないです。</t>
+  </si>
+  <si>
+    <t>不,不太冷。</t>
+  </si>
+  <si>
+    <t>その じしょは いいですか。</t>
+  </si>
+  <si>
+    <t>その 辞書は いいですか。</t>
+  </si>
+  <si>
+    <t>那本字典好用嗎？</t>
+  </si>
+  <si>
+    <t>いいえ、あまり よくないです。</t>
+  </si>
+  <si>
+    <t>不,不太好用。</t>
+  </si>
+  <si>
+    <t>とうきょうの ちかてつは どうですか。</t>
+  </si>
+  <si>
+    <t>東京の 地下鉄は どうですか。</t>
+  </si>
+  <si>
+    <t>你覺得東京地鐵怎麼樣？</t>
+  </si>
+  <si>
+    <t>きれいです。 そして べんりです。</t>
+  </si>
+  <si>
+    <t>きれいです。 そして 便利です。</t>
+  </si>
+  <si>
+    <t>很乾淨,也很方便。很漂亮,也很方便。</t>
+  </si>
+  <si>
+    <t>きのう えいが 映画を みました。</t>
+  </si>
+  <si>
+    <t>きのう 映画を 見ました。</t>
+  </si>
+  <si>
+    <t>我昨天看了一部電影。</t>
+  </si>
+  <si>
+    <t>どんな えいがですか。</t>
+  </si>
+  <si>
+    <t>どんな 映画ですか。</t>
+  </si>
+  <si>
+    <t>是什麼類型的電影？</t>
+  </si>
+  <si>
+    <t>「しちにんの さむらい」です。 ふるいですが、とても おもしろい えいがです。</t>
+  </si>
+  <si>
+    <t>「七人の 侍」です。 古いですが、とても おもしろい 映画です。</t>
+  </si>
+  <si>
+    <t>是《七武士》。雖然是老電影,但非常有趣。</t>
+  </si>
+  <si>
+    <t>ミラーさんの かさは どれですか。</t>
+  </si>
+  <si>
+    <t>ミラーさんの 傘は どれですか。</t>
+  </si>
+  <si>
+    <t>哪一把是米勒先生的傘？</t>
+  </si>
+  <si>
+    <t>あの あおい かさです。</t>
+  </si>
+  <si>
+    <t>あの 青い 傘です。</t>
+  </si>
+  <si>
+    <t>那把藍色的傘。</t>
+  </si>
+  <si>
+    <t>*第9課文型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>私は イタリア料理が 好きです。</t>
+  </si>
+  <si>
+    <t>我喜歡義大利菜。</t>
+  </si>
+  <si>
+    <t>わたしは にほんごが すこし わかります。</t>
+  </si>
+  <si>
+    <t>私は 日本語が 少し わかります。</t>
+  </si>
+  <si>
+    <t>我懂一點日文。</t>
+  </si>
+  <si>
+    <t>きょうは こどもの たんじょうびですから、はやく かえります。</t>
+  </si>
+  <si>
+    <t>きょうは 子どもの 誕生日ですから、早く 帰ります。</t>
+  </si>
+  <si>
+    <t>今天是孩子的生日，所以我要早點回家。</t>
+  </si>
+  <si>
+    <t>わたしは イタリアりょうりが すきです。</t>
+  </si>
+  <si>
+    <t>おさけが すきですか。</t>
+  </si>
+  <si>
+    <t>你喜歡喝酒嗎？</t>
+  </si>
+  <si>
+    <t>お酒が 好きですか。</t>
+  </si>
+  <si>
+    <t>いいえ、すきじゃ(では) ありません。</t>
+  </si>
+  <si>
+    <t>いいえ、好きじゃ(では) ありません。</t>
+  </si>
+  <si>
+    <t>不，我不喜歡。</t>
+  </si>
+  <si>
+    <t>どんな スポーツが すきですか。</t>
+  </si>
+  <si>
+    <t>どんな スポーツが 好きですか。</t>
+  </si>
+  <si>
+    <t>你喜歡什麼運動？</t>
+  </si>
+  <si>
+    <t>サッカーが すきです。</t>
+  </si>
+  <si>
+    <t>サッカーが 好きです。</t>
+  </si>
+  <si>
+    <t>我喜歡足球。</t>
+  </si>
+  <si>
+    <t>カリナさんは えが じょうずですか。</t>
+  </si>
+  <si>
+    <t>カリナさんは 絵が 上手ですか。</t>
+  </si>
+  <si>
+    <t>卡琳娜擅長畫畫嗎？</t>
+  </si>
+  <si>
+    <t>はい、[カリナさんは] とても じょうずです。</t>
+  </si>
+  <si>
+    <t>はい、[カリナさんは] とても 上手です。</t>
+  </si>
+  <si>
+    <t>是的，卡琳娜畫得很好。</t>
+  </si>
+  <si>
+    <t>たなかさんは インドネシアごが わかりますか。</t>
+  </si>
+  <si>
+    <t>田中さんは インドネシア語が わかりますか。</t>
+  </si>
+  <si>
+    <t>田中懂印尼語嗎？</t>
+  </si>
+  <si>
+    <t>いいえ、ぜんぜん わかりません。</t>
+  </si>
+  <si>
+    <t>いいえ、全然 わかりません。</t>
+  </si>
+  <si>
+    <t>不，我完全不懂。</t>
+  </si>
+  <si>
+    <t>こまかい おかねが ありますか。</t>
+  </si>
+  <si>
+    <t>細かい お金が ありますか。</t>
+  </si>
+  <si>
+    <t>你有零錢嗎？</t>
+  </si>
+  <si>
+    <t>いいえ、ありません。</t>
+  </si>
+  <si>
+    <t>沒有。</t>
+  </si>
+  <si>
+    <t>まいあさ しんぶんを よみますか。</t>
+  </si>
+  <si>
+    <t>毎朝 新聞を 読みますか。</t>
+  </si>
+  <si>
+    <t>你每天早上都會​​讀報紙嗎？</t>
+  </si>
+  <si>
+    <t>いいえ、じかんが ありませんから、よみません。</t>
+  </si>
+  <si>
+    <t>いいえ、時間が ありませんから、読みません。</t>
+  </si>
+  <si>
+    <t>不，我沒時間，所以我不讀。</t>
+  </si>
+  <si>
+    <t>どうして きのう はやく かえりましたか。</t>
+  </si>
+  <si>
+    <t>どうして きのう 早く 帰りましたか。</t>
+  </si>
+  <si>
+    <t>你昨天為什麼提早回家了？</t>
+  </si>
+  <si>
+    <t>ようじが ありましたから。</t>
+  </si>
+  <si>
+    <t>用事が ありましたから。</t>
+  </si>
+  <si>
+    <t>因為我有事要做。</t>
+  </si>
+  <si>
+    <t>*第10課文型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>います(いる)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>用於</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>物品、植物、固定不動的物體</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等無生命、無法自主活動的對象。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>用於</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>人、動物、昆蟲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等有生命且能自主活動的生物。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>あります(ある)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~ 存在，~在(有生命)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~ 存在，~在(無生命)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鬼怪、幽靈在日本文化中被視為有生命的，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>あそこに さとうさんが います。</t>
+  </si>
+  <si>
+    <t>あそこに 佐藤さんが います。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">佐藤先生在那邊。  </t>
+  </si>
+  <si>
+    <t>つくえの うえに しゃしんが あります。</t>
+  </si>
+  <si>
+    <t>机の 上に 写真が あります。</t>
+  </si>
+  <si>
+    <t>桌子上有一張照片。</t>
+  </si>
+  <si>
+    <t>かぞくは ニューヨークに います。</t>
+  </si>
+  <si>
+    <t>家族は ニューヨークに います。</t>
+  </si>
+  <si>
+    <t>我的家人在紐約。</t>
+  </si>
+  <si>
+    <t>とうきょうィズニーランドは ちばけんに あります。</t>
+  </si>
+  <si>
+    <t>東京ディズニーランドは 千葉県に あります。</t>
+  </si>
+  <si>
+    <t>東京迪士尼樂園位於千葉縣。</t>
+  </si>
+  <si>
+    <t>基本結構</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>場所 + に + 主體 + います</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>場所 + に + 主體 + あります</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鬼怪、幽靈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>います例外</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>にわ に ねこが います</t>
+  </si>
+  <si>
+    <t>庭 に 猫が います</t>
+  </si>
+  <si>
+    <t>庭院有貓。- 動物</t>
+  </si>
+  <si>
+    <t>きょうしつ に せんせが います</t>
+  </si>
+  <si>
+    <t>教室 に 先生が います</t>
+  </si>
+  <si>
+    <t>教室有老師。- 人</t>
+  </si>
+  <si>
+    <t>つくえのうえ に ほんが あります</t>
+  </si>
+  <si>
+    <t>机の上 に 本が あります</t>
+  </si>
+  <si>
+    <t>桌子上有書。- 物品</t>
+  </si>
+  <si>
+    <t>あそこに おとこの ひとが いますね。 あの ひとは だれですか。</t>
+  </si>
+  <si>
+    <t>あそこに 男の 人が いますね。 あの 人は だれですか。</t>
+  </si>
+  <si>
+    <t>那邊有個男人。他是誰？</t>
+  </si>
+  <si>
+    <t>IMCの まつもとさんです。</t>
+  </si>
+  <si>
+    <t>IMCの 松本さんです。</t>
+  </si>
+  <si>
+    <t>那是IMC的松本先生。</t>
+  </si>
+  <si>
+    <t>この ちかくに でんわが ありますか。</t>
+  </si>
+  <si>
+    <t>この 近くに 電話が ありますか。</t>
+  </si>
+  <si>
+    <t>附近有電話嗎？</t>
+  </si>
+  <si>
+    <t>はい、あそこに あります。</t>
+  </si>
+  <si>
+    <t>有，那邊有一部。</t>
+  </si>
+  <si>
+    <t>にわに だれが いますか。</t>
+  </si>
+  <si>
+    <t>庭に だれが いますか。</t>
+  </si>
+  <si>
+    <t>花園裡誰在？</t>
+  </si>
+  <si>
+    <t>だれも いません。ねこが います。</t>
+  </si>
+  <si>
+    <t>だれも いません。猫が います。</t>
+  </si>
+  <si>
+    <t>那裡沒人。有一隻貓。</t>
+  </si>
+  <si>
+    <t>はこの なかに なにが ありますか。</t>
+  </si>
+  <si>
+    <t>箱の 中に 何が ありますか。</t>
+  </si>
+  <si>
+    <t>這個盒子裡裝的是什麼？</t>
+  </si>
+  <si>
+    <t>ふるい てがみや しゃしん [など]が あります。</t>
+  </si>
+  <si>
+    <t>古い 手紙や 写真 [など]が あります。</t>
+  </si>
+  <si>
+    <t>裡面有一些舊信件和照片[等等]。</t>
+  </si>
+  <si>
+    <t>かいぎしつに います。</t>
+  </si>
+  <si>
+    <t>会議室に います。</t>
+  </si>
+  <si>
+    <t>在會議室。</t>
+  </si>
+  <si>
+    <t>ゆうびんきょくは どこに ありますか。</t>
+  </si>
+  <si>
+    <t>郵便局は どこに ありますか。</t>
+  </si>
+  <si>
+    <t>郵局在哪裡？</t>
+  </si>
+  <si>
+    <t>えきの ちかくです。ぎんこうの まえに あります。</t>
+  </si>
+  <si>
+    <t>駅の 近くです。銀行の 前に あります。</t>
+  </si>
+  <si>
+    <t>就在車站附近。就在銀行對面。</t>
+  </si>
+  <si>
+    <t>ミラーさんは どこに いますか。</t>
   </si>
 </sst>
 </file>
@@ -2827,11 +3611,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2847,6 +3634,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3146,7 +3937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B91EE72-412B-4BEC-A7E9-A97446845EE1}">
-  <dimension ref="A1:C318"/>
+  <dimension ref="A1:C400"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="57.21875" customWidth="1"/>
@@ -4420,1996 +5211,2850 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>659</v>
+        <v>865</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>660</v>
+        <v>866</v>
       </c>
       <c r="B125" t="s">
-        <v>666</v>
+        <v>872</v>
       </c>
       <c r="C125" t="s">
-        <v>663</v>
+        <v>867</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>661</v>
+        <v>868</v>
       </c>
       <c r="B126" t="s">
-        <v>667</v>
+        <v>873</v>
       </c>
       <c r="C126" t="s">
-        <v>664</v>
+        <v>869</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>662</v>
-      </c>
-      <c r="B127" t="s">
-        <v>668</v>
+        <v>870</v>
       </c>
       <c r="C127" t="s">
-        <v>665</v>
+        <v>871</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>669</v>
+        <v>874</v>
       </c>
       <c r="B128" t="s">
-        <v>670</v>
+        <v>875</v>
       </c>
       <c r="C128" t="s">
-        <v>673</v>
+        <v>876</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>671</v>
+        <v>877</v>
       </c>
       <c r="B129" t="s">
-        <v>672</v>
+        <v>878</v>
       </c>
       <c r="C129" t="s">
-        <v>674</v>
+        <v>879</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>675</v>
+        <v>880</v>
       </c>
       <c r="B130" t="s">
-        <v>676</v>
+        <v>881</v>
       </c>
       <c r="C130" t="s">
-        <v>691</v>
+        <v>882</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>677</v>
+        <v>883</v>
       </c>
       <c r="B131" t="s">
-        <v>678</v>
+        <v>884</v>
       </c>
       <c r="C131" t="s">
-        <v>692</v>
+        <v>885</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>679</v>
+        <v>886</v>
       </c>
       <c r="B132" t="s">
-        <v>680</v>
+        <v>887</v>
       </c>
       <c r="C132" t="s">
-        <v>693</v>
+        <v>888</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>681</v>
-      </c>
-      <c r="B133" t="s">
-        <v>682</v>
+        <v>889</v>
       </c>
       <c r="C133" t="s">
-        <v>694</v>
+        <v>890</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>683</v>
+        <v>891</v>
       </c>
       <c r="B134" t="s">
-        <v>684</v>
+        <v>892</v>
       </c>
       <c r="C134" t="s">
-        <v>695</v>
+        <v>893</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>685</v>
+        <v>894</v>
       </c>
       <c r="B135" t="s">
-        <v>686</v>
+        <v>895</v>
       </c>
       <c r="C135" t="s">
-        <v>696</v>
+        <v>896</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>690</v>
+        <v>743</v>
       </c>
       <c r="B136" t="s">
-        <v>687</v>
+        <v>744</v>
       </c>
       <c r="C136" t="s">
-        <v>697</v>
+        <v>745</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>688</v>
+        <v>897</v>
       </c>
       <c r="B137" t="s">
-        <v>689</v>
+        <v>898</v>
       </c>
       <c r="C137" t="s">
-        <v>698</v>
+        <v>899</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>699</v>
+        <v>900</v>
       </c>
       <c r="B138" t="s">
-        <v>700</v>
+        <v>901</v>
       </c>
       <c r="C138" t="s">
-        <v>707</v>
+        <v>902</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>701</v>
+        <v>903</v>
       </c>
       <c r="B139" t="s">
-        <v>702</v>
+        <v>904</v>
       </c>
       <c r="C139" t="s">
-        <v>708</v>
+        <v>905</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>703</v>
+        <v>906</v>
       </c>
       <c r="B140" t="s">
-        <v>704</v>
+        <v>907</v>
       </c>
       <c r="C140" t="s">
-        <v>709</v>
+        <v>908</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>705</v>
+        <v>909</v>
       </c>
       <c r="B141" t="s">
-        <v>706</v>
+        <v>910</v>
       </c>
       <c r="C141" t="s">
-        <v>710</v>
+        <v>911</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>170</v>
+        <v>912</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>171</v>
+        <v>913</v>
+      </c>
+      <c r="B143" t="s">
+        <v>914</v>
       </c>
       <c r="C143" t="s">
-        <v>172</v>
+        <v>915</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>173</v>
+        <v>916</v>
       </c>
       <c r="B144" t="s">
-        <v>174</v>
+        <v>917</v>
       </c>
       <c r="C144" t="s">
-        <v>175</v>
+        <v>918</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>176</v>
+        <v>919</v>
+      </c>
+      <c r="B145" t="s">
+        <v>920</v>
       </c>
       <c r="C145" t="s">
-        <v>177</v>
+        <v>921</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>178</v>
+        <v>922</v>
       </c>
       <c r="B146" t="s">
-        <v>179</v>
+        <v>924</v>
       </c>
       <c r="C146" t="s">
-        <v>180</v>
+        <v>923</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>176</v>
+        <v>925</v>
       </c>
       <c r="B147" t="s">
-        <v>181</v>
+        <v>926</v>
       </c>
       <c r="C147" t="s">
-        <v>177</v>
+        <v>927</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>182</v>
-      </c>
-      <c r="B148" t="s">
-        <v>183</v>
+        <v>928</v>
       </c>
       <c r="C148" t="s">
-        <v>180</v>
+        <v>929</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>184</v>
+        <v>930</v>
+      </c>
+      <c r="B149" t="s">
+        <v>931</v>
       </c>
       <c r="C149" t="s">
-        <v>185</v>
+        <v>932</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>186</v>
-      </c>
-      <c r="B150" t="s">
-        <v>187</v>
+        <v>933</v>
       </c>
       <c r="C150" t="s">
-        <v>188</v>
+        <v>934</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>189</v>
+        <v>935</v>
       </c>
       <c r="B151" t="s">
-        <v>190</v>
+        <v>936</v>
       </c>
       <c r="C151" t="s">
-        <v>191</v>
+        <v>937</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>192</v>
+        <v>938</v>
       </c>
       <c r="B152" t="s">
-        <v>193</v>
+        <v>939</v>
+      </c>
+      <c r="C152" t="s">
+        <v>940</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>194</v>
+        <v>941</v>
       </c>
       <c r="B153" t="s">
-        <v>195</v>
+        <v>942</v>
       </c>
       <c r="C153" t="s">
-        <v>196</v>
+        <v>943</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>197</v>
+        <v>944</v>
       </c>
       <c r="B154" t="s">
-        <v>198</v>
+        <v>945</v>
       </c>
       <c r="C154" t="s">
-        <v>199</v>
+        <v>946</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>200</v>
+        <v>947</v>
       </c>
       <c r="B155" t="s">
-        <v>202</v>
+        <v>948</v>
       </c>
       <c r="C155" t="s">
-        <v>201</v>
+        <v>949</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>203</v>
-      </c>
-      <c r="B156" t="s">
-        <v>204</v>
+        <v>950</v>
       </c>
       <c r="C156" t="s">
-        <v>205</v>
+        <v>951</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>206</v>
+        <v>952</v>
       </c>
       <c r="B157" t="s">
-        <v>207</v>
+        <v>953</v>
       </c>
       <c r="C157" t="s">
-        <v>208</v>
+        <v>954</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>209</v>
+        <v>955</v>
       </c>
       <c r="B158" t="s">
-        <v>210</v>
+        <v>956</v>
       </c>
       <c r="C158" t="s">
-        <v>211</v>
+        <v>957</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>212</v>
+        <v>958</v>
       </c>
       <c r="B159" t="s">
-        <v>213</v>
+        <v>959</v>
       </c>
       <c r="C159" t="s">
-        <v>214</v>
+        <v>960</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>215</v>
+        <v>961</v>
       </c>
       <c r="B160" t="s">
-        <v>216</v>
+        <v>962</v>
       </c>
       <c r="C160" t="s">
-        <v>217</v>
+        <v>963</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>218</v>
+        <v>964</v>
       </c>
       <c r="B161" t="s">
-        <v>219</v>
+        <v>965</v>
+      </c>
+      <c r="C161" t="s">
+        <v>966</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>357</v>
+        <v>967</v>
+      </c>
+      <c r="B162" t="s">
+        <v>968</v>
+      </c>
+      <c r="C162" t="s">
+        <v>969</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>412</v>
+        <v>970</v>
+      </c>
+      <c r="B163" t="s">
+        <v>971</v>
       </c>
       <c r="C163" t="s">
-        <v>374</v>
+        <v>972</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>413</v>
-      </c>
-      <c r="B164" t="s">
-        <v>409</v>
-      </c>
-      <c r="C164" t="s">
-        <v>374</v>
+        <v>973</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>410</v>
+        <v>982</v>
+      </c>
+      <c r="B165" t="s">
+        <v>974</v>
       </c>
       <c r="C165" t="s">
-        <v>411</v>
+        <v>975</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>373</v>
+        <v>976</v>
       </c>
       <c r="B166" t="s">
-        <v>358</v>
+        <v>977</v>
       </c>
       <c r="C166" t="s">
-        <v>359</v>
+        <v>978</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>414</v>
+        <v>979</v>
+      </c>
+      <c r="B167" t="s">
+        <v>980</v>
       </c>
       <c r="C167" t="s">
-        <v>415</v>
+        <v>981</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>429</v>
+        <v>983</v>
       </c>
       <c r="B168" t="s">
-        <v>428</v>
+        <v>984</v>
       </c>
       <c r="C168" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>430</v>
+        <v>986</v>
       </c>
       <c r="B169" t="s">
-        <v>427</v>
+        <v>987</v>
       </c>
       <c r="C169" t="s">
-        <v>431</v>
+        <v>988</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>420</v>
+        <v>989</v>
       </c>
       <c r="B170" t="s">
-        <v>421</v>
+        <v>990</v>
       </c>
       <c r="C170" t="s">
-        <v>416</v>
+        <v>991</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>361</v>
+        <v>992</v>
       </c>
       <c r="B171" t="s">
-        <v>362</v>
+        <v>993</v>
       </c>
       <c r="C171" t="s">
-        <v>432</v>
+        <v>994</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>418</v>
+        <v>995</v>
       </c>
       <c r="B172" t="s">
-        <v>417</v>
+        <v>996</v>
       </c>
       <c r="C172" t="s">
-        <v>419</v>
+        <v>997</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>423</v>
+        <v>998</v>
       </c>
       <c r="B173" t="s">
-        <v>422</v>
+        <v>999</v>
       </c>
       <c r="C173" t="s">
-        <v>424</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>433</v>
+        <v>1001</v>
       </c>
       <c r="B174" t="s">
-        <v>434</v>
+        <v>1002</v>
       </c>
       <c r="C174" t="s">
-        <v>435</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>426</v>
+        <v>1004</v>
       </c>
       <c r="B175" t="s">
-        <v>425</v>
+        <v>1005</v>
       </c>
       <c r="C175" t="s">
-        <v>436</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>363</v>
+        <v>1007</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1008</v>
       </c>
       <c r="C176" t="s">
-        <v>364</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>365</v>
-      </c>
-      <c r="B177" t="s">
-        <v>366</v>
+        <v>1010</v>
       </c>
       <c r="C177" t="s">
-        <v>367</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>368</v>
+        <v>1012</v>
       </c>
       <c r="B178" t="s">
-        <v>369</v>
+        <v>1013</v>
       </c>
       <c r="C178" t="s">
-        <v>370</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>371</v>
+        <v>1015</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1016</v>
       </c>
       <c r="C179" t="s">
-        <v>372</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>375</v>
+        <v>1018</v>
       </c>
       <c r="B180" t="s">
-        <v>376</v>
+        <v>1019</v>
       </c>
       <c r="C180" t="s">
-        <v>377</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>378</v>
+        <v>1021</v>
       </c>
       <c r="B181" t="s">
-        <v>379</v>
+        <v>1022</v>
       </c>
       <c r="C181" t="s">
-        <v>380</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>381</v>
-      </c>
-      <c r="B182" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>406</v>
-      </c>
-      <c r="B183" t="s">
-        <v>407</v>
+        <v>1025</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>1029</v>
       </c>
       <c r="C183" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>383</v>
-      </c>
-      <c r="B184" t="s">
-        <v>384</v>
+        <v>1028</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>1030</v>
       </c>
       <c r="C184" t="s">
-        <v>385</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>386</v>
+        <v>1048</v>
       </c>
       <c r="B185" t="s">
-        <v>387</v>
+        <v>1047</v>
       </c>
       <c r="C185" t="s">
-        <v>388</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>389</v>
+        <v>1044</v>
       </c>
       <c r="B186" t="s">
-        <v>408</v>
+        <v>1045</v>
       </c>
       <c r="C186" t="s">
-        <v>404</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>390</v>
+        <v>1049</v>
       </c>
       <c r="B187" t="s">
-        <v>391</v>
+        <v>1050</v>
       </c>
       <c r="C187" t="s">
-        <v>392</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>393</v>
+        <v>1052</v>
       </c>
       <c r="B188" t="s">
-        <v>394</v>
+        <v>1053</v>
       </c>
       <c r="C188" t="s">
-        <v>395</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>396</v>
+        <v>1055</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1056</v>
       </c>
       <c r="C189" t="s">
-        <v>397</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>398</v>
+        <v>1032</v>
       </c>
       <c r="B190" t="s">
-        <v>399</v>
+        <v>1033</v>
       </c>
       <c r="C190" t="s">
-        <v>400</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>401</v>
+        <v>1035</v>
       </c>
       <c r="B191" t="s">
-        <v>402</v>
+        <v>1036</v>
       </c>
       <c r="C191" t="s">
-        <v>403</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>437</v>
+        <v>1038</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C192" t="s">
+        <v>1040</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>487</v>
+        <v>1041</v>
       </c>
       <c r="B193" t="s">
-        <v>438</v>
+        <v>1042</v>
       </c>
       <c r="C193" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>491</v>
+        <v>1058</v>
       </c>
       <c r="B194" t="s">
-        <v>488</v>
+        <v>1059</v>
       </c>
       <c r="C194" t="s">
-        <v>489</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>444</v>
+        <v>1061</v>
       </c>
       <c r="B195" t="s">
-        <v>445</v>
+        <v>1062</v>
       </c>
       <c r="C195" t="s">
-        <v>440</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>493</v>
+        <v>1064</v>
       </c>
       <c r="B196" t="s">
-        <v>492</v>
+        <v>1065</v>
       </c>
       <c r="C196" t="s">
-        <v>490</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>441</v>
-      </c>
-      <c r="B197" t="s">
-        <v>442</v>
+        <v>1067</v>
       </c>
       <c r="C197" t="s">
-        <v>443</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>446</v>
+        <v>1069</v>
       </c>
       <c r="B198" t="s">
-        <v>447</v>
+        <v>1070</v>
       </c>
       <c r="C198" t="s">
-        <v>448</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>449</v>
+        <v>1072</v>
       </c>
       <c r="B199" t="s">
-        <v>450</v>
+        <v>1073</v>
       </c>
       <c r="C199" t="s">
-        <v>451</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>452</v>
+        <v>1075</v>
       </c>
       <c r="B200" t="s">
-        <v>453</v>
+        <v>1076</v>
       </c>
       <c r="C200" t="s">
-        <v>454</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>455</v>
+        <v>1078</v>
       </c>
       <c r="B201" t="s">
-        <v>456</v>
+        <v>1079</v>
       </c>
       <c r="C201" t="s">
-        <v>457</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>458</v>
-      </c>
-      <c r="B202" t="s">
-        <v>459</v>
+        <v>1090</v>
       </c>
       <c r="C202" t="s">
-        <v>460</v>
+        <v>623</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>463</v>
+        <v>1081</v>
       </c>
       <c r="B203" t="s">
-        <v>461</v>
+        <v>1082</v>
       </c>
       <c r="C203" t="s">
-        <v>462</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>464</v>
+        <v>1084</v>
       </c>
       <c r="B204" t="s">
-        <v>465</v>
+        <v>1085</v>
       </c>
       <c r="C204" t="s">
-        <v>466</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>467</v>
+        <v>1087</v>
       </c>
       <c r="B205" t="s">
-        <v>468</v>
+        <v>1088</v>
       </c>
       <c r="C205" t="s">
-        <v>469</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>470</v>
-      </c>
-      <c r="B206" t="s">
-        <v>471</v>
-      </c>
-      <c r="C206" t="s">
-        <v>472</v>
+        <v>659</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>473</v>
+        <v>660</v>
+      </c>
+      <c r="B207" t="s">
+        <v>666</v>
       </c>
       <c r="C207" t="s">
-        <v>474</v>
+        <v>663</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>475</v>
+        <v>661</v>
       </c>
       <c r="B208" t="s">
-        <v>476</v>
+        <v>667</v>
       </c>
       <c r="C208" t="s">
-        <v>477</v>
+        <v>664</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>478</v>
+        <v>662</v>
       </c>
       <c r="B209" t="s">
-        <v>479</v>
+        <v>668</v>
       </c>
       <c r="C209" t="s">
-        <v>480</v>
+        <v>665</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>481</v>
+        <v>669</v>
       </c>
       <c r="B210" t="s">
-        <v>482</v>
+        <v>670</v>
       </c>
       <c r="C210" t="s">
-        <v>483</v>
+        <v>673</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>485</v>
+        <v>671</v>
       </c>
       <c r="B211" t="s">
-        <v>486</v>
+        <v>672</v>
       </c>
       <c r="C211" t="s">
-        <v>484</v>
+        <v>674</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>550</v>
+        <v>675</v>
+      </c>
+      <c r="B212" t="s">
+        <v>676</v>
+      </c>
+      <c r="C212" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>552</v>
+        <v>677</v>
       </c>
       <c r="B213" t="s">
-        <v>553</v>
+        <v>678</v>
       </c>
       <c r="C213" t="s">
-        <v>554</v>
+        <v>692</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>555</v>
+        <v>679</v>
       </c>
       <c r="B214" t="s">
-        <v>556</v>
+        <v>680</v>
       </c>
       <c r="C214" t="s">
-        <v>557</v>
+        <v>693</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>558</v>
+        <v>681</v>
       </c>
       <c r="B215" t="s">
-        <v>559</v>
+        <v>682</v>
       </c>
       <c r="C215" t="s">
-        <v>560</v>
+        <v>694</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>561</v>
+        <v>683</v>
       </c>
       <c r="B216" t="s">
-        <v>562</v>
+        <v>684</v>
       </c>
       <c r="C216" t="s">
-        <v>563</v>
+        <v>695</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>564</v>
+        <v>685</v>
       </c>
       <c r="B217" t="s">
-        <v>565</v>
+        <v>686</v>
       </c>
       <c r="C217" t="s">
-        <v>566</v>
+        <v>696</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>567</v>
+        <v>690</v>
+      </c>
+      <c r="B218" t="s">
+        <v>687</v>
       </c>
       <c r="C218" t="s">
-        <v>568</v>
+        <v>697</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>569</v>
+        <v>688</v>
+      </c>
+      <c r="B219" t="s">
+        <v>689</v>
       </c>
       <c r="C219" t="s">
-        <v>570</v>
+        <v>698</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>571</v>
+        <v>699</v>
+      </c>
+      <c r="B220" t="s">
+        <v>700</v>
       </c>
       <c r="C220" t="s">
-        <v>572</v>
+        <v>707</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>573</v>
+        <v>701</v>
       </c>
       <c r="B221" t="s">
-        <v>574</v>
+        <v>702</v>
       </c>
       <c r="C221" t="s">
-        <v>575</v>
+        <v>708</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>576</v>
+        <v>703</v>
       </c>
       <c r="B222" t="s">
-        <v>577</v>
+        <v>704</v>
       </c>
       <c r="C222" t="s">
-        <v>578</v>
+        <v>709</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>579</v>
+        <v>705</v>
       </c>
       <c r="B223" t="s">
-        <v>580</v>
+        <v>706</v>
       </c>
       <c r="C223" t="s">
-        <v>581</v>
+        <v>710</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>582</v>
-      </c>
-      <c r="C224" t="s">
-        <v>583</v>
+        <v>170</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>584</v>
+        <v>171</v>
       </c>
       <c r="C225" t="s">
-        <v>585</v>
+        <v>172</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>586</v>
+        <v>173</v>
       </c>
       <c r="B226" t="s">
-        <v>587</v>
+        <v>174</v>
       </c>
       <c r="C226" t="s">
-        <v>588</v>
+        <v>175</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>589</v>
-      </c>
-      <c r="B227" t="s">
-        <v>590</v>
+        <v>176</v>
       </c>
       <c r="C227" t="s">
-        <v>591</v>
+        <v>177</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>592</v>
+        <v>178</v>
       </c>
       <c r="B228" t="s">
-        <v>600</v>
+        <v>179</v>
       </c>
       <c r="C228" t="s">
-        <v>593</v>
+        <v>180</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>594</v>
+        <v>176</v>
       </c>
       <c r="B229" t="s">
-        <v>601</v>
+        <v>181</v>
       </c>
       <c r="C229" t="s">
-        <v>602</v>
+        <v>177</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>595</v>
+        <v>182</v>
       </c>
       <c r="B230" t="s">
-        <v>596</v>
+        <v>183</v>
       </c>
       <c r="C230" t="s">
-        <v>603</v>
+        <v>180</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>597</v>
-      </c>
-      <c r="B231" t="s">
-        <v>598</v>
+        <v>184</v>
       </c>
       <c r="C231" t="s">
-        <v>599</v>
+        <v>185</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>551</v>
+        <v>186</v>
+      </c>
+      <c r="B232" t="s">
+        <v>187</v>
+      </c>
+      <c r="C232" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>604</v>
+        <v>189</v>
       </c>
       <c r="B233" t="s">
-        <v>605</v>
+        <v>190</v>
       </c>
       <c r="C233" t="s">
-        <v>606</v>
+        <v>191</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>607</v>
+        <v>192</v>
       </c>
       <c r="B234" t="s">
-        <v>609</v>
-      </c>
-      <c r="C234" t="s">
-        <v>608</v>
+        <v>193</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>610</v>
+        <v>194</v>
       </c>
       <c r="B235" t="s">
-        <v>621</v>
+        <v>195</v>
       </c>
       <c r="C235" t="s">
-        <v>611</v>
+        <v>196</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>612</v>
+        <v>197</v>
       </c>
       <c r="B236" t="s">
-        <v>613</v>
+        <v>198</v>
       </c>
       <c r="C236" t="s">
-        <v>614</v>
+        <v>199</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>615</v>
+        <v>200</v>
       </c>
       <c r="B237" t="s">
-        <v>616</v>
+        <v>202</v>
       </c>
       <c r="C237" t="s">
-        <v>617</v>
+        <v>201</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>618</v>
+        <v>203</v>
       </c>
       <c r="B238" t="s">
-        <v>619</v>
+        <v>204</v>
       </c>
       <c r="C238" t="s">
-        <v>620</v>
+        <v>205</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>622</v>
+        <v>206</v>
+      </c>
+      <c r="B239" t="s">
+        <v>207</v>
       </c>
       <c r="C239" t="s">
-        <v>623</v>
+        <v>208</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>624</v>
+        <v>209</v>
       </c>
       <c r="B240" t="s">
-        <v>625</v>
+        <v>210</v>
       </c>
       <c r="C240" t="s">
-        <v>626</v>
+        <v>211</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>627</v>
+        <v>212</v>
       </c>
       <c r="B241" t="s">
-        <v>628</v>
+        <v>213</v>
       </c>
       <c r="C241" t="s">
-        <v>629</v>
+        <v>214</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>635</v>
+        <v>215</v>
       </c>
       <c r="B242" t="s">
-        <v>630</v>
+        <v>216</v>
       </c>
       <c r="C242" t="s">
-        <v>631</v>
+        <v>217</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>632</v>
+        <v>218</v>
       </c>
       <c r="B243" t="s">
-        <v>633</v>
-      </c>
-      <c r="C243" t="s">
-        <v>634</v>
+        <v>219</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>636</v>
-      </c>
-      <c r="B244" t="s">
-        <v>637</v>
-      </c>
-      <c r="C244" t="s">
-        <v>638</v>
+        <v>357</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>641</v>
-      </c>
-      <c r="B245" t="s">
-        <v>639</v>
+        <v>412</v>
       </c>
       <c r="C245" t="s">
-        <v>640</v>
+        <v>374</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>642</v>
+        <v>413</v>
       </c>
       <c r="B246" t="s">
-        <v>643</v>
+        <v>409</v>
       </c>
       <c r="C246" t="s">
-        <v>644</v>
+        <v>374</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>645</v>
-      </c>
-      <c r="B247" t="s">
-        <v>646</v>
+        <v>410</v>
       </c>
       <c r="C247" t="s">
-        <v>647</v>
+        <v>411</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>648</v>
+        <v>373</v>
       </c>
       <c r="B248" t="s">
-        <v>649</v>
+        <v>358</v>
       </c>
       <c r="C248" t="s">
-        <v>650</v>
+        <v>359</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>651</v>
-      </c>
-      <c r="B249" t="s">
-        <v>652</v>
+        <v>414</v>
       </c>
       <c r="C249" t="s">
-        <v>653</v>
+        <v>415</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>658</v>
+        <v>429</v>
       </c>
       <c r="B250" t="s">
-        <v>654</v>
+        <v>428</v>
       </c>
       <c r="C250" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>656</v>
+        <v>430</v>
+      </c>
+      <c r="B251" t="s">
+        <v>427</v>
       </c>
       <c r="C251" t="s">
-        <v>657</v>
+        <v>431</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>494</v>
+        <v>420</v>
+      </c>
+      <c r="B252" t="s">
+        <v>421</v>
+      </c>
+      <c r="C252" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>495</v>
+        <v>361</v>
       </c>
       <c r="B253" t="s">
-        <v>496</v>
+        <v>362</v>
       </c>
       <c r="C253" t="s">
-        <v>497</v>
+        <v>432</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>498</v>
+        <v>418</v>
       </c>
       <c r="B254" t="s">
-        <v>499</v>
+        <v>417</v>
       </c>
       <c r="C254" t="s">
-        <v>500</v>
+        <v>419</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>501</v>
+        <v>423</v>
       </c>
       <c r="B255" t="s">
-        <v>502</v>
+        <v>422</v>
       </c>
       <c r="C255" t="s">
-        <v>503</v>
+        <v>424</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>504</v>
+        <v>433</v>
       </c>
       <c r="B256" t="s">
-        <v>505</v>
+        <v>434</v>
       </c>
       <c r="C256" t="s">
-        <v>506</v>
+        <v>435</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>507</v>
+        <v>426</v>
       </c>
       <c r="B257" t="s">
-        <v>508</v>
+        <v>425</v>
       </c>
       <c r="C257" t="s">
-        <v>509</v>
+        <v>436</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>510</v>
+        <v>363</v>
       </c>
       <c r="C258" t="s">
-        <v>511</v>
+        <v>364</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>512</v>
+        <v>365</v>
       </c>
       <c r="B259" t="s">
-        <v>513</v>
+        <v>366</v>
       </c>
       <c r="C259" t="s">
-        <v>514</v>
+        <v>367</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>515</v>
+        <v>368</v>
       </c>
       <c r="B260" t="s">
-        <v>516</v>
+        <v>369</v>
       </c>
       <c r="C260" t="s">
-        <v>517</v>
+        <v>370</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>518</v>
-      </c>
-      <c r="B261" t="s">
-        <v>519</v>
+        <v>371</v>
       </c>
       <c r="C261" t="s">
-        <v>520</v>
+        <v>372</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>521</v>
+        <v>375</v>
       </c>
       <c r="B262" t="s">
-        <v>522</v>
+        <v>376</v>
       </c>
       <c r="C262" t="s">
-        <v>523</v>
+        <v>377</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>524</v>
+        <v>378</v>
       </c>
       <c r="B263" t="s">
-        <v>525</v>
+        <v>379</v>
       </c>
       <c r="C263" t="s">
-        <v>526</v>
+        <v>380</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>527</v>
+        <v>381</v>
       </c>
       <c r="B264" t="s">
-        <v>528</v>
-      </c>
-      <c r="C264" t="s">
-        <v>529</v>
+        <v>382</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>530</v>
+        <v>406</v>
       </c>
       <c r="B265" t="s">
-        <v>539</v>
+        <v>407</v>
       </c>
       <c r="C265" t="s">
-        <v>531</v>
+        <v>405</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>532</v>
+        <v>383</v>
+      </c>
+      <c r="B266" t="s">
+        <v>384</v>
       </c>
       <c r="C266" t="s">
-        <v>533</v>
+        <v>385</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>534</v>
+        <v>386</v>
+      </c>
+      <c r="B267" t="s">
+        <v>387</v>
       </c>
       <c r="C267" t="s">
-        <v>535</v>
+        <v>388</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>536</v>
+        <v>389</v>
       </c>
       <c r="B268" t="s">
-        <v>537</v>
+        <v>408</v>
       </c>
       <c r="C268" t="s">
-        <v>538</v>
+        <v>404</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>540</v>
+        <v>390</v>
       </c>
       <c r="B269" t="s">
-        <v>541</v>
+        <v>391</v>
       </c>
       <c r="C269" t="s">
-        <v>542</v>
+        <v>392</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>543</v>
+        <v>393</v>
       </c>
       <c r="B270" t="s">
-        <v>549</v>
+        <v>394</v>
       </c>
       <c r="C270" t="s">
-        <v>544</v>
+        <v>395</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>197</v>
-      </c>
-      <c r="B271" t="s">
-        <v>198</v>
+        <v>396</v>
       </c>
       <c r="C271" t="s">
-        <v>545</v>
+        <v>397</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>546</v>
+        <v>398</v>
       </c>
       <c r="B272" t="s">
-        <v>547</v>
+        <v>399</v>
       </c>
       <c r="C272" t="s">
-        <v>548</v>
+        <v>400</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>711</v>
+        <v>401</v>
+      </c>
+      <c r="B273" t="s">
+        <v>402</v>
+      </c>
+      <c r="C273" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>712</v>
-      </c>
-      <c r="B274" t="s">
-        <v>728</v>
-      </c>
-      <c r="C274" t="s">
-        <v>713</v>
+        <v>437</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>714</v>
+        <v>487</v>
       </c>
       <c r="B275" t="s">
-        <v>729</v>
+        <v>438</v>
       </c>
       <c r="C275" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>716</v>
+        <v>491</v>
       </c>
       <c r="B276" t="s">
-        <v>717</v>
+        <v>488</v>
       </c>
       <c r="C276" t="s">
-        <v>718</v>
+        <v>489</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>719</v>
+        <v>444</v>
       </c>
       <c r="B277" t="s">
-        <v>720</v>
+        <v>445</v>
       </c>
       <c r="C277" t="s">
-        <v>721</v>
+        <v>440</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>722</v>
+        <v>493</v>
       </c>
       <c r="B278" t="s">
-        <v>723</v>
+        <v>492</v>
       </c>
       <c r="C278" t="s">
-        <v>724</v>
+        <v>490</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>725</v>
+        <v>441</v>
       </c>
       <c r="B279" t="s">
-        <v>726</v>
+        <v>442</v>
       </c>
       <c r="C279" t="s">
-        <v>727</v>
+        <v>443</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>730</v>
+        <v>446</v>
       </c>
       <c r="B280" t="s">
-        <v>770</v>
+        <v>447</v>
       </c>
       <c r="C280" t="s">
-        <v>731</v>
+        <v>448</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>732</v>
+        <v>449</v>
       </c>
       <c r="B281" t="s">
-        <v>733</v>
+        <v>450</v>
       </c>
       <c r="C281" t="s">
-        <v>734</v>
+        <v>451</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>735</v>
+        <v>452</v>
       </c>
       <c r="B282" t="s">
-        <v>736</v>
+        <v>453</v>
       </c>
       <c r="C282" t="s">
-        <v>737</v>
+        <v>454</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>738</v>
+        <v>455</v>
       </c>
       <c r="B283" t="s">
-        <v>739</v>
+        <v>456</v>
       </c>
       <c r="C283" t="s">
-        <v>740</v>
+        <v>457</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>741</v>
+        <v>458</v>
       </c>
       <c r="B284" t="s">
-        <v>771</v>
+        <v>459</v>
       </c>
       <c r="C284" t="s">
-        <v>742</v>
+        <v>460</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>743</v>
+        <v>463</v>
       </c>
       <c r="B285" t="s">
-        <v>744</v>
+        <v>461</v>
       </c>
       <c r="C285" t="s">
-        <v>745</v>
+        <v>462</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>746</v>
+        <v>464</v>
       </c>
       <c r="B286" t="s">
-        <v>772</v>
+        <v>465</v>
       </c>
       <c r="C286" t="s">
-        <v>747</v>
+        <v>466</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>748</v>
+        <v>467</v>
       </c>
       <c r="B287" t="s">
-        <v>773</v>
+        <v>468</v>
       </c>
       <c r="C287" t="s">
-        <v>749</v>
+        <v>469</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>750</v>
+        <v>470</v>
+      </c>
+      <c r="B288" t="s">
+        <v>471</v>
       </c>
       <c r="C288" t="s">
-        <v>751</v>
+        <v>472</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>752</v>
-      </c>
-      <c r="B289" t="s">
-        <v>753</v>
+        <v>473</v>
       </c>
       <c r="C289" t="s">
-        <v>754</v>
+        <v>474</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>755</v>
+        <v>475</v>
       </c>
       <c r="B290" t="s">
-        <v>756</v>
+        <v>476</v>
       </c>
       <c r="C290" t="s">
-        <v>757</v>
+        <v>477</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>758</v>
+        <v>478</v>
       </c>
       <c r="B291" t="s">
-        <v>759</v>
+        <v>479</v>
       </c>
       <c r="C291" t="s">
-        <v>760</v>
+        <v>480</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>761</v>
+        <v>481</v>
       </c>
       <c r="B292" t="s">
-        <v>762</v>
+        <v>482</v>
       </c>
       <c r="C292" t="s">
-        <v>763</v>
+        <v>483</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>764</v>
+        <v>485</v>
       </c>
       <c r="B293" t="s">
-        <v>765</v>
+        <v>486</v>
       </c>
       <c r="C293" t="s">
-        <v>766</v>
+        <v>484</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>767</v>
-      </c>
-      <c r="B294" t="s">
-        <v>768</v>
-      </c>
-      <c r="C294" t="s">
-        <v>769</v>
+        <v>550</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>220</v>
+        <v>552</v>
       </c>
       <c r="B295" t="s">
-        <v>221</v>
+        <v>553</v>
       </c>
       <c r="C295" t="s">
-        <v>222</v>
+        <v>554</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>274</v>
+        <v>555</v>
       </c>
       <c r="B296" t="s">
-        <v>275</v>
+        <v>556</v>
       </c>
       <c r="C296" t="s">
-        <v>223</v>
+        <v>557</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>224</v>
+        <v>558</v>
       </c>
       <c r="B297" t="s">
-        <v>276</v>
+        <v>559</v>
       </c>
       <c r="C297" t="s">
-        <v>225</v>
+        <v>560</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>277</v>
+        <v>561</v>
       </c>
       <c r="B298" t="s">
-        <v>278</v>
+        <v>562</v>
       </c>
       <c r="C298" t="s">
-        <v>226</v>
+        <v>563</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>227</v>
+        <v>564</v>
       </c>
       <c r="B299" t="s">
-        <v>279</v>
+        <v>565</v>
       </c>
       <c r="C299" t="s">
-        <v>280</v>
+        <v>566</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>228</v>
-      </c>
-      <c r="B300" t="s">
-        <v>281</v>
+        <v>567</v>
       </c>
       <c r="C300" t="s">
-        <v>229</v>
+        <v>568</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>230</v>
-      </c>
-      <c r="B301" t="s">
-        <v>231</v>
+        <v>569</v>
       </c>
       <c r="C301" t="s">
-        <v>232</v>
+        <v>570</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>233</v>
-      </c>
-      <c r="B302" t="s">
-        <v>234</v>
+        <v>571</v>
       </c>
       <c r="C302" t="s">
-        <v>235</v>
+        <v>572</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>236</v>
+        <v>573</v>
       </c>
       <c r="B303" t="s">
-        <v>237</v>
+        <v>574</v>
+      </c>
+      <c r="C303" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>238</v>
+        <v>576</v>
+      </c>
+      <c r="B304" t="s">
+        <v>577</v>
+      </c>
+      <c r="C304" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>239</v>
+        <v>579</v>
       </c>
       <c r="B305" t="s">
-        <v>240</v>
+        <v>580</v>
       </c>
       <c r="C305" t="s">
-        <v>241</v>
+        <v>581</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>242</v>
-      </c>
-      <c r="B306" t="s">
-        <v>243</v>
+        <v>582</v>
       </c>
       <c r="C306" t="s">
-        <v>244</v>
+        <v>583</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>245</v>
-      </c>
-      <c r="B307" t="s">
-        <v>246</v>
+        <v>584</v>
       </c>
       <c r="C307" t="s">
-        <v>247</v>
+        <v>585</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>248</v>
+        <v>586</v>
+      </c>
+      <c r="B308" t="s">
+        <v>587</v>
+      </c>
+      <c r="C308" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>249</v>
+        <v>589</v>
       </c>
       <c r="B309" t="s">
-        <v>250</v>
+        <v>590</v>
       </c>
       <c r="C309" t="s">
-        <v>251</v>
+        <v>591</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>252</v>
+        <v>592</v>
       </c>
       <c r="B310" t="s">
-        <v>253</v>
+        <v>600</v>
       </c>
       <c r="C310" t="s">
-        <v>254</v>
+        <v>593</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>255</v>
+        <v>594</v>
       </c>
       <c r="B311" t="s">
-        <v>256</v>
+        <v>601</v>
       </c>
       <c r="C311" t="s">
-        <v>257</v>
+        <v>602</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>258</v>
+        <v>595</v>
       </c>
       <c r="B312" t="s">
-        <v>259</v>
+        <v>596</v>
       </c>
       <c r="C312" t="s">
-        <v>260</v>
+        <v>603</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>261</v>
+        <v>597</v>
       </c>
       <c r="B313" t="s">
-        <v>262</v>
+        <v>598</v>
+      </c>
+      <c r="C313" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>263</v>
+        <v>551</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>264</v>
+        <v>604</v>
       </c>
       <c r="B315" t="s">
-        <v>265</v>
+        <v>605</v>
       </c>
       <c r="C315" t="s">
-        <v>266</v>
+        <v>606</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>267</v>
+        <v>607</v>
+      </c>
+      <c r="B316" t="s">
+        <v>609</v>
+      </c>
+      <c r="C316" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>268</v>
+        <v>610</v>
       </c>
       <c r="B317" t="s">
-        <v>269</v>
+        <v>621</v>
       </c>
       <c r="C317" t="s">
-        <v>270</v>
+        <v>611</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
+        <v>612</v>
+      </c>
+      <c r="B318" t="s">
+        <v>613</v>
+      </c>
+      <c r="C318" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>615</v>
+      </c>
+      <c r="B319" t="s">
+        <v>616</v>
+      </c>
+      <c r="C319" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>618</v>
+      </c>
+      <c r="B320" t="s">
+        <v>619</v>
+      </c>
+      <c r="C320" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>622</v>
+      </c>
+      <c r="C321" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>624</v>
+      </c>
+      <c r="B322" t="s">
+        <v>625</v>
+      </c>
+      <c r="C322" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>627</v>
+      </c>
+      <c r="B323" t="s">
+        <v>628</v>
+      </c>
+      <c r="C323" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>635</v>
+      </c>
+      <c r="B324" t="s">
+        <v>630</v>
+      </c>
+      <c r="C324" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>632</v>
+      </c>
+      <c r="B325" t="s">
+        <v>633</v>
+      </c>
+      <c r="C325" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>636</v>
+      </c>
+      <c r="B326" t="s">
+        <v>637</v>
+      </c>
+      <c r="C326" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>641</v>
+      </c>
+      <c r="B327" t="s">
+        <v>639</v>
+      </c>
+      <c r="C327" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>642</v>
+      </c>
+      <c r="B328" t="s">
+        <v>643</v>
+      </c>
+      <c r="C328" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>645</v>
+      </c>
+      <c r="B329" t="s">
+        <v>646</v>
+      </c>
+      <c r="C329" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>648</v>
+      </c>
+      <c r="B330" t="s">
+        <v>649</v>
+      </c>
+      <c r="C330" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>651</v>
+      </c>
+      <c r="B331" t="s">
+        <v>652</v>
+      </c>
+      <c r="C331" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>658</v>
+      </c>
+      <c r="B332" t="s">
+        <v>654</v>
+      </c>
+      <c r="C332" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>656</v>
+      </c>
+      <c r="C333" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>495</v>
+      </c>
+      <c r="B335" t="s">
+        <v>496</v>
+      </c>
+      <c r="C335" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>498</v>
+      </c>
+      <c r="B336" t="s">
+        <v>499</v>
+      </c>
+      <c r="C336" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>501</v>
+      </c>
+      <c r="B337" t="s">
+        <v>502</v>
+      </c>
+      <c r="C337" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>504</v>
+      </c>
+      <c r="B338" t="s">
+        <v>505</v>
+      </c>
+      <c r="C338" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>507</v>
+      </c>
+      <c r="B339" t="s">
+        <v>508</v>
+      </c>
+      <c r="C339" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>510</v>
+      </c>
+      <c r="C340" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>512</v>
+      </c>
+      <c r="B341" t="s">
+        <v>513</v>
+      </c>
+      <c r="C341" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>515</v>
+      </c>
+      <c r="B342" t="s">
+        <v>516</v>
+      </c>
+      <c r="C342" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>518</v>
+      </c>
+      <c r="B343" t="s">
+        <v>519</v>
+      </c>
+      <c r="C343" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>521</v>
+      </c>
+      <c r="B344" t="s">
+        <v>522</v>
+      </c>
+      <c r="C344" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>524</v>
+      </c>
+      <c r="B345" t="s">
+        <v>525</v>
+      </c>
+      <c r="C345" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>527</v>
+      </c>
+      <c r="B346" t="s">
+        <v>528</v>
+      </c>
+      <c r="C346" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>530</v>
+      </c>
+      <c r="B347" t="s">
+        <v>539</v>
+      </c>
+      <c r="C347" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>532</v>
+      </c>
+      <c r="C348" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>534</v>
+      </c>
+      <c r="C349" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>536</v>
+      </c>
+      <c r="B350" t="s">
+        <v>537</v>
+      </c>
+      <c r="C350" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>540</v>
+      </c>
+      <c r="B351" t="s">
+        <v>541</v>
+      </c>
+      <c r="C351" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A352" t="s">
+        <v>543</v>
+      </c>
+      <c r="B352" t="s">
+        <v>549</v>
+      </c>
+      <c r="C352" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A353" t="s">
+        <v>197</v>
+      </c>
+      <c r="B353" t="s">
+        <v>198</v>
+      </c>
+      <c r="C353" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A354" t="s">
+        <v>546</v>
+      </c>
+      <c r="B354" t="s">
+        <v>547</v>
+      </c>
+      <c r="C354" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A355" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A356" t="s">
+        <v>712</v>
+      </c>
+      <c r="B356" t="s">
+        <v>728</v>
+      </c>
+      <c r="C356" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>714</v>
+      </c>
+      <c r="B357" t="s">
+        <v>729</v>
+      </c>
+      <c r="C357" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>716</v>
+      </c>
+      <c r="B358" t="s">
+        <v>717</v>
+      </c>
+      <c r="C358" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>719</v>
+      </c>
+      <c r="B359" t="s">
+        <v>720</v>
+      </c>
+      <c r="C359" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>722</v>
+      </c>
+      <c r="B360" t="s">
+        <v>723</v>
+      </c>
+      <c r="C360" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>725</v>
+      </c>
+      <c r="B361" t="s">
+        <v>726</v>
+      </c>
+      <c r="C361" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>730</v>
+      </c>
+      <c r="B362" t="s">
+        <v>770</v>
+      </c>
+      <c r="C362" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>732</v>
+      </c>
+      <c r="B363" t="s">
+        <v>733</v>
+      </c>
+      <c r="C363" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>735</v>
+      </c>
+      <c r="B364" t="s">
+        <v>736</v>
+      </c>
+      <c r="C364" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>738</v>
+      </c>
+      <c r="B365" t="s">
+        <v>739</v>
+      </c>
+      <c r="C365" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>741</v>
+      </c>
+      <c r="B366" t="s">
+        <v>771</v>
+      </c>
+      <c r="C366" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>743</v>
+      </c>
+      <c r="B367" t="s">
+        <v>744</v>
+      </c>
+      <c r="C367" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>746</v>
+      </c>
+      <c r="B368" t="s">
+        <v>772</v>
+      </c>
+      <c r="C368" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>748</v>
+      </c>
+      <c r="B369" t="s">
+        <v>773</v>
+      </c>
+      <c r="C369" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>750</v>
+      </c>
+      <c r="C370" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>752</v>
+      </c>
+      <c r="B371" t="s">
+        <v>753</v>
+      </c>
+      <c r="C371" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>755</v>
+      </c>
+      <c r="B372" t="s">
+        <v>756</v>
+      </c>
+      <c r="C372" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>758</v>
+      </c>
+      <c r="B373" t="s">
+        <v>759</v>
+      </c>
+      <c r="C373" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>761</v>
+      </c>
+      <c r="B374" t="s">
+        <v>762</v>
+      </c>
+      <c r="C374" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>764</v>
+      </c>
+      <c r="B375" t="s">
+        <v>765</v>
+      </c>
+      <c r="C375" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>767</v>
+      </c>
+      <c r="B376" t="s">
+        <v>768</v>
+      </c>
+      <c r="C376" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>220</v>
+      </c>
+      <c r="B377" t="s">
+        <v>221</v>
+      </c>
+      <c r="C377" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>274</v>
+      </c>
+      <c r="B378" t="s">
+        <v>275</v>
+      </c>
+      <c r="C378" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>224</v>
+      </c>
+      <c r="B379" t="s">
+        <v>276</v>
+      </c>
+      <c r="C379" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>277</v>
+      </c>
+      <c r="B380" t="s">
+        <v>278</v>
+      </c>
+      <c r="C380" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>227</v>
+      </c>
+      <c r="B381" t="s">
+        <v>279</v>
+      </c>
+      <c r="C381" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>228</v>
+      </c>
+      <c r="B382" t="s">
+        <v>281</v>
+      </c>
+      <c r="C382" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>230</v>
+      </c>
+      <c r="B383" t="s">
+        <v>231</v>
+      </c>
+      <c r="C383" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>233</v>
+      </c>
+      <c r="B384" t="s">
+        <v>234</v>
+      </c>
+      <c r="C384" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>236</v>
+      </c>
+      <c r="B385" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>239</v>
+      </c>
+      <c r="B387" t="s">
+        <v>240</v>
+      </c>
+      <c r="C387" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>242</v>
+      </c>
+      <c r="B388" t="s">
+        <v>243</v>
+      </c>
+      <c r="C388" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>245</v>
+      </c>
+      <c r="B389" t="s">
+        <v>246</v>
+      </c>
+      <c r="C389" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>249</v>
+      </c>
+      <c r="B391" t="s">
+        <v>250</v>
+      </c>
+      <c r="C391" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>252</v>
+      </c>
+      <c r="B392" t="s">
+        <v>253</v>
+      </c>
+      <c r="C392" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>255</v>
+      </c>
+      <c r="B393" t="s">
+        <v>256</v>
+      </c>
+      <c r="C393" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>258</v>
+      </c>
+      <c r="B394" t="s">
+        <v>259</v>
+      </c>
+      <c r="C394" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>261</v>
+      </c>
+      <c r="B395" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>264</v>
+      </c>
+      <c r="B397" t="s">
+        <v>265</v>
+      </c>
+      <c r="C397" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>268</v>
+      </c>
+      <c r="B399" t="s">
+        <v>269</v>
+      </c>
+      <c r="C399" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
         <v>271</v>
       </c>
-      <c r="B318" t="s">
+      <c r="B400" t="s">
         <v>272</v>
       </c>
-      <c r="C318" t="s">
+      <c r="C400" t="s">
         <v>273</v>
       </c>
     </row>

--- a/00-日語文型整理.xlsx
+++ b/00-日語文型整理.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://guandamachine-my.sharepoint.com/personal/ec03_gd_guandamachine_com_tw/Documents/Fly/日語/日語練習網站/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D0ED304-CB8C-4E80-ADCE-8FE909AAD359}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F80A05B-6FA1-4A2D-91AB-FF35B16B82C9}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{0F3A2E6B-B5D2-4B57-9A1E-3E6BF54CF7A6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0F3A2E6B-B5D2-4B57-9A1E-3E6BF54CF7A6}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="1091">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="1140">
   <si>
     <t>わたしわ マイク・ミラーです</t>
   </si>
@@ -2314,9 +2314,6 @@
   </si>
   <si>
     <t>從圖書館借書需要藉書證</t>
-  </si>
-  <si>
-    <t>この　ボタンを　おすと、おつりが　でます</t>
   </si>
   <si>
     <t>按這個按鈕找的零錢就會出來</t>
@@ -3553,12 +3550,203 @@
   <si>
     <t>ミラーさんは どこに いますか。</t>
   </si>
+  <si>
+    <t>～とき</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在…的時候</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是用來連接兩個句子、表示時間點的接續助詞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表示動作尚未完成、或是習慣性的動作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日本へ行くとき、飛行機で本を読みます。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去日本的時候，在飛機上看書。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>動詞た形 + とき</t>
+  </si>
+  <si>
+    <t>V-た + とき</t>
+  </si>
+  <si>
+    <t>表示動作已經完成,類似「當…之後」的感覺。</t>
+  </si>
+  <si>
+    <t>にほんへいったとき、ともだちにかいました</t>
+  </si>
+  <si>
+    <t>日本へ行ったとき、友達に会いました</t>
+  </si>
+  <si>
+    <t>去了日本時,見了朋友</t>
+  </si>
+  <si>
+    <t>名詞 + の + とき</t>
+  </si>
+  <si>
+    <t>N + の + とき</t>
+  </si>
+  <si>
+    <t>子供のとき、よく泣きました</t>
+  </si>
+  <si>
+    <t>小時候,常常哭</t>
+  </si>
+  <si>
+    <t>な形容詞 + な + とき</t>
+  </si>
+  <si>
+    <t>na-adj + な + とき</t>
+  </si>
+  <si>
+    <t>暇なとき、映画を見ます</t>
+  </si>
+  <si>
+    <t>空閒的時候,看電影</t>
+  </si>
+  <si>
+    <t>い形容詞 + とき</t>
+  </si>
+  <si>
+    <t>i-adj + とき</t>
+  </si>
+  <si>
+    <t>喉が痛いとき、薬を飲みます</t>
+  </si>
+  <si>
+    <t>喉嚨痛的時候,喝藥</t>
+  </si>
+  <si>
+    <t>V-る + とき</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">動詞原形 + とき </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大阪へ行く時、カバンを買います。</t>
+  </si>
+  <si>
+    <t>還沒去大阪，在路上或到了才買</t>
+  </si>
+  <si>
+    <t>大阪へ行った時、カバンを買います。</t>
+  </si>
+  <si>
+    <t>預定到了大阪之後才買</t>
+  </si>
+  <si>
+    <t>大阪へ行く時、カバンを買いました。</t>
+  </si>
+  <si>
+    <t>已經去過大阪，是在出發前或路上買的</t>
+  </si>
+  <si>
+    <t>大阪へ行った時、カバンを買いました。</t>
+  </si>
+  <si>
+    <t>已經去過大阪，是在到了大阪之後才買的</t>
+  </si>
+  <si>
+    <t>この　ボタンを　おすと、おつりが　でます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一…就… (動詞辞書形 + と)</t>
+  </si>
+  <si>
+    <t>此用法表示前項成立後，後項必然發生，屬於自然現象、習慣或機械操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">~ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> ~ 表示接續/條件</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>春になると、桜が咲きます</t>
+  </si>
+  <si>
+    <t>自然規律</t>
+  </si>
+  <si>
+    <t>一到春天,櫻花就會開。</t>
+  </si>
+  <si>
+    <t>ボタンを押すと、水が出ます</t>
+  </si>
+  <si>
+    <t>機械操作</t>
+  </si>
+  <si>
+    <t>按下按鈕,水就會出來</t>
+  </si>
+  <si>
+    <t>彼は家に帰ると、すぐ寝ます</t>
+  </si>
+  <si>
+    <t>固定習慣</t>
+  </si>
+  <si>
+    <t>他一回到家,馬上就會睡覺</t>
+  </si>
+  <si>
+    <t>ドアを開けると、猫がいました</t>
+  </si>
+  <si>
+    <t>發現</t>
+  </si>
+  <si>
+    <t>打開門一看,發現有隻貓</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3588,6 +3776,14 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3611,12 +3807,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3641,9 +3840,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3681,7 +3880,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3787,7 +3986,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3929,7 +4128,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3937,7 +4136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B91EE72-412B-4BEC-A7E9-A97446845EE1}">
-  <dimension ref="A1:C400"/>
+  <dimension ref="A1:C420"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="57.21875" customWidth="1"/>
@@ -4876,1155 +5075,1155 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>774</v>
+      </c>
+      <c r="B93" t="s">
         <v>775</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>776</v>
-      </c>
-      <c r="C93" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>777</v>
+      </c>
+      <c r="B94" t="s">
         <v>778</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>779</v>
-      </c>
-      <c r="C94" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>780</v>
+      </c>
+      <c r="B95" t="s">
         <v>781</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
         <v>782</v>
-      </c>
-      <c r="C95" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
+        <v>806</v>
+      </c>
+      <c r="B96" t="s">
         <v>807</v>
       </c>
-      <c r="B96" t="s">
-        <v>808</v>
-      </c>
       <c r="C96" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>784</v>
+      </c>
+      <c r="B97" t="s">
         <v>785</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>786</v>
-      </c>
-      <c r="C97" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>787</v>
+      </c>
+      <c r="B98" t="s">
         <v>788</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>789</v>
-      </c>
-      <c r="C98" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>790</v>
+      </c>
+      <c r="B99" t="s">
         <v>791</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>792</v>
-      </c>
-      <c r="C99" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>793</v>
+      </c>
+      <c r="B100" t="s">
+        <v>808</v>
+      </c>
+      <c r="C100" t="s">
         <v>794</v>
-      </c>
-      <c r="B100" t="s">
-        <v>809</v>
-      </c>
-      <c r="C100" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>795</v>
+      </c>
+      <c r="B101" t="s">
         <v>796</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
         <v>797</v>
-      </c>
-      <c r="C101" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>798</v>
+      </c>
+      <c r="B102" t="s">
         <v>799</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>800</v>
-      </c>
-      <c r="C102" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>801</v>
+      </c>
+      <c r="B103" t="s">
+        <v>809</v>
+      </c>
+      <c r="C103" t="s">
         <v>802</v>
-      </c>
-      <c r="B103" t="s">
-        <v>810</v>
-      </c>
-      <c r="C103" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>803</v>
+      </c>
+      <c r="B104" t="s">
         <v>804</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
         <v>805</v>
-      </c>
-      <c r="C104" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
+        <v>810</v>
+      </c>
+      <c r="B106" t="s">
         <v>811</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
         <v>812</v>
-      </c>
-      <c r="C106" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>813</v>
+      </c>
+      <c r="B107" t="s">
         <v>814</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>815</v>
-      </c>
-      <c r="C107" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>816</v>
+      </c>
+      <c r="B108" t="s">
         <v>817</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
         <v>818</v>
-      </c>
-      <c r="C108" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
+        <v>819</v>
+      </c>
+      <c r="B109" t="s">
         <v>820</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>821</v>
-      </c>
-      <c r="C109" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
+        <v>822</v>
+      </c>
+      <c r="B110" t="s">
         <v>823</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>824</v>
-      </c>
-      <c r="C110" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
+        <v>825</v>
+      </c>
+      <c r="B111" t="s">
         <v>826</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" t="s">
         <v>827</v>
-      </c>
-      <c r="C111" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>828</v>
+      </c>
+      <c r="B112" t="s">
+        <v>858</v>
+      </c>
+      <c r="C112" t="s">
         <v>829</v>
-      </c>
-      <c r="B112" t="s">
-        <v>859</v>
-      </c>
-      <c r="C112" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
+        <v>830</v>
+      </c>
+      <c r="B113" t="s">
         <v>831</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
         <v>832</v>
-      </c>
-      <c r="C113" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
+        <v>833</v>
+      </c>
+      <c r="B114" t="s">
         <v>834</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" t="s">
         <v>835</v>
-      </c>
-      <c r="C114" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
+        <v>836</v>
+      </c>
+      <c r="B115" t="s">
         <v>837</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
         <v>838</v>
-      </c>
-      <c r="C115" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
+        <v>839</v>
+      </c>
+      <c r="B116" t="s">
         <v>840</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C116" t="s">
         <v>841</v>
-      </c>
-      <c r="C116" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
+        <v>842</v>
+      </c>
+      <c r="B117" t="s">
         <v>843</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" t="s">
         <v>844</v>
-      </c>
-      <c r="C117" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
+        <v>845</v>
+      </c>
+      <c r="B118" t="s">
         <v>846</v>
       </c>
-      <c r="B118" t="s">
+      <c r="C118" t="s">
         <v>847</v>
-      </c>
-      <c r="C118" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B119" t="s">
+        <v>848</v>
+      </c>
+      <c r="C119" t="s">
         <v>849</v>
-      </c>
-      <c r="C119" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
+        <v>862</v>
+      </c>
+      <c r="B120" t="s">
         <v>863</v>
       </c>
-      <c r="B120" t="s">
-        <v>864</v>
-      </c>
       <c r="C120" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
+        <v>859</v>
+      </c>
+      <c r="B121" t="s">
         <v>860</v>
       </c>
-      <c r="B121" t="s">
-        <v>861</v>
-      </c>
       <c r="C121" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
+        <v>852</v>
+      </c>
+      <c r="B122" t="s">
         <v>853</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C122" t="s">
         <v>854</v>
-      </c>
-      <c r="C122" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
+        <v>855</v>
+      </c>
+      <c r="B123" t="s">
         <v>856</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
         <v>857</v>
-      </c>
-      <c r="C123" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
+        <v>865</v>
+      </c>
+      <c r="B125" t="s">
+        <v>871</v>
+      </c>
+      <c r="C125" t="s">
         <v>866</v>
-      </c>
-      <c r="B125" t="s">
-        <v>872</v>
-      </c>
-      <c r="C125" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
+        <v>867</v>
+      </c>
+      <c r="B126" t="s">
+        <v>872</v>
+      </c>
+      <c r="C126" t="s">
         <v>868</v>
-      </c>
-      <c r="B126" t="s">
-        <v>873</v>
-      </c>
-      <c r="C126" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
+        <v>869</v>
+      </c>
+      <c r="C127" t="s">
         <v>870</v>
-      </c>
-      <c r="C127" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
+        <v>873</v>
+      </c>
+      <c r="B128" t="s">
         <v>874</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
         <v>875</v>
-      </c>
-      <c r="C128" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
+        <v>876</v>
+      </c>
+      <c r="B129" t="s">
         <v>877</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>878</v>
-      </c>
-      <c r="C129" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
+        <v>879</v>
+      </c>
+      <c r="B130" t="s">
         <v>880</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" t="s">
         <v>881</v>
-      </c>
-      <c r="C130" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
+        <v>882</v>
+      </c>
+      <c r="B131" t="s">
         <v>883</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131" t="s">
         <v>884</v>
-      </c>
-      <c r="C131" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
+        <v>885</v>
+      </c>
+      <c r="B132" t="s">
         <v>886</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
         <v>887</v>
-      </c>
-      <c r="C132" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
+        <v>888</v>
+      </c>
+      <c r="C133" t="s">
         <v>889</v>
-      </c>
-      <c r="C133" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
+        <v>890</v>
+      </c>
+      <c r="B134" t="s">
         <v>891</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" t="s">
         <v>892</v>
-      </c>
-      <c r="C134" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
+        <v>893</v>
+      </c>
+      <c r="B135" t="s">
         <v>894</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" t="s">
         <v>895</v>
-      </c>
-      <c r="C135" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
+        <v>742</v>
+      </c>
+      <c r="B136" t="s">
         <v>743</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C136" t="s">
         <v>744</v>
-      </c>
-      <c r="C136" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
+        <v>896</v>
+      </c>
+      <c r="B137" t="s">
         <v>897</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C137" t="s">
         <v>898</v>
-      </c>
-      <c r="C137" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
+        <v>899</v>
+      </c>
+      <c r="B138" t="s">
         <v>900</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C138" t="s">
         <v>901</v>
-      </c>
-      <c r="C138" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
+        <v>902</v>
+      </c>
+      <c r="B139" t="s">
         <v>903</v>
       </c>
-      <c r="B139" t="s">
+      <c r="C139" t="s">
         <v>904</v>
-      </c>
-      <c r="C139" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
+        <v>905</v>
+      </c>
+      <c r="B140" t="s">
         <v>906</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C140" t="s">
         <v>907</v>
-      </c>
-      <c r="C140" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
+        <v>908</v>
+      </c>
+      <c r="B141" t="s">
         <v>909</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C141" t="s">
         <v>910</v>
-      </c>
-      <c r="C141" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
+        <v>912</v>
+      </c>
+      <c r="B143" t="s">
         <v>913</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
         <v>914</v>
-      </c>
-      <c r="C143" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>915</v>
+      </c>
+      <c r="B144" t="s">
         <v>916</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
         <v>917</v>
-      </c>
-      <c r="C144" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
+        <v>918</v>
+      </c>
+      <c r="B145" t="s">
         <v>919</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C145" t="s">
         <v>920</v>
-      </c>
-      <c r="C145" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
+        <v>921</v>
+      </c>
+      <c r="B146" t="s">
+        <v>923</v>
+      </c>
+      <c r="C146" t="s">
         <v>922</v>
-      </c>
-      <c r="B146" t="s">
-        <v>924</v>
-      </c>
-      <c r="C146" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
+        <v>924</v>
+      </c>
+      <c r="B147" t="s">
         <v>925</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C147" t="s">
         <v>926</v>
-      </c>
-      <c r="C147" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
+        <v>927</v>
+      </c>
+      <c r="C148" t="s">
         <v>928</v>
-      </c>
-      <c r="C148" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
+        <v>929</v>
+      </c>
+      <c r="B149" t="s">
         <v>930</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C149" t="s">
         <v>931</v>
-      </c>
-      <c r="C149" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
+        <v>932</v>
+      </c>
+      <c r="C150" t="s">
         <v>933</v>
-      </c>
-      <c r="C150" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
+        <v>934</v>
+      </c>
+      <c r="B151" t="s">
         <v>935</v>
       </c>
-      <c r="B151" t="s">
+      <c r="C151" t="s">
         <v>936</v>
-      </c>
-      <c r="C151" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
+        <v>937</v>
+      </c>
+      <c r="B152" t="s">
         <v>938</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" t="s">
         <v>939</v>
-      </c>
-      <c r="C152" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
+        <v>940</v>
+      </c>
+      <c r="B153" t="s">
         <v>941</v>
       </c>
-      <c r="B153" t="s">
+      <c r="C153" t="s">
         <v>942</v>
-      </c>
-      <c r="C153" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>943</v>
+      </c>
+      <c r="B154" t="s">
         <v>944</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C154" t="s">
         <v>945</v>
-      </c>
-      <c r="C154" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>946</v>
+      </c>
+      <c r="B155" t="s">
         <v>947</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C155" t="s">
         <v>948</v>
-      </c>
-      <c r="C155" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
+        <v>949</v>
+      </c>
+      <c r="C156" t="s">
         <v>950</v>
-      </c>
-      <c r="C156" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
+        <v>951</v>
+      </c>
+      <c r="B157" t="s">
         <v>952</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157" t="s">
         <v>953</v>
-      </c>
-      <c r="C157" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
+        <v>954</v>
+      </c>
+      <c r="B158" t="s">
         <v>955</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C158" t="s">
         <v>956</v>
-      </c>
-      <c r="C158" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
+        <v>957</v>
+      </c>
+      <c r="B159" t="s">
         <v>958</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C159" t="s">
         <v>959</v>
-      </c>
-      <c r="C159" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>960</v>
+      </c>
+      <c r="B160" t="s">
         <v>961</v>
       </c>
-      <c r="B160" t="s">
+      <c r="C160" t="s">
         <v>962</v>
-      </c>
-      <c r="C160" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
+        <v>963</v>
+      </c>
+      <c r="B161" t="s">
         <v>964</v>
       </c>
-      <c r="B161" t="s">
+      <c r="C161" t="s">
         <v>965</v>
-      </c>
-      <c r="C161" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
+        <v>966</v>
+      </c>
+      <c r="B162" t="s">
         <v>967</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C162" t="s">
         <v>968</v>
-      </c>
-      <c r="C162" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
+        <v>969</v>
+      </c>
+      <c r="B163" t="s">
         <v>970</v>
       </c>
-      <c r="B163" t="s">
+      <c r="C163" t="s">
         <v>971</v>
-      </c>
-      <c r="C163" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B165" t="s">
+        <v>973</v>
+      </c>
+      <c r="C165" t="s">
         <v>974</v>
-      </c>
-      <c r="C165" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
+        <v>975</v>
+      </c>
+      <c r="B166" t="s">
         <v>976</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C166" t="s">
         <v>977</v>
-      </c>
-      <c r="C166" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
+        <v>978</v>
+      </c>
+      <c r="B167" t="s">
         <v>979</v>
       </c>
-      <c r="B167" t="s">
+      <c r="C167" t="s">
         <v>980</v>
-      </c>
-      <c r="C167" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
+        <v>982</v>
+      </c>
+      <c r="B168" t="s">
         <v>983</v>
       </c>
-      <c r="B168" t="s">
+      <c r="C168" t="s">
         <v>984</v>
-      </c>
-      <c r="C168" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
+        <v>985</v>
+      </c>
+      <c r="B169" t="s">
         <v>986</v>
       </c>
-      <c r="B169" t="s">
+      <c r="C169" t="s">
         <v>987</v>
-      </c>
-      <c r="C169" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
+        <v>988</v>
+      </c>
+      <c r="B170" t="s">
         <v>989</v>
       </c>
-      <c r="B170" t="s">
+      <c r="C170" t="s">
         <v>990</v>
-      </c>
-      <c r="C170" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
+        <v>991</v>
+      </c>
+      <c r="B171" t="s">
         <v>992</v>
       </c>
-      <c r="B171" t="s">
+      <c r="C171" t="s">
         <v>993</v>
-      </c>
-      <c r="C171" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
+        <v>994</v>
+      </c>
+      <c r="B172" t="s">
         <v>995</v>
       </c>
-      <c r="B172" t="s">
+      <c r="C172" t="s">
         <v>996</v>
-      </c>
-      <c r="C172" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
+        <v>997</v>
+      </c>
+      <c r="B173" t="s">
         <v>998</v>
       </c>
-      <c r="B173" t="s">
+      <c r="C173" t="s">
         <v>999</v>
-      </c>
-      <c r="C173" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B174" t="s">
         <v>1001</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" t="s">
         <v>1002</v>
-      </c>
-      <c r="C174" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B175" t="s">
         <v>1004</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C175" t="s">
         <v>1005</v>
-      </c>
-      <c r="C175" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B176" t="s">
         <v>1007</v>
       </c>
-      <c r="B176" t="s">
+      <c r="C176" t="s">
         <v>1008</v>
-      </c>
-      <c r="C176" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C177" t="s">
         <v>1010</v>
-      </c>
-      <c r="C177" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B178" t="s">
         <v>1012</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C178" t="s">
         <v>1013</v>
-      </c>
-      <c r="C178" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B179" t="s">
         <v>1015</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C179" t="s">
         <v>1016</v>
-      </c>
-      <c r="C179" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B180" t="s">
         <v>1018</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
         <v>1019</v>
-      </c>
-      <c r="C180" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B181" t="s">
         <v>1021</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
         <v>1022</v>
-      </c>
-      <c r="C181" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C183" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C184" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B185" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C185" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B186" t="s">
         <v>1044</v>
       </c>
-      <c r="B186" t="s">
+      <c r="C186" t="s">
         <v>1045</v>
-      </c>
-      <c r="C186" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B187" t="s">
         <v>1049</v>
       </c>
-      <c r="B187" t="s">
+      <c r="C187" t="s">
         <v>1050</v>
-      </c>
-      <c r="C187" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B188" t="s">
         <v>1052</v>
       </c>
-      <c r="B188" t="s">
+      <c r="C188" t="s">
         <v>1053</v>
-      </c>
-      <c r="C188" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B189" t="s">
         <v>1055</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C189" t="s">
         <v>1056</v>
-      </c>
-      <c r="C189" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B190" t="s">
         <v>1032</v>
       </c>
-      <c r="B190" t="s">
+      <c r="C190" t="s">
         <v>1033</v>
-      </c>
-      <c r="C190" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B191" t="s">
         <v>1035</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C191" t="s">
         <v>1036</v>
-      </c>
-      <c r="C191" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B192" t="s">
         <v>1038</v>
       </c>
-      <c r="B192" t="s">
+      <c r="C192" t="s">
         <v>1039</v>
-      </c>
-      <c r="C192" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B193" t="s">
         <v>1041</v>
       </c>
-      <c r="B193" t="s">
+      <c r="C193" t="s">
         <v>1042</v>
-      </c>
-      <c r="C193" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B194" t="s">
         <v>1058</v>
       </c>
-      <c r="B194" t="s">
+      <c r="C194" t="s">
         <v>1059</v>
-      </c>
-      <c r="C194" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B195" t="s">
         <v>1061</v>
       </c>
-      <c r="B195" t="s">
+      <c r="C195" t="s">
         <v>1062</v>
-      </c>
-      <c r="C195" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B196" t="s">
         <v>1064</v>
       </c>
-      <c r="B196" t="s">
+      <c r="C196" t="s">
         <v>1065</v>
-      </c>
-      <c r="C196" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C197" t="s">
         <v>1067</v>
-      </c>
-      <c r="C197" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B198" t="s">
         <v>1069</v>
       </c>
-      <c r="B198" t="s">
+      <c r="C198" t="s">
         <v>1070</v>
-      </c>
-      <c r="C198" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B199" t="s">
         <v>1072</v>
       </c>
-      <c r="B199" t="s">
+      <c r="C199" t="s">
         <v>1073</v>
-      </c>
-      <c r="C199" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B200" t="s">
         <v>1075</v>
       </c>
-      <c r="B200" t="s">
+      <c r="C200" t="s">
         <v>1076</v>
-      </c>
-      <c r="C200" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B201" t="s">
         <v>1078</v>
       </c>
-      <c r="B201" t="s">
+      <c r="C201" t="s">
         <v>1079</v>
-      </c>
-      <c r="C201" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C202" t="s">
         <v>623</v>
@@ -6032,35 +6231,35 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B203" t="s">
         <v>1081</v>
       </c>
-      <c r="B203" t="s">
+      <c r="C203" t="s">
         <v>1082</v>
-      </c>
-      <c r="C203" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B204" t="s">
         <v>1084</v>
       </c>
-      <c r="B204" t="s">
+      <c r="C204" t="s">
         <v>1085</v>
-      </c>
-      <c r="C204" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B205" t="s">
         <v>1087</v>
       </c>
-      <c r="B205" t="s">
+      <c r="C205" t="s">
         <v>1088</v>
-      </c>
-      <c r="C205" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
@@ -7598,463 +7797,650 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>712</v>
+        <v>1090</v>
       </c>
       <c r="B356" t="s">
-        <v>728</v>
+        <v>1091</v>
       </c>
       <c r="C356" t="s">
-        <v>713</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>714</v>
+        <v>1115</v>
       </c>
       <c r="B357" t="s">
-        <v>729</v>
+        <v>1114</v>
       </c>
       <c r="C357" t="s">
-        <v>715</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>716</v>
-      </c>
-      <c r="B358" t="s">
-        <v>717</v>
+        <v>1094</v>
       </c>
       <c r="C358" t="s">
-        <v>718</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>719</v>
+        <v>1096</v>
       </c>
       <c r="B359" t="s">
-        <v>720</v>
+        <v>1097</v>
       </c>
       <c r="C359" t="s">
-        <v>721</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>722</v>
+        <v>1099</v>
       </c>
       <c r="B360" t="s">
-        <v>723</v>
+        <v>1100</v>
       </c>
       <c r="C360" t="s">
-        <v>724</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>725</v>
+        <v>1102</v>
       </c>
       <c r="B361" t="s">
-        <v>726</v>
-      </c>
-      <c r="C361" t="s">
-        <v>727</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>730</v>
-      </c>
-      <c r="B362" t="s">
-        <v>770</v>
+        <v>1104</v>
       </c>
       <c r="C362" t="s">
-        <v>731</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>732</v>
+        <v>1106</v>
       </c>
       <c r="B363" t="s">
-        <v>733</v>
-      </c>
-      <c r="C363" t="s">
-        <v>734</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>735</v>
-      </c>
-      <c r="B364" t="s">
-        <v>736</v>
+        <v>1108</v>
       </c>
       <c r="C364" t="s">
-        <v>737</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>738</v>
+        <v>1110</v>
       </c>
       <c r="B365" t="s">
-        <v>739</v>
-      </c>
-      <c r="C365" t="s">
-        <v>740</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>741</v>
-      </c>
-      <c r="B366" t="s">
-        <v>771</v>
+        <v>1112</v>
       </c>
       <c r="C366" t="s">
-        <v>742</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>743</v>
-      </c>
-      <c r="B367" t="s">
-        <v>744</v>
+        <v>1116</v>
       </c>
       <c r="C367" t="s">
-        <v>745</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>746</v>
-      </c>
-      <c r="B368" t="s">
-        <v>772</v>
+        <v>1118</v>
       </c>
       <c r="C368" t="s">
-        <v>747</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>748</v>
-      </c>
-      <c r="B369" t="s">
-        <v>773</v>
+        <v>1120</v>
       </c>
       <c r="C369" t="s">
-        <v>749</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>750</v>
+        <v>1122</v>
       </c>
       <c r="C370" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A371" t="s">
-        <v>752</v>
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="A371" s="3" t="s">
+        <v>1127</v>
       </c>
       <c r="B371" t="s">
-        <v>753</v>
+        <v>1125</v>
       </c>
       <c r="C371" t="s">
-        <v>754</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>755</v>
+        <v>1128</v>
       </c>
       <c r="B372" t="s">
-        <v>756</v>
+        <v>1129</v>
       </c>
       <c r="C372" t="s">
-        <v>757</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>758</v>
+        <v>1131</v>
       </c>
       <c r="B373" t="s">
-        <v>759</v>
+        <v>1132</v>
       </c>
       <c r="C373" t="s">
-        <v>760</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>761</v>
+        <v>1134</v>
       </c>
       <c r="B374" t="s">
-        <v>762</v>
+        <v>1135</v>
       </c>
       <c r="C374" t="s">
-        <v>763</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>764</v>
+        <v>1137</v>
       </c>
       <c r="B375" t="s">
-        <v>765</v>
+        <v>1138</v>
       </c>
       <c r="C375" t="s">
-        <v>766</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>767</v>
+        <v>712</v>
       </c>
       <c r="B376" t="s">
-        <v>768</v>
+        <v>727</v>
       </c>
       <c r="C376" t="s">
-        <v>769</v>
+        <v>713</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>220</v>
+        <v>1124</v>
       </c>
       <c r="B377" t="s">
-        <v>221</v>
+        <v>728</v>
       </c>
       <c r="C377" t="s">
-        <v>222</v>
+        <v>714</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>274</v>
+        <v>715</v>
       </c>
       <c r="B378" t="s">
-        <v>275</v>
+        <v>716</v>
       </c>
       <c r="C378" t="s">
-        <v>223</v>
+        <v>717</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>224</v>
+        <v>718</v>
       </c>
       <c r="B379" t="s">
-        <v>276</v>
+        <v>719</v>
       </c>
       <c r="C379" t="s">
-        <v>225</v>
+        <v>720</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>277</v>
+        <v>721</v>
       </c>
       <c r="B380" t="s">
-        <v>278</v>
+        <v>722</v>
       </c>
       <c r="C380" t="s">
-        <v>226</v>
+        <v>723</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>227</v>
+        <v>724</v>
       </c>
       <c r="B381" t="s">
-        <v>279</v>
+        <v>725</v>
       </c>
       <c r="C381" t="s">
-        <v>280</v>
+        <v>726</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>228</v>
+        <v>729</v>
       </c>
       <c r="B382" t="s">
-        <v>281</v>
+        <v>769</v>
       </c>
       <c r="C382" t="s">
-        <v>229</v>
+        <v>730</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>230</v>
+        <v>731</v>
       </c>
       <c r="B383" t="s">
-        <v>231</v>
+        <v>732</v>
       </c>
       <c r="C383" t="s">
-        <v>232</v>
+        <v>733</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>233</v>
+        <v>734</v>
       </c>
       <c r="B384" t="s">
-        <v>234</v>
+        <v>735</v>
       </c>
       <c r="C384" t="s">
-        <v>235</v>
+        <v>736</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>236</v>
+        <v>737</v>
       </c>
       <c r="B385" t="s">
-        <v>237</v>
+        <v>738</v>
+      </c>
+      <c r="C385" t="s">
+        <v>739</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>238</v>
+        <v>740</v>
+      </c>
+      <c r="B386" t="s">
+        <v>770</v>
+      </c>
+      <c r="C386" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>239</v>
+        <v>742</v>
       </c>
       <c r="B387" t="s">
-        <v>240</v>
+        <v>743</v>
       </c>
       <c r="C387" t="s">
-        <v>241</v>
+        <v>744</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>242</v>
+        <v>745</v>
       </c>
       <c r="B388" t="s">
-        <v>243</v>
+        <v>771</v>
       </c>
       <c r="C388" t="s">
-        <v>244</v>
+        <v>746</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>245</v>
+        <v>747</v>
       </c>
       <c r="B389" t="s">
-        <v>246</v>
+        <v>772</v>
       </c>
       <c r="C389" t="s">
-        <v>247</v>
+        <v>748</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>248</v>
+        <v>749</v>
+      </c>
+      <c r="C390" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>249</v>
+        <v>751</v>
       </c>
       <c r="B391" t="s">
-        <v>250</v>
+        <v>752</v>
       </c>
       <c r="C391" t="s">
-        <v>251</v>
+        <v>753</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>252</v>
+        <v>754</v>
       </c>
       <c r="B392" t="s">
-        <v>253</v>
+        <v>755</v>
       </c>
       <c r="C392" t="s">
-        <v>254</v>
+        <v>756</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>255</v>
+        <v>757</v>
       </c>
       <c r="B393" t="s">
-        <v>256</v>
+        <v>758</v>
       </c>
       <c r="C393" t="s">
-        <v>257</v>
+        <v>759</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>258</v>
+        <v>760</v>
       </c>
       <c r="B394" t="s">
-        <v>259</v>
+        <v>761</v>
       </c>
       <c r="C394" t="s">
-        <v>260</v>
+        <v>762</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>261</v>
+        <v>763</v>
       </c>
       <c r="B395" t="s">
-        <v>262</v>
+        <v>764</v>
+      </c>
+      <c r="C395" t="s">
+        <v>765</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>263</v>
+        <v>766</v>
+      </c>
+      <c r="B396" t="s">
+        <v>767</v>
+      </c>
+      <c r="C396" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="B397" t="s">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="C397" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>267</v>
+        <v>274</v>
+      </c>
+      <c r="B398" t="s">
+        <v>275</v>
+      </c>
+      <c r="C398" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="B399" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C399" t="s">
-        <v>270</v>
+        <v>225</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
+        <v>277</v>
+      </c>
+      <c r="B400" t="s">
+        <v>278</v>
+      </c>
+      <c r="C400" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>227</v>
+      </c>
+      <c r="B401" t="s">
+        <v>279</v>
+      </c>
+      <c r="C401" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>228</v>
+      </c>
+      <c r="B402" t="s">
+        <v>281</v>
+      </c>
+      <c r="C402" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>230</v>
+      </c>
+      <c r="B403" t="s">
+        <v>231</v>
+      </c>
+      <c r="C403" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>233</v>
+      </c>
+      <c r="B404" t="s">
+        <v>234</v>
+      </c>
+      <c r="C404" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>236</v>
+      </c>
+      <c r="B405" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>239</v>
+      </c>
+      <c r="B407" t="s">
+        <v>240</v>
+      </c>
+      <c r="C407" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>242</v>
+      </c>
+      <c r="B408" t="s">
+        <v>243</v>
+      </c>
+      <c r="C408" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>245</v>
+      </c>
+      <c r="B409" t="s">
+        <v>246</v>
+      </c>
+      <c r="C409" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
+        <v>249</v>
+      </c>
+      <c r="B411" t="s">
+        <v>250</v>
+      </c>
+      <c r="C411" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>252</v>
+      </c>
+      <c r="B412" t="s">
+        <v>253</v>
+      </c>
+      <c r="C412" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>255</v>
+      </c>
+      <c r="B413" t="s">
+        <v>256</v>
+      </c>
+      <c r="C413" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>258</v>
+      </c>
+      <c r="B414" t="s">
+        <v>259</v>
+      </c>
+      <c r="C414" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>261</v>
+      </c>
+      <c r="B415" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>264</v>
+      </c>
+      <c r="B417" t="s">
+        <v>265</v>
+      </c>
+      <c r="C417" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>268</v>
+      </c>
+      <c r="B419" t="s">
+        <v>269</v>
+      </c>
+      <c r="C419" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
         <v>271</v>
       </c>
-      <c r="B400" t="s">
+      <c r="B420" t="s">
         <v>272</v>
       </c>
-      <c r="C400" t="s">
+      <c r="C420" t="s">
         <v>273</v>
       </c>
     </row>

--- a/00-日語文型整理.xlsx
+++ b/00-日語文型整理.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://guandamachine-my.sharepoint.com/personal/ec03_gd_guandamachine_com_tw/Documents/Fly/日語/日語練習網站/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="229" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F80A05B-6FA1-4A2D-91AB-FF35B16B82C9}"/>
+  <xr:revisionPtr revIDLastSave="259" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C08091AD-1969-4326-9701-9CAE70725F0A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0F3A2E6B-B5D2-4B57-9A1E-3E6BF54CF7A6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0F3A2E6B-B5D2-4B57-9A1E-3E6BF54CF7A6}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1191">
   <si>
     <t>わたしわ マイク・ミラーです</t>
   </si>
@@ -3740,6 +3740,168 @@
   </si>
   <si>
     <t>打開門一看,發現有隻貓</t>
+  </si>
+  <si>
+    <t>*第24課文型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さとうさんは わたしに クリスマスカードを くれました</t>
+  </si>
+  <si>
+    <t>佐藤さんは 私に クリスマスカードを くれました</t>
+  </si>
+  <si>
+    <t>佐藤女士送了我一張聖誕卡</t>
+  </si>
+  <si>
+    <t>わたしは きむらさんに ほんを かして あげました</t>
+  </si>
+  <si>
+    <t>私は 木村さんに 本を 貸して あげました</t>
+  </si>
+  <si>
+    <t>我借給木村先生一本書</t>
+  </si>
+  <si>
+    <t>わたしは やまださんに びょう いんの でんわばんごう を おしえて もらいました</t>
+  </si>
+  <si>
+    <t>わたしは 山田さんに 病院の 電話番号を 教えて もらいました</t>
+  </si>
+  <si>
+    <t>山田先生給了我醫院的電話號碼</t>
+  </si>
+  <si>
+    <t>ははは わたしに セーターを おくって くれました</t>
+  </si>
+  <si>
+    <t>母は 私に セーターを 送って くれました</t>
+  </si>
+  <si>
+    <t>我媽媽寄給我一件毛衣</t>
+  </si>
+  <si>
+    <t>あげる あげます あげました</t>
+  </si>
+  <si>
+    <t>給予 1→2/1→3/2→3/3→3</t>
+  </si>
+  <si>
+    <t>くれる くれます くれました</t>
+  </si>
+  <si>
+    <t>給予 2→1/3→1/3→2</t>
+  </si>
+  <si>
+    <t>もらう もらいます むらいました</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>得到/獲得 1←3/2←3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>句型: 給予者 は 獲得者 に 物品 を あげる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>句型: 給予者 は 獲得者 に 物品 を くれる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>句型: 獲得者 は 給予者 に 物品 を もらう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>たろうくんは おばあちゃんが すきですか</t>
+  </si>
+  <si>
+    <t>太郎君は おばあちゃんが 好きですか</t>
+  </si>
+  <si>
+    <t>太郎，你喜歡你奶奶嗎？</t>
+  </si>
+  <si>
+    <t>…はい、すきです。 おばあちゃんは いつも おかしを くれます</t>
+  </si>
+  <si>
+    <t>……是的，我喜歡。奶奶總是給我吃糖。</t>
+  </si>
+  <si>
+    <t>おいしい ワインですね</t>
+  </si>
+  <si>
+    <t>這酒真好喝。</t>
+  </si>
+  <si>
+    <t>…ええ、さとうさんが くれました。 フランスの ワインです。</t>
+  </si>
+  <si>
+    <t>……是的，佐藤先生送我的。是法國葡萄酒。</t>
+  </si>
+  <si>
+    <t>太郎君は 母の 日に お母さんに 何を して あげますか</t>
+  </si>
+  <si>
+    <t>母親節那天，太郎會為媽媽做些什麼呢？</t>
+  </si>
+  <si>
+    <t>…ピアノを ひいて あげます</t>
+  </si>
+  <si>
+    <t>…ピアノを 弾いて あげます</t>
+  </si>
+  <si>
+    <t>……他會為媽媽彈鋼琴</t>
+  </si>
+  <si>
+    <t>…はい、好きです。 おばあちゃんは いつも お菓子を くれます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>…ええ、佐藤さんが くれました。 フランスの ワインです</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>たろうくんは ははの ひに おかあさんに なにを して あげますか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ミラーさん、きのうの パーティーの りょうりは ぜんぶ じぶんで つくりましたか</t>
+  </si>
+  <si>
+    <t>ミラーさん、きのうの パーティーの 料理は 全部 自分で 作りましたか</t>
+  </si>
+  <si>
+    <t>米勒先生，昨天聚會的所有食物都是您自己做的嗎？</t>
+  </si>
+  <si>
+    <t>…いいえ、ワンさんに てつだって もらいました</t>
+  </si>
+  <si>
+    <t>…いいえ、ワンさんに 手伝って もらいました</t>
+  </si>
+  <si>
+    <t>……不，王先生幫我做的</t>
+  </si>
+  <si>
+    <t>でんしゃ で いきましたか</t>
+  </si>
+  <si>
+    <t>電車で 行きましたか</t>
+  </si>
+  <si>
+    <t>你是坐火車去的嗎？</t>
+  </si>
+  <si>
+    <t>…いいえ。 やまださんが くるまで おくって くれました</t>
+  </si>
+  <si>
+    <t>…いいえ。 山田さんが 車で 送って くれました</t>
+  </si>
+  <si>
+    <t>……不是。山田先生開車送我去的</t>
   </si>
 </sst>
 </file>
@@ -3840,9 +4002,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3880,7 +4042,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3986,7 +4148,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4128,7 +4290,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4136,7 +4298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B91EE72-412B-4BEC-A7E9-A97446845EE1}">
-  <dimension ref="A1:C420"/>
+  <dimension ref="A1:C438"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="57.21875" customWidth="1"/>
@@ -8212,235 +8374,424 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>220</v>
-      </c>
-      <c r="B397" t="s">
-        <v>221</v>
-      </c>
-      <c r="C397" t="s">
-        <v>222</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>274</v>
+        <v>1153</v>
       </c>
       <c r="B398" t="s">
-        <v>275</v>
+        <v>1154</v>
       </c>
       <c r="C398" t="s">
-        <v>223</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>224</v>
+        <v>1155</v>
       </c>
       <c r="B399" t="s">
-        <v>276</v>
+        <v>1156</v>
       </c>
       <c r="C399" t="s">
-        <v>225</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>277</v>
+        <v>1157</v>
       </c>
       <c r="B400" t="s">
-        <v>278</v>
+        <v>1158</v>
       </c>
       <c r="C400" t="s">
-        <v>226</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>227</v>
+        <v>1141</v>
       </c>
       <c r="B401" t="s">
-        <v>279</v>
+        <v>1142</v>
       </c>
       <c r="C401" t="s">
-        <v>280</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>228</v>
+        <v>1144</v>
       </c>
       <c r="B402" t="s">
-        <v>281</v>
+        <v>1145</v>
       </c>
       <c r="C402" t="s">
-        <v>229</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>230</v>
+        <v>1147</v>
       </c>
       <c r="B403" t="s">
-        <v>231</v>
+        <v>1148</v>
       </c>
       <c r="C403" t="s">
-        <v>232</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>233</v>
+        <v>1150</v>
       </c>
       <c r="B404" t="s">
-        <v>234</v>
+        <v>1151</v>
       </c>
       <c r="C404" t="s">
-        <v>235</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>236</v>
+        <v>1162</v>
       </c>
       <c r="B405" t="s">
-        <v>237</v>
+        <v>1163</v>
+      </c>
+      <c r="C405" t="s">
+        <v>1164</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>238</v>
+        <v>1165</v>
+      </c>
+      <c r="B406" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C406" t="s">
+        <v>1166</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>239</v>
-      </c>
-      <c r="B407" t="s">
-        <v>240</v>
+        <v>1167</v>
       </c>
       <c r="C407" t="s">
-        <v>241</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>242</v>
+        <v>1169</v>
       </c>
       <c r="B408" t="s">
-        <v>243</v>
+        <v>1177</v>
       </c>
       <c r="C408" t="s">
-        <v>244</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>245</v>
+        <v>1178</v>
       </c>
       <c r="B409" t="s">
-        <v>246</v>
+        <v>1171</v>
       </c>
       <c r="C409" t="s">
-        <v>247</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>248</v>
+        <v>1173</v>
+      </c>
+      <c r="B410" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C410" t="s">
+        <v>1175</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>249</v>
+        <v>1179</v>
       </c>
       <c r="B411" t="s">
-        <v>250</v>
+        <v>1180</v>
       </c>
       <c r="C411" t="s">
-        <v>251</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>252</v>
+        <v>1182</v>
       </c>
       <c r="B412" t="s">
-        <v>253</v>
+        <v>1183</v>
       </c>
       <c r="C412" t="s">
-        <v>254</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>255</v>
+        <v>1185</v>
       </c>
       <c r="B413" t="s">
-        <v>256</v>
+        <v>1186</v>
       </c>
       <c r="C413" t="s">
-        <v>257</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>258</v>
+        <v>1188</v>
       </c>
       <c r="B414" t="s">
-        <v>259</v>
+        <v>1189</v>
       </c>
       <c r="C414" t="s">
-        <v>260</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="B415" t="s">
-        <v>262</v>
+        <v>221</v>
+      </c>
+      <c r="C415" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>263</v>
+        <v>274</v>
+      </c>
+      <c r="B416" t="s">
+        <v>275</v>
+      </c>
+      <c r="C416" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="B417" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="C417" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>267</v>
+        <v>277</v>
+      </c>
+      <c r="B418" t="s">
+        <v>278</v>
+      </c>
+      <c r="C418" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>268</v>
+        <v>227</v>
       </c>
       <c r="B419" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C419" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
+        <v>228</v>
+      </c>
+      <c r="B420" t="s">
+        <v>281</v>
+      </c>
+      <c r="C420" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>230</v>
+      </c>
+      <c r="B421" t="s">
+        <v>231</v>
+      </c>
+      <c r="C421" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>233</v>
+      </c>
+      <c r="B422" t="s">
+        <v>234</v>
+      </c>
+      <c r="C422" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>236</v>
+      </c>
+      <c r="B423" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>239</v>
+      </c>
+      <c r="B425" t="s">
+        <v>240</v>
+      </c>
+      <c r="C425" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>242</v>
+      </c>
+      <c r="B426" t="s">
+        <v>243</v>
+      </c>
+      <c r="C426" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>245</v>
+      </c>
+      <c r="B427" t="s">
+        <v>246</v>
+      </c>
+      <c r="C427" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>249</v>
+      </c>
+      <c r="B429" t="s">
+        <v>250</v>
+      </c>
+      <c r="C429" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>252</v>
+      </c>
+      <c r="B430" t="s">
+        <v>253</v>
+      </c>
+      <c r="C430" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>255</v>
+      </c>
+      <c r="B431" t="s">
+        <v>256</v>
+      </c>
+      <c r="C431" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>258</v>
+      </c>
+      <c r="B432" t="s">
+        <v>259</v>
+      </c>
+      <c r="C432" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>261</v>
+      </c>
+      <c r="B433" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>264</v>
+      </c>
+      <c r="B435" t="s">
+        <v>265</v>
+      </c>
+      <c r="C435" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>268</v>
+      </c>
+      <c r="B437" t="s">
+        <v>269</v>
+      </c>
+      <c r="C437" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
         <v>271</v>
       </c>
-      <c r="B420" t="s">
+      <c r="B438" t="s">
         <v>272</v>
       </c>
-      <c r="C420" t="s">
+      <c r="C438" t="s">
         <v>273</v>
       </c>
     </row>

--- a/00-日語文型整理.xlsx
+++ b/00-日語文型整理.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://guandamachine-my.sharepoint.com/personal/ec03_gd_guandamachine_com_tw/Documents/Fly/日語/日語練習網站/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="259" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C08091AD-1969-4326-9701-9CAE70725F0A}"/>
+  <xr:revisionPtr revIDLastSave="328" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1BDFFA5-8995-4720-AC84-2B7DC64E8AD3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0F3A2E6B-B5D2-4B57-9A1E-3E6BF54CF7A6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{0F3A2E6B-B5D2-4B57-9A1E-3E6BF54CF7A6}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" iterateDelta="1E-4"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="1377">
   <si>
     <t>わたしわ マイク・ミラーです</t>
   </si>
@@ -1093,24 +1093,15 @@
     <t>いきます かえります きました</t>
   </si>
   <si>
-    <t>行きます 帰ります 来ました</t>
-  </si>
-  <si>
     <t>去某地 回(家) 來(這裡)</t>
   </si>
   <si>
     <t>わたし は きょうと へ いきます</t>
   </si>
   <si>
-    <t>私 は 京都 へ 行きます</t>
-  </si>
-  <si>
     <t>我去京都</t>
   </si>
   <si>
-    <t>A は 交通工具 で 地點(場所) へ 帰(かえ)ります(行(い)きます)（来(き)ました）</t>
-  </si>
-  <si>
     <t>わたし は タクシー で いえ へ かえります。</t>
   </si>
   <si>
@@ -1127,10 +1118,6 @@
   </si>
   <si>
     <t>我和家人一起來到日本(過去式)</t>
-  </si>
-  <si>
-    <t>A は 地點(場所) へ行(い)きます(帰(かえ)ります)（来(き)ました）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>去、來、回去某地點用 へ</t>
@@ -3902,6 +3889,592 @@
   </si>
   <si>
     <t>……不是。山田先生開車送我去的</t>
+  </si>
+  <si>
+    <t>A は 地點(場所) へいきます かえります きます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A は 地點(場所) へ 行きます 帰ります 来ます）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行きます 帰ります 来ます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>私 は 京都 へ 行きます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A は 交通工具 で 地點(場所) へ 帰ります 行きます 来ます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A は 交通工具 で 地點(場所) へ かえります いきます きます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*第11課文型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*第12課文型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かいぎしつ に テーブルが ななつ あります</t>
+  </si>
+  <si>
+    <t>会議室に テーブルが 7つ あります</t>
+  </si>
+  <si>
+    <t>會議室裡有7張桌子</t>
+  </si>
+  <si>
+    <t>わたしは にほんに 1ねん います</t>
+  </si>
+  <si>
+    <t>私は 日本に 1年 います</t>
+  </si>
+  <si>
+    <t>我在日本已經一年了</t>
+  </si>
+  <si>
+    <t>りんごを いくつ かいましたか</t>
+  </si>
+  <si>
+    <t>りんごを いくつ 買いましたか</t>
+  </si>
+  <si>
+    <t>你買了幾個蘋果</t>
+  </si>
+  <si>
+    <t>…よっつ かいました</t>
+  </si>
+  <si>
+    <t>…4つ 買いました</t>
+  </si>
+  <si>
+    <t>……我買了四個。</t>
+  </si>
+  <si>
+    <t>80えんの きってを 5まいと はがきを 2まい ください</t>
+  </si>
+  <si>
+    <t>80円の 切手を 5枚と はがきを 2枚 ください</t>
+  </si>
+  <si>
+    <t>請給我五張80日圓的郵票和兩張明信片。</t>
+  </si>
+  <si>
+    <t>…はい。ぜんぶで 500えんです</t>
+  </si>
+  <si>
+    <t>……好的。共500日元。</t>
+  </si>
+  <si>
+    <t>…はい。全部で 500円です</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふじだいがくに がいこくじんの せんせいが いますか</t>
+  </si>
+  <si>
+    <t>富士大学に 外国人の 先生が いますか</t>
+  </si>
+  <si>
+    <t>富士大學有外籍教授嗎？</t>
+  </si>
+  <si>
+    <t>…はい、3にん います。 みんな アメリカじんです</t>
+  </si>
+  <si>
+    <t>…はい、3人 います。 みんな アメリカ人です</t>
+  </si>
+  <si>
+    <t>……有，三位。他們都是美國人。</t>
+  </si>
+  <si>
+    <t>かぞく は なんにんですか</t>
+  </si>
+  <si>
+    <t>家族 は 何人ですか</t>
+  </si>
+  <si>
+    <t>你家有幾口人？</t>
+  </si>
+  <si>
+    <t>…5にんです。 りょうしんと あねと あにが います</t>
+  </si>
+  <si>
+    <t>…5人です。 両親と 姉と 兄が います</t>
+  </si>
+  <si>
+    <t>……五口之家。我有父母、一個姊姊和一個哥哥</t>
+  </si>
+  <si>
+    <t>しゅうかんに なんかい テニスを しますか。</t>
+  </si>
+  <si>
+    <t>1週間に 何回 テニスを しますか。</t>
+  </si>
+  <si>
+    <t>你一週打幾次網球？</t>
+  </si>
+  <si>
+    <t>…2かいぐらい します。</t>
+  </si>
+  <si>
+    <t>…2回ぐらい します。</t>
+  </si>
+  <si>
+    <t>……大概兩次。</t>
+  </si>
+  <si>
+    <t>たなかさんは どのくらい スペインごを べん きょうしましたか</t>
+  </si>
+  <si>
+    <t>田中さんは どのくらい スペイン語を 勉強しましたか</t>
+  </si>
+  <si>
+    <t>田中先生，您學西班牙語多久了？</t>
+  </si>
+  <si>
+    <t>…3かげつ べんきょうしました。</t>
+  </si>
+  <si>
+    <t>…3か月 勉強しました。</t>
+  </si>
+  <si>
+    <t>……三個月。</t>
+  </si>
+  <si>
+    <t>えっ、3かげつだけですか。 じょうずですね。</t>
+  </si>
+  <si>
+    <t>えっ、3か月だけですか。 上手ですね。</t>
+  </si>
+  <si>
+    <t>什麼？才三個月？真厲害！</t>
+  </si>
+  <si>
+    <t>おおさかから とうきょうまで しんかんせんで どのくらい かかりますか</t>
+  </si>
+  <si>
+    <t>大阪から 東京まで 新幹線で どのくらい かかりますか</t>
+  </si>
+  <si>
+    <t>從大阪坐新幹線到東京要花多久時間？</t>
+  </si>
+  <si>
+    <t>…2じかんはん かかります。</t>
+  </si>
+  <si>
+    <t>…2時間半 かかります。</t>
+  </si>
+  <si>
+    <t>……兩個半小時。</t>
+  </si>
+  <si>
+    <t>みかんを いつつ かいました</t>
+  </si>
+  <si>
+    <t>みかんを 5つ 買いました</t>
+  </si>
+  <si>
+    <t>我買了五個橘子</t>
+  </si>
+  <si>
+    <t>みかんを やっつ かいました</t>
+  </si>
+  <si>
+    <t>みかんを 8つ 買いました</t>
+  </si>
+  <si>
+    <t>我買了八個橘子</t>
+  </si>
+  <si>
+    <t>みかんを とお かいました</t>
+  </si>
+  <si>
+    <t>みかんを 10つ 買いました</t>
+  </si>
+  <si>
+    <t>我買了十個橘子</t>
+  </si>
+  <si>
+    <t>みかんを いくつ かいましたか</t>
+  </si>
+  <si>
+    <t>みかんを いくつ 買いましたか</t>
+  </si>
+  <si>
+    <t>你買了幾個橘子？</t>
+  </si>
+  <si>
+    <t>90えんの きってを 1まい ください</t>
+  </si>
+  <si>
+    <t>90円の 切手を 1まい ください</t>
+  </si>
+  <si>
+    <t>請給我一張90日元郵票。</t>
+  </si>
+  <si>
+    <t>90えんの きってを 2まい ください</t>
+  </si>
+  <si>
+    <t>90円の 切手を 2まい ください</t>
+  </si>
+  <si>
+    <t>請給我兩張90日元郵票</t>
+  </si>
+  <si>
+    <t>90えんの きってを 5まい ください</t>
+  </si>
+  <si>
+    <t>90円の 切手を 5まい ください</t>
+  </si>
+  <si>
+    <t>請給我五張90日元郵票</t>
+  </si>
+  <si>
+    <t>この かいしゃに かいこくじんが ひとり います</t>
+  </si>
+  <si>
+    <t>この 会社に 外国人が 1り います</t>
+  </si>
+  <si>
+    <t>這家公司有一名外國人。</t>
+  </si>
+  <si>
+    <t>この かいしゃに かいこくじんが ふたり います</t>
+  </si>
+  <si>
+    <t>この 会社に 外国人が 2り います</t>
+  </si>
+  <si>
+    <t>這家公司有兩名外國人。</t>
+  </si>
+  <si>
+    <t>この かいしゃに かいこくじんが 3にん います</t>
+  </si>
+  <si>
+    <t>この 会社に 外国人が 3にん います</t>
+  </si>
+  <si>
+    <t>這家公司有四名外國人。</t>
+  </si>
+  <si>
+    <t>この かいしゃに かいこくじんが 4にん います</t>
+  </si>
+  <si>
+    <t>この 会社に 外国人が 4にん います</t>
+  </si>
+  <si>
+    <t>この かいしゃに かいこくじんが なんにん いますか</t>
+  </si>
+  <si>
+    <t>この 会社に 外国人が なんにん いますか</t>
+  </si>
+  <si>
+    <t>這家公司共有多少名外國人？</t>
+  </si>
+  <si>
+    <t>1しゅうかん に 1かい えいがを みます</t>
+  </si>
+  <si>
+    <t>1週間 に 1かい 映画を 見ます</t>
+  </si>
+  <si>
+    <t>我每週看一次電影</t>
+  </si>
+  <si>
+    <t>1かげつ に 2かい えいがを みます</t>
+  </si>
+  <si>
+    <t>1か月 に 2かい 映画を 見ます</t>
+  </si>
+  <si>
+    <t>我每月看兩次電影</t>
+  </si>
+  <si>
+    <t>1ねん に 5かいぐらい えいがを みます</t>
+  </si>
+  <si>
+    <t>1年 に 5かいぐらい 映画を 見ます</t>
+  </si>
+  <si>
+    <t>我每年大約看五次電影</t>
+  </si>
+  <si>
+    <t>1ねん に なんかい えいがを みますか</t>
+  </si>
+  <si>
+    <t>1年 に なんかい 映画を 見ますか</t>
+  </si>
+  <si>
+    <t>你一年看幾次電影？</t>
+  </si>
+  <si>
+    <t>わたしは くにで 5しゅうかん にほんごを べんきょうしました</t>
+  </si>
+  <si>
+    <t>私は 国で 5しゅうかん 日本語を 勉強しました</t>
+  </si>
+  <si>
+    <t>我在本國學習了5個星期日語。</t>
+  </si>
+  <si>
+    <t>わたしは くにで 6かげつ にほんごを べんきょうしました</t>
+  </si>
+  <si>
+    <t>私は 国で 6かげつ 日本語を 勉強しました</t>
+  </si>
+  <si>
+    <t>我在本國學習了6個月日文。</t>
+  </si>
+  <si>
+    <t>わたしは くにで 1ねんぐらい にほんごを べんきょうしました</t>
+  </si>
+  <si>
+    <t>私は 国で 1ねんぐらい 日本語を 勉強しました</t>
+  </si>
+  <si>
+    <t>我在本國學習了大約1年日語。</t>
+  </si>
+  <si>
+    <t>あなたは くにで 1ねんぐらい にほんごを べんきょうしましたか</t>
+  </si>
+  <si>
+    <t>あなたは 国で どのくらい 日本語を 勉強しましたか</t>
+  </si>
+  <si>
+    <t>在本國學習日語多久了？</t>
+  </si>
+  <si>
+    <t>わたしの くにから にほんまで ひこうきで 4じかん かかります</t>
+  </si>
+  <si>
+    <t>私の 国から 日本まで 飛行機で 4時間 かかります</t>
+  </si>
+  <si>
+    <t>從我的國家飛往日本需要4個小時。</t>
+  </si>
+  <si>
+    <t>わたしの くにから にほんまで ひこうきで 5じかんはん かかります</t>
+  </si>
+  <si>
+    <t>私の 国から 日本まで 飛行機で 5時間はん かかります</t>
+  </si>
+  <si>
+    <t>從我的國家飛往日本需要5個半小時。</t>
+  </si>
+  <si>
+    <t>わたしの くにから にほんまで ひこうきで 12じかん かかります</t>
+  </si>
+  <si>
+    <t>從我的國家飛往日本需要12小時。</t>
+  </si>
+  <si>
+    <t>あなたの くにから にほんまで ひこうきで どのくらい かかりますか</t>
+  </si>
+  <si>
+    <t>あなたの 国から 日本まで 飛行機で どのくらい かかりますか</t>
+  </si>
+  <si>
+    <t>從你的國家飛往日本需要多長時間？</t>
+  </si>
+  <si>
+    <t>きのうは あめでした</t>
+  </si>
+  <si>
+    <t>きのうは 雨でした</t>
+  </si>
+  <si>
+    <t>昨天下雨了</t>
+  </si>
+  <si>
+    <t>きのうは さむかったです</t>
+  </si>
+  <si>
+    <t>きのうは 寒かったです</t>
+  </si>
+  <si>
+    <t>昨天很冷</t>
+  </si>
+  <si>
+    <t>北海道比九州大</t>
+  </si>
+  <si>
+    <t>わたしは 1ねんで なつが いちばん すきです</t>
+  </si>
+  <si>
+    <t>夏天是我最喜歡的季節</t>
+  </si>
+  <si>
+    <t>ほっかいどうは きゅうしゅうより おおきいです</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北海道は 九州より 大きいです</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A は B より [形容詞] です</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>私の 国から 日本まで 飛行機で 12時間 かかります</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>私は 1年で 夏が いちばん 好きです</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>這句話的文法結構是：</t>
+  </si>
+  <si>
+    <t>A は Bより [形容詞] です,用來表示 A 在某個性質或程度上勝過 B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>きょうとは しずかでしたか 京都は 静かでしたか</t>
+  </si>
+  <si>
+    <t>京都安靜嗎？</t>
+  </si>
+  <si>
+    <t>…いいえ、しずかじゃ ありませんでした</t>
+  </si>
+  <si>
+    <t>…いいえ、静かじゃ ありませんでした</t>
+  </si>
+  <si>
+    <t>……不，一點也不安靜。</t>
+  </si>
+  <si>
+    <t>りょこうは たのしかったですか</t>
+  </si>
+  <si>
+    <t>旅行は 楽しかったですか</t>
+  </si>
+  <si>
+    <t>旅遊玩得開心嗎？</t>
+  </si>
+  <si>
+    <t>…はい、とても たのしかったです</t>
+  </si>
+  <si>
+    <t>…はい、とても 楽しかったです</t>
+  </si>
+  <si>
+    <t>……是的，非常開心</t>
+  </si>
+  <si>
+    <t>てんきは よかったですか</t>
+  </si>
+  <si>
+    <t>天気は よかったですか</t>
+  </si>
+  <si>
+    <t>天氣好嗎？</t>
+  </si>
+  <si>
+    <t>……不，天氣不太好</t>
+  </si>
+  <si>
+    <t>きのうの パーティーは どうでしたか</t>
+  </si>
+  <si>
+    <t>昨天的聚會怎麼樣？</t>
+  </si>
+  <si>
+    <t>…とても にぎやかでした。 いろいろな ひとに あいました</t>
+  </si>
+  <si>
+    <t>…とても にぎやかでした。 いろいろな 人に 会いました</t>
+  </si>
+  <si>
+    <t>……那裡非常熱鬧。我遇到了各種各樣的的人。</t>
+  </si>
+  <si>
+    <t>とうきょうは ニューヨークより ひとが おおいですか</t>
+  </si>
+  <si>
+    <t>東京は ニューヨークより 人が 多いですか</t>
+  </si>
+  <si>
+    <t>東京的人口比紐約多嗎？</t>
+  </si>
+  <si>
+    <t>…はい、ずっと おおいです</t>
+  </si>
+  <si>
+    <t>…はい、ずっと 多いです</t>
+  </si>
+  <si>
+    <t>……是的，東京的人口比紐約多很多。</t>
+  </si>
+  <si>
+    <t>…いいえ、あまりよくなかったです</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>くうこうまで バスと でんしゃと どちらが はやいですか</t>
+  </si>
+  <si>
+    <t>空港まで バスと 電車と どちらが 速いですか</t>
+  </si>
+  <si>
+    <t>去機場，搭公車還是火車最快？</t>
+  </si>
+  <si>
+    <t>…でんしゃの ほうが はやいです</t>
+  </si>
+  <si>
+    <t>…電車の ほうが 速いです</t>
+  </si>
+  <si>
+    <t>……火車比較快。</t>
+  </si>
+  <si>
+    <t>うみと やまと どちらが すきですか</t>
+  </si>
+  <si>
+    <t>海と 山と どちらが 好きですか</t>
+  </si>
+  <si>
+    <t>你喜歡大海還是山？</t>
+  </si>
+  <si>
+    <t>…どちらも すきです</t>
+  </si>
+  <si>
+    <t>…どちらも 好きです</t>
+  </si>
+  <si>
+    <t>……我都喜歡。</t>
+  </si>
+  <si>
+    <t>にほんりょうり [の なか]で なにが いちばん すきですか</t>
+  </si>
+  <si>
+    <t>日本料理 [の 中]で 何が いちばん 好きですか</t>
+  </si>
+  <si>
+    <t>你最喜歡的日本料理是什麼？</t>
+  </si>
+  <si>
+    <t>…てんぷらが いちばん すきです</t>
+  </si>
+  <si>
+    <t>…てんぷらが いちばん 好きです</t>
+  </si>
+  <si>
+    <t>……我最喜歡天婦羅。</t>
   </si>
 </sst>
 </file>
@@ -4298,7 +4871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B91EE72-412B-4BEC-A7E9-A97446845EE1}">
-  <dimension ref="A1:C438"/>
+  <dimension ref="A1:C502"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="57.21875" customWidth="1"/>
@@ -5180,3618 +5753,4307 @@
         <v>341</v>
       </c>
       <c r="B87" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C87" t="s">
         <v>342</v>
-      </c>
-      <c r="C87" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>354</v>
+        <v>1187</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1188</v>
       </c>
       <c r="C88" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>343</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C89" t="s">
         <v>344</v>
-      </c>
-      <c r="B89" t="s">
-        <v>345</v>
-      </c>
-      <c r="C89" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>347</v>
+        <v>1192</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1191</v>
       </c>
       <c r="C90" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B91" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C91" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B92" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C92" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B93" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="C93" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="B94" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="C94" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="B95" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="C95" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="B96" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="C96" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="B97" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C97" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B98" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C98" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B99" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="C99" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B100" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="C100" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B101" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="C101" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="B102" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="C102" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B103" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="C103" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B104" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="C104" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B106" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="C106" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="B107" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C107" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B108" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="C108" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="B109" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="C109" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B110" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="C110" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B111" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="C111" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="B112" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="C112" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="B113" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C113" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B114" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="C114" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B115" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="C115" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="B116" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="C116" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="B117" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="C117" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="B118" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="C118" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="B119" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="C119" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="B120" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="C120" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="B121" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C121" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B122" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C122" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B123" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C123" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="B125" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="C125" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B126" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C126" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="C127" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="B128" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C128" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="B129" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="C129" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B130" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="C130" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B131" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="C131" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="B132" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C132" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="C133" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="B134" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="C134" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="B135" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="C135" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="B136" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="C136" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B137" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="C137" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="B138" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="C138" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B139" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="C139" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="B140" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="C140" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="B141" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="C141" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B143" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="C143" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B144" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="C144" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B145" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="C145" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B146" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="C146" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B147" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="C147" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="C148" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B149" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="C149" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="C150" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="B151" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="C151" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="B152" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C152" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="B153" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="C153" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="B154" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="C154" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="B155" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="C155" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="C156" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="B157" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="C157" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="B158" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="C158" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="B159" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="C159" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="B160" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="C160" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="B161" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="C161" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="B162" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="C162" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B163" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="C163" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="B165" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="C165" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="B166" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="C166" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B167" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="C167" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B168" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="C168" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B169" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="C169" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="B170" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="C170" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="B171" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="C171" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="B172" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="C172" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B173" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="C173" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="B174" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="C174" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="B175" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="C175" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="B176" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="C176" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="C177" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="B178" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="C178" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="B179" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="C179" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="B180" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C180" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="B181" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="C181" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B183" s="2" t="s">
         <v>1024</v>
       </c>
-      <c r="B183" s="2" t="s">
-        <v>1028</v>
-      </c>
       <c r="C183" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="C184" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="B185" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="C185" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="B186" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="C186" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="B187" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="C187" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="B188" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="C188" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="B189" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="C189" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="B190" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="C190" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="B191" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="C191" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="B192" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="C192" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="B193" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="C193" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="B194" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="C194" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B195" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="C195" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="B196" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="C196" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="C197" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="B198" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="C198" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="B199" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="C199" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="B200" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="C200" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="B201" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="C201" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="C202" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="B203" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C203" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="B204" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="C204" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="B205" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="C205" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>659</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>660</v>
+        <v>1195</v>
       </c>
       <c r="B207" t="s">
-        <v>666</v>
+        <v>1196</v>
       </c>
       <c r="C207" t="s">
-        <v>663</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>661</v>
+        <v>1198</v>
       </c>
       <c r="B208" t="s">
-        <v>667</v>
+        <v>1199</v>
       </c>
       <c r="C208" t="s">
-        <v>664</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>662</v>
+        <v>1201</v>
       </c>
       <c r="B209" t="s">
-        <v>668</v>
+        <v>1202</v>
       </c>
       <c r="C209" t="s">
-        <v>665</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>669</v>
+        <v>1204</v>
       </c>
       <c r="B210" t="s">
-        <v>670</v>
+        <v>1205</v>
       </c>
       <c r="C210" t="s">
-        <v>673</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>671</v>
+        <v>1207</v>
       </c>
       <c r="B211" t="s">
-        <v>672</v>
+        <v>1208</v>
       </c>
       <c r="C211" t="s">
-        <v>674</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>675</v>
+        <v>1210</v>
       </c>
       <c r="B212" t="s">
-        <v>676</v>
+        <v>1212</v>
       </c>
       <c r="C212" t="s">
-        <v>691</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>677</v>
+        <v>1213</v>
       </c>
       <c r="B213" t="s">
-        <v>678</v>
+        <v>1214</v>
       </c>
       <c r="C213" t="s">
-        <v>692</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>679</v>
+        <v>1216</v>
       </c>
       <c r="B214" t="s">
-        <v>680</v>
+        <v>1217</v>
       </c>
       <c r="C214" t="s">
-        <v>693</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>681</v>
+        <v>1219</v>
       </c>
       <c r="B215" t="s">
-        <v>682</v>
+        <v>1220</v>
       </c>
       <c r="C215" t="s">
-        <v>694</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>683</v>
+        <v>1222</v>
       </c>
       <c r="B216" t="s">
-        <v>684</v>
+        <v>1223</v>
       </c>
       <c r="C216" t="s">
-        <v>695</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>685</v>
+        <v>1225</v>
       </c>
       <c r="B217" t="s">
-        <v>686</v>
+        <v>1226</v>
       </c>
       <c r="C217" t="s">
-        <v>696</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>690</v>
+        <v>1228</v>
       </c>
       <c r="B218" t="s">
-        <v>687</v>
+        <v>1229</v>
       </c>
       <c r="C218" t="s">
-        <v>697</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>688</v>
+        <v>1231</v>
       </c>
       <c r="B219" t="s">
-        <v>689</v>
+        <v>1232</v>
       </c>
       <c r="C219" t="s">
-        <v>698</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>699</v>
+        <v>1234</v>
       </c>
       <c r="B220" t="s">
-        <v>700</v>
+        <v>1235</v>
       </c>
       <c r="C220" t="s">
-        <v>707</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>701</v>
+        <v>1237</v>
       </c>
       <c r="B221" t="s">
-        <v>702</v>
+        <v>1238</v>
       </c>
       <c r="C221" t="s">
-        <v>708</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>703</v>
+        <v>1240</v>
       </c>
       <c r="B222" t="s">
-        <v>704</v>
+        <v>1241</v>
       </c>
       <c r="C222" t="s">
-        <v>709</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>705</v>
+        <v>1243</v>
       </c>
       <c r="B223" t="s">
-        <v>706</v>
+        <v>1244</v>
       </c>
       <c r="C223" t="s">
-        <v>710</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>170</v>
+        <v>1246</v>
+      </c>
+      <c r="B224" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C224" t="s">
+        <v>1248</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>171</v>
+        <v>1249</v>
+      </c>
+      <c r="B225" t="s">
+        <v>1250</v>
       </c>
       <c r="C225" t="s">
-        <v>172</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>173</v>
+        <v>1252</v>
       </c>
       <c r="B226" t="s">
-        <v>174</v>
+        <v>1253</v>
       </c>
       <c r="C226" t="s">
-        <v>175</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>176</v>
+        <v>1255</v>
+      </c>
+      <c r="B227" t="s">
+        <v>1256</v>
       </c>
       <c r="C227" t="s">
-        <v>177</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>178</v>
+        <v>1258</v>
       </c>
       <c r="B228" t="s">
-        <v>179</v>
+        <v>1259</v>
       </c>
       <c r="C228" t="s">
-        <v>180</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>176</v>
+        <v>1261</v>
       </c>
       <c r="B229" t="s">
-        <v>181</v>
+        <v>1262</v>
       </c>
       <c r="C229" t="s">
-        <v>177</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>182</v>
+        <v>1264</v>
       </c>
       <c r="B230" t="s">
-        <v>183</v>
+        <v>1265</v>
       </c>
       <c r="C230" t="s">
-        <v>180</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>184</v>
+        <v>1267</v>
+      </c>
+      <c r="B231" t="s">
+        <v>1268</v>
       </c>
       <c r="C231" t="s">
-        <v>185</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>186</v>
+        <v>1270</v>
       </c>
       <c r="B232" t="s">
-        <v>187</v>
+        <v>1271</v>
       </c>
       <c r="C232" t="s">
-        <v>188</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>189</v>
+        <v>1273</v>
       </c>
       <c r="B233" t="s">
-        <v>190</v>
+        <v>1274</v>
       </c>
       <c r="C233" t="s">
-        <v>191</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>192</v>
+        <v>1276</v>
       </c>
       <c r="B234" t="s">
-        <v>193</v>
+        <v>1277</v>
+      </c>
+      <c r="C234" t="s">
+        <v>1275</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>194</v>
+        <v>1278</v>
       </c>
       <c r="B235" t="s">
-        <v>195</v>
+        <v>1279</v>
       </c>
       <c r="C235" t="s">
-        <v>196</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>197</v>
+        <v>1281</v>
       </c>
       <c r="B236" t="s">
-        <v>198</v>
+        <v>1282</v>
       </c>
       <c r="C236" t="s">
-        <v>199</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>200</v>
+        <v>1284</v>
       </c>
       <c r="B237" t="s">
-        <v>202</v>
+        <v>1285</v>
       </c>
       <c r="C237" t="s">
-        <v>201</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>203</v>
+        <v>1287</v>
       </c>
       <c r="B238" t="s">
-        <v>204</v>
+        <v>1288</v>
       </c>
       <c r="C238" t="s">
-        <v>205</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>206</v>
+        <v>1290</v>
       </c>
       <c r="B239" t="s">
-        <v>207</v>
+        <v>1291</v>
       </c>
       <c r="C239" t="s">
-        <v>208</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>209</v>
+        <v>1293</v>
       </c>
       <c r="B240" t="s">
-        <v>210</v>
+        <v>1294</v>
       </c>
       <c r="C240" t="s">
-        <v>211</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>212</v>
+        <v>1296</v>
       </c>
       <c r="B241" t="s">
-        <v>213</v>
+        <v>1297</v>
       </c>
       <c r="C241" t="s">
-        <v>214</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>215</v>
+        <v>1299</v>
       </c>
       <c r="B242" t="s">
-        <v>216</v>
+        <v>1300</v>
       </c>
       <c r="C242" t="s">
-        <v>217</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>218</v>
+        <v>1302</v>
       </c>
       <c r="B243" t="s">
-        <v>219</v>
+        <v>1303</v>
+      </c>
+      <c r="C243" t="s">
+        <v>1304</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>357</v>
+        <v>1305</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C244" t="s">
+        <v>1307</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>412</v>
+        <v>1308</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1309</v>
       </c>
       <c r="C245" t="s">
-        <v>374</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>413</v>
+        <v>1311</v>
       </c>
       <c r="B246" t="s">
-        <v>409</v>
+        <v>1328</v>
       </c>
       <c r="C246" t="s">
-        <v>374</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>410</v>
+        <v>1313</v>
+      </c>
+      <c r="B247" t="s">
+        <v>1314</v>
       </c>
       <c r="C247" t="s">
-        <v>411</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>373</v>
-      </c>
-      <c r="B248" t="s">
-        <v>358</v>
-      </c>
-      <c r="C248" t="s">
-        <v>359</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>414</v>
+        <v>1327</v>
+      </c>
+      <c r="B249" t="s">
+        <v>1330</v>
       </c>
       <c r="C249" t="s">
-        <v>415</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>429</v>
+        <v>1316</v>
       </c>
       <c r="B250" t="s">
-        <v>428</v>
+        <v>1317</v>
       </c>
       <c r="C250" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>430</v>
+        <v>1319</v>
       </c>
       <c r="B251" t="s">
-        <v>427</v>
+        <v>1320</v>
       </c>
       <c r="C251" t="s">
-        <v>431</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>420</v>
+        <v>1325</v>
       </c>
       <c r="B252" t="s">
-        <v>421</v>
+        <v>1326</v>
       </c>
       <c r="C252" t="s">
-        <v>416</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>361</v>
+        <v>1323</v>
       </c>
       <c r="B253" t="s">
-        <v>362</v>
+        <v>1329</v>
       </c>
       <c r="C253" t="s">
-        <v>432</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>418</v>
+        <v>1332</v>
       </c>
       <c r="B254" t="s">
-        <v>417</v>
-      </c>
-      <c r="C254" t="s">
-        <v>419</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>423</v>
+        <v>1334</v>
       </c>
       <c r="B255" t="s">
-        <v>422</v>
+        <v>1335</v>
       </c>
       <c r="C255" t="s">
-        <v>424</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>433</v>
+        <v>1337</v>
       </c>
       <c r="B256" t="s">
-        <v>434</v>
+        <v>1338</v>
       </c>
       <c r="C256" t="s">
-        <v>435</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>426</v>
+        <v>1340</v>
       </c>
       <c r="B257" t="s">
-        <v>425</v>
+        <v>1341</v>
       </c>
       <c r="C257" t="s">
-        <v>436</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>363</v>
+        <v>1343</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1344</v>
       </c>
       <c r="C258" t="s">
-        <v>364</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>365</v>
-      </c>
-      <c r="B259" t="s">
-        <v>366</v>
+        <v>1358</v>
       </c>
       <c r="C259" t="s">
-        <v>367</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>368</v>
-      </c>
-      <c r="B260" t="s">
-        <v>369</v>
+        <v>1347</v>
       </c>
       <c r="C260" t="s">
-        <v>370</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>371</v>
+        <v>1349</v>
+      </c>
+      <c r="B261" t="s">
+        <v>1350</v>
       </c>
       <c r="C261" t="s">
-        <v>372</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>375</v>
+        <v>1352</v>
       </c>
       <c r="B262" t="s">
-        <v>376</v>
+        <v>1353</v>
       </c>
       <c r="C262" t="s">
-        <v>377</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>378</v>
+        <v>1355</v>
       </c>
       <c r="B263" t="s">
-        <v>379</v>
+        <v>1356</v>
       </c>
       <c r="C263" t="s">
-        <v>380</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>381</v>
+        <v>1359</v>
       </c>
       <c r="B264" t="s">
-        <v>382</v>
+        <v>1360</v>
+      </c>
+      <c r="C264" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>406</v>
+        <v>1362</v>
       </c>
       <c r="B265" t="s">
-        <v>407</v>
+        <v>1363</v>
       </c>
       <c r="C265" t="s">
-        <v>405</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>383</v>
+        <v>1365</v>
       </c>
       <c r="B266" t="s">
-        <v>384</v>
+        <v>1366</v>
       </c>
       <c r="C266" t="s">
-        <v>385</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>386</v>
+        <v>1368</v>
       </c>
       <c r="B267" t="s">
-        <v>387</v>
+        <v>1369</v>
       </c>
       <c r="C267" t="s">
-        <v>388</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>389</v>
+        <v>1371</v>
       </c>
       <c r="B268" t="s">
-        <v>408</v>
+        <v>1372</v>
       </c>
       <c r="C268" t="s">
-        <v>404</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>390</v>
+        <v>1374</v>
       </c>
       <c r="B269" t="s">
-        <v>391</v>
+        <v>1375</v>
       </c>
       <c r="C269" t="s">
-        <v>392</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>393</v>
-      </c>
-      <c r="B270" t="s">
-        <v>394</v>
-      </c>
-      <c r="C270" t="s">
-        <v>395</v>
+        <v>655</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>396</v>
+        <v>656</v>
+      </c>
+      <c r="B271" t="s">
+        <v>662</v>
       </c>
       <c r="C271" t="s">
-        <v>397</v>
+        <v>659</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>398</v>
+        <v>657</v>
       </c>
       <c r="B272" t="s">
-        <v>399</v>
+        <v>663</v>
       </c>
       <c r="C272" t="s">
-        <v>400</v>
+        <v>660</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>401</v>
+        <v>658</v>
       </c>
       <c r="B273" t="s">
-        <v>402</v>
+        <v>664</v>
       </c>
       <c r="C273" t="s">
-        <v>403</v>
+        <v>661</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>437</v>
+        <v>665</v>
+      </c>
+      <c r="B274" t="s">
+        <v>666</v>
+      </c>
+      <c r="C274" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>487</v>
+        <v>667</v>
       </c>
       <c r="B275" t="s">
-        <v>438</v>
+        <v>668</v>
       </c>
       <c r="C275" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>491</v>
+        <v>671</v>
       </c>
       <c r="B276" t="s">
-        <v>488</v>
+        <v>672</v>
       </c>
       <c r="C276" t="s">
-        <v>489</v>
+        <v>687</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>444</v>
+        <v>673</v>
       </c>
       <c r="B277" t="s">
-        <v>445</v>
+        <v>674</v>
       </c>
       <c r="C277" t="s">
-        <v>440</v>
+        <v>688</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>493</v>
+        <v>675</v>
       </c>
       <c r="B278" t="s">
-        <v>492</v>
+        <v>676</v>
       </c>
       <c r="C278" t="s">
-        <v>490</v>
+        <v>689</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>441</v>
+        <v>677</v>
       </c>
       <c r="B279" t="s">
-        <v>442</v>
+        <v>678</v>
       </c>
       <c r="C279" t="s">
-        <v>443</v>
+        <v>690</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>446</v>
+        <v>679</v>
       </c>
       <c r="B280" t="s">
-        <v>447</v>
+        <v>680</v>
       </c>
       <c r="C280" t="s">
-        <v>448</v>
+        <v>691</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>449</v>
+        <v>681</v>
       </c>
       <c r="B281" t="s">
-        <v>450</v>
+        <v>682</v>
       </c>
       <c r="C281" t="s">
-        <v>451</v>
+        <v>692</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>452</v>
+        <v>686</v>
       </c>
       <c r="B282" t="s">
-        <v>453</v>
+        <v>683</v>
       </c>
       <c r="C282" t="s">
-        <v>454</v>
+        <v>693</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>455</v>
+        <v>684</v>
       </c>
       <c r="B283" t="s">
-        <v>456</v>
+        <v>685</v>
       </c>
       <c r="C283" t="s">
-        <v>457</v>
+        <v>694</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>458</v>
+        <v>695</v>
       </c>
       <c r="B284" t="s">
-        <v>459</v>
+        <v>696</v>
       </c>
       <c r="C284" t="s">
-        <v>460</v>
+        <v>703</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>463</v>
+        <v>697</v>
       </c>
       <c r="B285" t="s">
-        <v>461</v>
+        <v>698</v>
       </c>
       <c r="C285" t="s">
-        <v>462</v>
+        <v>704</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>464</v>
+        <v>699</v>
       </c>
       <c r="B286" t="s">
-        <v>465</v>
+        <v>700</v>
       </c>
       <c r="C286" t="s">
-        <v>466</v>
+        <v>705</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>467</v>
+        <v>701</v>
       </c>
       <c r="B287" t="s">
-        <v>468</v>
+        <v>702</v>
       </c>
       <c r="C287" t="s">
-        <v>469</v>
+        <v>706</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>470</v>
-      </c>
-      <c r="B288" t="s">
-        <v>471</v>
-      </c>
-      <c r="C288" t="s">
-        <v>472</v>
+        <v>170</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>473</v>
+        <v>171</v>
       </c>
       <c r="C289" t="s">
-        <v>474</v>
+        <v>172</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>475</v>
+        <v>173</v>
       </c>
       <c r="B290" t="s">
-        <v>476</v>
+        <v>174</v>
       </c>
       <c r="C290" t="s">
-        <v>477</v>
+        <v>175</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>478</v>
-      </c>
-      <c r="B291" t="s">
-        <v>479</v>
+        <v>176</v>
       </c>
       <c r="C291" t="s">
-        <v>480</v>
+        <v>177</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>481</v>
+        <v>178</v>
       </c>
       <c r="B292" t="s">
-        <v>482</v>
+        <v>179</v>
       </c>
       <c r="C292" t="s">
-        <v>483</v>
+        <v>180</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>485</v>
+        <v>176</v>
       </c>
       <c r="B293" t="s">
-        <v>486</v>
+        <v>181</v>
       </c>
       <c r="C293" t="s">
-        <v>484</v>
+        <v>177</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>550</v>
+        <v>182</v>
+      </c>
+      <c r="B294" t="s">
+        <v>183</v>
+      </c>
+      <c r="C294" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>552</v>
-      </c>
-      <c r="B295" t="s">
-        <v>553</v>
+        <v>184</v>
       </c>
       <c r="C295" t="s">
-        <v>554</v>
+        <v>185</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>555</v>
+        <v>186</v>
       </c>
       <c r="B296" t="s">
-        <v>556</v>
+        <v>187</v>
       </c>
       <c r="C296" t="s">
-        <v>557</v>
+        <v>188</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>558</v>
+        <v>189</v>
       </c>
       <c r="B297" t="s">
-        <v>559</v>
+        <v>190</v>
       </c>
       <c r="C297" t="s">
-        <v>560</v>
+        <v>191</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>561</v>
+        <v>192</v>
       </c>
       <c r="B298" t="s">
-        <v>562</v>
-      </c>
-      <c r="C298" t="s">
-        <v>563</v>
+        <v>193</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>564</v>
+        <v>194</v>
       </c>
       <c r="B299" t="s">
-        <v>565</v>
+        <v>195</v>
       </c>
       <c r="C299" t="s">
-        <v>566</v>
+        <v>196</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>567</v>
+        <v>197</v>
+      </c>
+      <c r="B300" t="s">
+        <v>198</v>
       </c>
       <c r="C300" t="s">
-        <v>568</v>
+        <v>199</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>569</v>
+        <v>200</v>
+      </c>
+      <c r="B301" t="s">
+        <v>202</v>
       </c>
       <c r="C301" t="s">
-        <v>570</v>
+        <v>201</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>571</v>
+        <v>203</v>
+      </c>
+      <c r="B302" t="s">
+        <v>204</v>
       </c>
       <c r="C302" t="s">
-        <v>572</v>
+        <v>205</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>573</v>
+        <v>206</v>
       </c>
       <c r="B303" t="s">
-        <v>574</v>
+        <v>207</v>
       </c>
       <c r="C303" t="s">
-        <v>575</v>
+        <v>208</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>576</v>
+        <v>209</v>
       </c>
       <c r="B304" t="s">
-        <v>577</v>
+        <v>210</v>
       </c>
       <c r="C304" t="s">
-        <v>578</v>
+        <v>211</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>579</v>
+        <v>212</v>
       </c>
       <c r="B305" t="s">
-        <v>580</v>
+        <v>213</v>
       </c>
       <c r="C305" t="s">
-        <v>581</v>
+        <v>214</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>582</v>
+        <v>215</v>
+      </c>
+      <c r="B306" t="s">
+        <v>216</v>
       </c>
       <c r="C306" t="s">
-        <v>583</v>
+        <v>217</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>584</v>
-      </c>
-      <c r="C307" t="s">
-        <v>585</v>
+        <v>218</v>
+      </c>
+      <c r="B307" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>586</v>
-      </c>
-      <c r="B308" t="s">
-        <v>587</v>
-      </c>
-      <c r="C308" t="s">
-        <v>588</v>
+        <v>353</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>589</v>
-      </c>
-      <c r="B309" t="s">
-        <v>590</v>
+        <v>408</v>
       </c>
       <c r="C309" t="s">
-        <v>591</v>
+        <v>370</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>592</v>
+        <v>409</v>
       </c>
       <c r="B310" t="s">
-        <v>600</v>
+        <v>405</v>
       </c>
       <c r="C310" t="s">
-        <v>593</v>
+        <v>370</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>594</v>
-      </c>
-      <c r="B311" t="s">
-        <v>601</v>
+        <v>406</v>
       </c>
       <c r="C311" t="s">
-        <v>602</v>
+        <v>407</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>595</v>
+        <v>369</v>
       </c>
       <c r="B312" t="s">
-        <v>596</v>
+        <v>354</v>
       </c>
       <c r="C312" t="s">
-        <v>603</v>
+        <v>355</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>597</v>
-      </c>
-      <c r="B313" t="s">
-        <v>598</v>
+        <v>410</v>
       </c>
       <c r="C313" t="s">
-        <v>599</v>
+        <v>411</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+        <v>425</v>
+      </c>
+      <c r="B314" t="s">
+        <v>424</v>
+      </c>
+      <c r="C314" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>604</v>
+        <v>426</v>
       </c>
       <c r="B315" t="s">
-        <v>605</v>
+        <v>423</v>
       </c>
       <c r="C315" t="s">
-        <v>606</v>
+        <v>427</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>607</v>
+        <v>416</v>
       </c>
       <c r="B316" t="s">
-        <v>609</v>
+        <v>417</v>
       </c>
       <c r="C316" t="s">
-        <v>608</v>
+        <v>412</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>610</v>
+        <v>357</v>
       </c>
       <c r="B317" t="s">
-        <v>621</v>
+        <v>358</v>
       </c>
       <c r="C317" t="s">
-        <v>611</v>
+        <v>428</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>612</v>
+        <v>414</v>
       </c>
       <c r="B318" t="s">
-        <v>613</v>
+        <v>413</v>
       </c>
       <c r="C318" t="s">
-        <v>614</v>
+        <v>415</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>615</v>
+        <v>419</v>
       </c>
       <c r="B319" t="s">
-        <v>616</v>
+        <v>418</v>
       </c>
       <c r="C319" t="s">
-        <v>617</v>
+        <v>420</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>618</v>
+        <v>429</v>
       </c>
       <c r="B320" t="s">
-        <v>619</v>
+        <v>430</v>
       </c>
       <c r="C320" t="s">
-        <v>620</v>
+        <v>431</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>622</v>
+        <v>422</v>
+      </c>
+      <c r="B321" t="s">
+        <v>421</v>
       </c>
       <c r="C321" t="s">
-        <v>623</v>
+        <v>432</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>624</v>
-      </c>
-      <c r="B322" t="s">
-        <v>625</v>
+        <v>359</v>
       </c>
       <c r="C322" t="s">
-        <v>626</v>
+        <v>360</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>627</v>
+        <v>361</v>
       </c>
       <c r="B323" t="s">
-        <v>628</v>
+        <v>362</v>
       </c>
       <c r="C323" t="s">
-        <v>629</v>
+        <v>363</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>635</v>
+        <v>364</v>
       </c>
       <c r="B324" t="s">
-        <v>630</v>
+        <v>365</v>
       </c>
       <c r="C324" t="s">
-        <v>631</v>
+        <v>366</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>632</v>
-      </c>
-      <c r="B325" t="s">
-        <v>633</v>
+        <v>367</v>
       </c>
       <c r="C325" t="s">
-        <v>634</v>
+        <v>368</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>636</v>
+        <v>371</v>
       </c>
       <c r="B326" t="s">
-        <v>637</v>
+        <v>372</v>
       </c>
       <c r="C326" t="s">
-        <v>638</v>
+        <v>373</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>641</v>
+        <v>374</v>
       </c>
       <c r="B327" t="s">
-        <v>639</v>
+        <v>375</v>
       </c>
       <c r="C327" t="s">
-        <v>640</v>
+        <v>376</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>642</v>
+        <v>377</v>
       </c>
       <c r="B328" t="s">
-        <v>643</v>
-      </c>
-      <c r="C328" t="s">
-        <v>644</v>
+        <v>378</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>645</v>
+        <v>402</v>
       </c>
       <c r="B329" t="s">
-        <v>646</v>
+        <v>403</v>
       </c>
       <c r="C329" t="s">
-        <v>647</v>
+        <v>401</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>648</v>
+        <v>379</v>
       </c>
       <c r="B330" t="s">
-        <v>649</v>
+        <v>380</v>
       </c>
       <c r="C330" t="s">
-        <v>650</v>
+        <v>381</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>651</v>
+        <v>382</v>
       </c>
       <c r="B331" t="s">
-        <v>652</v>
+        <v>383</v>
       </c>
       <c r="C331" t="s">
-        <v>653</v>
+        <v>384</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>658</v>
+        <v>385</v>
       </c>
       <c r="B332" t="s">
-        <v>654</v>
+        <v>404</v>
       </c>
       <c r="C332" t="s">
-        <v>655</v>
+        <v>400</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>656</v>
+        <v>386</v>
+      </c>
+      <c r="B333" t="s">
+        <v>387</v>
       </c>
       <c r="C333" t="s">
-        <v>657</v>
+        <v>388</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>494</v>
+        <v>389</v>
+      </c>
+      <c r="B334" t="s">
+        <v>390</v>
+      </c>
+      <c r="C334" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>495</v>
-      </c>
-      <c r="B335" t="s">
-        <v>496</v>
+        <v>392</v>
       </c>
       <c r="C335" t="s">
-        <v>497</v>
+        <v>393</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>498</v>
+        <v>394</v>
       </c>
       <c r="B336" t="s">
-        <v>499</v>
+        <v>395</v>
       </c>
       <c r="C336" t="s">
-        <v>500</v>
+        <v>396</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>501</v>
+        <v>397</v>
       </c>
       <c r="B337" t="s">
-        <v>502</v>
+        <v>398</v>
       </c>
       <c r="C337" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>504</v>
-      </c>
-      <c r="B338" t="s">
-        <v>505</v>
-      </c>
-      <c r="C338" t="s">
-        <v>506</v>
+        <v>433</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>507</v>
+        <v>483</v>
       </c>
       <c r="B339" t="s">
-        <v>508</v>
+        <v>434</v>
       </c>
       <c r="C339" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>510</v>
+        <v>487</v>
+      </c>
+      <c r="B340" t="s">
+        <v>484</v>
       </c>
       <c r="C340" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>512</v>
+        <v>440</v>
       </c>
       <c r="B341" t="s">
-        <v>513</v>
+        <v>441</v>
       </c>
       <c r="C341" t="s">
-        <v>514</v>
+        <v>436</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="B342" t="s">
-        <v>516</v>
+        <v>488</v>
       </c>
       <c r="C342" t="s">
-        <v>517</v>
+        <v>486</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>518</v>
+        <v>437</v>
       </c>
       <c r="B343" t="s">
-        <v>519</v>
+        <v>438</v>
       </c>
       <c r="C343" t="s">
-        <v>520</v>
+        <v>439</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>521</v>
+        <v>442</v>
       </c>
       <c r="B344" t="s">
-        <v>522</v>
+        <v>443</v>
       </c>
       <c r="C344" t="s">
-        <v>523</v>
+        <v>444</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>524</v>
+        <v>445</v>
       </c>
       <c r="B345" t="s">
-        <v>525</v>
+        <v>446</v>
       </c>
       <c r="C345" t="s">
-        <v>526</v>
+        <v>447</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>527</v>
+        <v>448</v>
       </c>
       <c r="B346" t="s">
-        <v>528</v>
+        <v>449</v>
       </c>
       <c r="C346" t="s">
-        <v>529</v>
+        <v>450</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>530</v>
+        <v>451</v>
       </c>
       <c r="B347" t="s">
-        <v>539</v>
+        <v>452</v>
       </c>
       <c r="C347" t="s">
-        <v>531</v>
+        <v>453</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>532</v>
+        <v>454</v>
+      </c>
+      <c r="B348" t="s">
+        <v>455</v>
       </c>
       <c r="C348" t="s">
-        <v>533</v>
+        <v>456</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>534</v>
+        <v>459</v>
+      </c>
+      <c r="B349" t="s">
+        <v>457</v>
       </c>
       <c r="C349" t="s">
-        <v>535</v>
+        <v>458</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>536</v>
+        <v>460</v>
       </c>
       <c r="B350" t="s">
-        <v>537</v>
+        <v>461</v>
       </c>
       <c r="C350" t="s">
-        <v>538</v>
+        <v>462</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>540</v>
+        <v>463</v>
       </c>
       <c r="B351" t="s">
-        <v>541</v>
+        <v>464</v>
       </c>
       <c r="C351" t="s">
-        <v>542</v>
+        <v>465</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>543</v>
+        <v>466</v>
       </c>
       <c r="B352" t="s">
-        <v>549</v>
+        <v>467</v>
       </c>
       <c r="C352" t="s">
-        <v>544</v>
+        <v>468</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>197</v>
-      </c>
-      <c r="B353" t="s">
-        <v>198</v>
+        <v>469</v>
       </c>
       <c r="C353" t="s">
-        <v>545</v>
+        <v>470</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>546</v>
+        <v>471</v>
       </c>
       <c r="B354" t="s">
-        <v>547</v>
+        <v>472</v>
       </c>
       <c r="C354" t="s">
-        <v>548</v>
+        <v>473</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>711</v>
+        <v>474</v>
+      </c>
+      <c r="B355" t="s">
+        <v>475</v>
+      </c>
+      <c r="C355" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>1090</v>
+        <v>477</v>
       </c>
       <c r="B356" t="s">
-        <v>1091</v>
+        <v>478</v>
       </c>
       <c r="C356" t="s">
-        <v>1092</v>
+        <v>479</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>1115</v>
+        <v>481</v>
       </c>
       <c r="B357" t="s">
-        <v>1114</v>
+        <v>482</v>
       </c>
       <c r="C357" t="s">
-        <v>1093</v>
+        <v>480</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C358" t="s">
-        <v>1095</v>
+        <v>546</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>1096</v>
+        <v>548</v>
       </c>
       <c r="B359" t="s">
-        <v>1097</v>
+        <v>549</v>
       </c>
       <c r="C359" t="s">
-        <v>1098</v>
+        <v>550</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>1099</v>
+        <v>551</v>
       </c>
       <c r="B360" t="s">
-        <v>1100</v>
+        <v>552</v>
       </c>
       <c r="C360" t="s">
-        <v>1101</v>
+        <v>553</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>1102</v>
+        <v>554</v>
       </c>
       <c r="B361" t="s">
-        <v>1103</v>
+        <v>555</v>
+      </c>
+      <c r="C361" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>1104</v>
+        <v>557</v>
+      </c>
+      <c r="B362" t="s">
+        <v>558</v>
       </c>
       <c r="C362" t="s">
-        <v>1105</v>
+        <v>559</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>1106</v>
+        <v>560</v>
       </c>
       <c r="B363" t="s">
-        <v>1107</v>
+        <v>561</v>
+      </c>
+      <c r="C363" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>1108</v>
+        <v>563</v>
       </c>
       <c r="C364" t="s">
-        <v>1109</v>
+        <v>564</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>1110</v>
-      </c>
-      <c r="B365" t="s">
-        <v>1111</v>
+        <v>565</v>
+      </c>
+      <c r="C365" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>1112</v>
+        <v>567</v>
       </c>
       <c r="C366" t="s">
-        <v>1113</v>
+        <v>568</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>1116</v>
+        <v>569</v>
+      </c>
+      <c r="B367" t="s">
+        <v>570</v>
       </c>
       <c r="C367" t="s">
-        <v>1117</v>
+        <v>571</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>1118</v>
+        <v>572</v>
+      </c>
+      <c r="B368" t="s">
+        <v>573</v>
       </c>
       <c r="C368" t="s">
-        <v>1119</v>
+        <v>574</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>1120</v>
+        <v>575</v>
+      </c>
+      <c r="B369" t="s">
+        <v>576</v>
       </c>
       <c r="C369" t="s">
-        <v>1121</v>
+        <v>577</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>1122</v>
+        <v>578</v>
       </c>
       <c r="C370" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A371" s="3" t="s">
-        <v>1127</v>
-      </c>
-      <c r="B371" t="s">
-        <v>1125</v>
+        <v>579</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>580</v>
       </c>
       <c r="C371" t="s">
-        <v>1126</v>
+        <v>581</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>1128</v>
+        <v>582</v>
       </c>
       <c r="B372" t="s">
-        <v>1129</v>
+        <v>583</v>
       </c>
       <c r="C372" t="s">
-        <v>1130</v>
+        <v>584</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>1131</v>
+        <v>585</v>
       </c>
       <c r="B373" t="s">
-        <v>1132</v>
+        <v>586</v>
       </c>
       <c r="C373" t="s">
-        <v>1133</v>
+        <v>587</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>1134</v>
+        <v>588</v>
       </c>
       <c r="B374" t="s">
-        <v>1135</v>
+        <v>596</v>
       </c>
       <c r="C374" t="s">
-        <v>1136</v>
+        <v>589</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>1137</v>
+        <v>590</v>
       </c>
       <c r="B375" t="s">
-        <v>1138</v>
+        <v>597</v>
       </c>
       <c r="C375" t="s">
-        <v>1139</v>
+        <v>598</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>712</v>
+        <v>591</v>
       </c>
       <c r="B376" t="s">
-        <v>727</v>
+        <v>592</v>
       </c>
       <c r="C376" t="s">
-        <v>713</v>
+        <v>599</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>1124</v>
+        <v>593</v>
       </c>
       <c r="B377" t="s">
-        <v>728</v>
+        <v>594</v>
       </c>
       <c r="C377" t="s">
-        <v>714</v>
+        <v>595</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>715</v>
-      </c>
-      <c r="B378" t="s">
-        <v>716</v>
-      </c>
-      <c r="C378" t="s">
-        <v>717</v>
+        <v>547</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>718</v>
+        <v>600</v>
       </c>
       <c r="B379" t="s">
-        <v>719</v>
+        <v>601</v>
       </c>
       <c r="C379" t="s">
-        <v>720</v>
+        <v>602</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>721</v>
+        <v>603</v>
       </c>
       <c r="B380" t="s">
-        <v>722</v>
+        <v>605</v>
       </c>
       <c r="C380" t="s">
-        <v>723</v>
+        <v>604</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>724</v>
+        <v>606</v>
       </c>
       <c r="B381" t="s">
-        <v>725</v>
+        <v>617</v>
       </c>
       <c r="C381" t="s">
-        <v>726</v>
+        <v>607</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>729</v>
+        <v>608</v>
       </c>
       <c r="B382" t="s">
-        <v>769</v>
+        <v>609</v>
       </c>
       <c r="C382" t="s">
-        <v>730</v>
+        <v>610</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>731</v>
+        <v>611</v>
       </c>
       <c r="B383" t="s">
-        <v>732</v>
+        <v>612</v>
       </c>
       <c r="C383" t="s">
-        <v>733</v>
+        <v>613</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>734</v>
+        <v>614</v>
       </c>
       <c r="B384" t="s">
-        <v>735</v>
+        <v>615</v>
       </c>
       <c r="C384" t="s">
-        <v>736</v>
+        <v>616</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>737</v>
-      </c>
-      <c r="B385" t="s">
-        <v>738</v>
+        <v>618</v>
       </c>
       <c r="C385" t="s">
-        <v>739</v>
+        <v>619</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>740</v>
+        <v>620</v>
       </c>
       <c r="B386" t="s">
-        <v>770</v>
+        <v>621</v>
       </c>
       <c r="C386" t="s">
-        <v>741</v>
+        <v>622</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>742</v>
+        <v>623</v>
       </c>
       <c r="B387" t="s">
-        <v>743</v>
+        <v>624</v>
       </c>
       <c r="C387" t="s">
-        <v>744</v>
+        <v>625</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>745</v>
+        <v>631</v>
       </c>
       <c r="B388" t="s">
-        <v>771</v>
+        <v>626</v>
       </c>
       <c r="C388" t="s">
-        <v>746</v>
+        <v>627</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>747</v>
+        <v>628</v>
       </c>
       <c r="B389" t="s">
-        <v>772</v>
+        <v>629</v>
       </c>
       <c r="C389" t="s">
-        <v>748</v>
+        <v>630</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>749</v>
+        <v>632</v>
+      </c>
+      <c r="B390" t="s">
+        <v>633</v>
       </c>
       <c r="C390" t="s">
-        <v>750</v>
+        <v>634</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>751</v>
+        <v>637</v>
       </c>
       <c r="B391" t="s">
-        <v>752</v>
+        <v>635</v>
       </c>
       <c r="C391" t="s">
-        <v>753</v>
+        <v>636</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>754</v>
+        <v>638</v>
       </c>
       <c r="B392" t="s">
-        <v>755</v>
+        <v>639</v>
       </c>
       <c r="C392" t="s">
-        <v>756</v>
+        <v>640</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>757</v>
+        <v>641</v>
       </c>
       <c r="B393" t="s">
-        <v>758</v>
+        <v>642</v>
       </c>
       <c r="C393" t="s">
-        <v>759</v>
+        <v>643</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>760</v>
+        <v>644</v>
       </c>
       <c r="B394" t="s">
-        <v>761</v>
+        <v>645</v>
       </c>
       <c r="C394" t="s">
-        <v>762</v>
+        <v>646</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>763</v>
+        <v>647</v>
       </c>
       <c r="B395" t="s">
-        <v>764</v>
+        <v>648</v>
       </c>
       <c r="C395" t="s">
-        <v>765</v>
+        <v>649</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>766</v>
+        <v>654</v>
       </c>
       <c r="B396" t="s">
-        <v>767</v>
+        <v>650</v>
       </c>
       <c r="C396" t="s">
-        <v>768</v>
+        <v>651</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>1140</v>
+        <v>652</v>
+      </c>
+      <c r="C397" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>1153</v>
-      </c>
-      <c r="B398" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C398" t="s">
-        <v>1159</v>
+        <v>490</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>1155</v>
+        <v>491</v>
       </c>
       <c r="B399" t="s">
-        <v>1156</v>
+        <v>492</v>
       </c>
       <c r="C399" t="s">
-        <v>1160</v>
+        <v>493</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>1157</v>
+        <v>494</v>
       </c>
       <c r="B400" t="s">
-        <v>1158</v>
+        <v>495</v>
       </c>
       <c r="C400" t="s">
-        <v>1161</v>
+        <v>496</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>1141</v>
+        <v>497</v>
       </c>
       <c r="B401" t="s">
-        <v>1142</v>
+        <v>498</v>
       </c>
       <c r="C401" t="s">
-        <v>1143</v>
+        <v>499</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>1144</v>
+        <v>500</v>
       </c>
       <c r="B402" t="s">
-        <v>1145</v>
+        <v>501</v>
       </c>
       <c r="C402" t="s">
-        <v>1146</v>
+        <v>502</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>1147</v>
+        <v>503</v>
       </c>
       <c r="B403" t="s">
-        <v>1148</v>
+        <v>504</v>
       </c>
       <c r="C403" t="s">
-        <v>1149</v>
+        <v>505</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B404" t="s">
-        <v>1151</v>
+        <v>506</v>
       </c>
       <c r="C404" t="s">
-        <v>1152</v>
+        <v>507</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>1162</v>
+        <v>508</v>
       </c>
       <c r="B405" t="s">
-        <v>1163</v>
+        <v>509</v>
       </c>
       <c r="C405" t="s">
-        <v>1164</v>
+        <v>510</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>1165</v>
+        <v>511</v>
       </c>
       <c r="B406" t="s">
-        <v>1176</v>
+        <v>512</v>
       </c>
       <c r="C406" t="s">
-        <v>1166</v>
+        <v>513</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>1167</v>
+        <v>514</v>
+      </c>
+      <c r="B407" t="s">
+        <v>515</v>
       </c>
       <c r="C407" t="s">
-        <v>1168</v>
+        <v>516</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>1169</v>
+        <v>517</v>
       </c>
       <c r="B408" t="s">
-        <v>1177</v>
+        <v>518</v>
       </c>
       <c r="C408" t="s">
-        <v>1170</v>
+        <v>519</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>1178</v>
+        <v>520</v>
       </c>
       <c r="B409" t="s">
-        <v>1171</v>
+        <v>521</v>
       </c>
       <c r="C409" t="s">
-        <v>1172</v>
+        <v>522</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>1173</v>
+        <v>523</v>
       </c>
       <c r="B410" t="s">
-        <v>1174</v>
+        <v>524</v>
       </c>
       <c r="C410" t="s">
-        <v>1175</v>
+        <v>525</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>1179</v>
+        <v>526</v>
       </c>
       <c r="B411" t="s">
-        <v>1180</v>
+        <v>535</v>
       </c>
       <c r="C411" t="s">
-        <v>1181</v>
+        <v>527</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B412" t="s">
-        <v>1183</v>
+        <v>528</v>
       </c>
       <c r="C412" t="s">
-        <v>1184</v>
+        <v>529</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B413" t="s">
-        <v>1186</v>
+        <v>530</v>
       </c>
       <c r="C413" t="s">
-        <v>1187</v>
+        <v>531</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>1188</v>
+        <v>532</v>
       </c>
       <c r="B414" t="s">
-        <v>1189</v>
+        <v>533</v>
       </c>
       <c r="C414" t="s">
-        <v>1190</v>
+        <v>534</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>220</v>
+        <v>536</v>
       </c>
       <c r="B415" t="s">
-        <v>221</v>
+        <v>537</v>
       </c>
       <c r="C415" t="s">
-        <v>222</v>
+        <v>538</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>274</v>
+        <v>539</v>
       </c>
       <c r="B416" t="s">
-        <v>275</v>
+        <v>545</v>
       </c>
       <c r="C416" t="s">
-        <v>223</v>
+        <v>540</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="B417" t="s">
-        <v>276</v>
+        <v>198</v>
       </c>
       <c r="C417" t="s">
-        <v>225</v>
+        <v>541</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>277</v>
+        <v>542</v>
       </c>
       <c r="B418" t="s">
-        <v>278</v>
+        <v>543</v>
       </c>
       <c r="C418" t="s">
-        <v>226</v>
+        <v>544</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>227</v>
-      </c>
-      <c r="B419" t="s">
-        <v>279</v>
-      </c>
-      <c r="C419" t="s">
-        <v>280</v>
+        <v>707</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>228</v>
+        <v>1086</v>
       </c>
       <c r="B420" t="s">
-        <v>281</v>
+        <v>1087</v>
       </c>
       <c r="C420" t="s">
-        <v>229</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>230</v>
+        <v>1111</v>
       </c>
       <c r="B421" t="s">
-        <v>231</v>
+        <v>1110</v>
       </c>
       <c r="C421" t="s">
-        <v>232</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>233</v>
-      </c>
-      <c r="B422" t="s">
-        <v>234</v>
+        <v>1090</v>
       </c>
       <c r="C422" t="s">
-        <v>235</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>236</v>
+        <v>1092</v>
       </c>
       <c r="B423" t="s">
-        <v>237</v>
+        <v>1093</v>
+      </c>
+      <c r="C423" t="s">
+        <v>1094</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>238</v>
+        <v>1095</v>
+      </c>
+      <c r="B424" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C424" t="s">
+        <v>1097</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>239</v>
+        <v>1098</v>
       </c>
       <c r="B425" t="s">
-        <v>240</v>
-      </c>
-      <c r="C425" t="s">
-        <v>241</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>242</v>
-      </c>
-      <c r="B426" t="s">
-        <v>243</v>
+        <v>1100</v>
       </c>
       <c r="C426" t="s">
-        <v>244</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>245</v>
+        <v>1102</v>
       </c>
       <c r="B427" t="s">
-        <v>246</v>
-      </c>
-      <c r="C427" t="s">
-        <v>247</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>248</v>
+        <v>1104</v>
+      </c>
+      <c r="C428" t="s">
+        <v>1105</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>249</v>
+        <v>1106</v>
       </c>
       <c r="B429" t="s">
-        <v>250</v>
-      </c>
-      <c r="C429" t="s">
-        <v>251</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>252</v>
-      </c>
-      <c r="B430" t="s">
-        <v>253</v>
+        <v>1108</v>
       </c>
       <c r="C430" t="s">
-        <v>254</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>255</v>
-      </c>
-      <c r="B431" t="s">
-        <v>256</v>
+        <v>1112</v>
       </c>
       <c r="C431" t="s">
-        <v>257</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>258</v>
-      </c>
-      <c r="B432" t="s">
-        <v>259</v>
+        <v>1114</v>
       </c>
       <c r="C432" t="s">
-        <v>260</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>261</v>
-      </c>
-      <c r="B433" t="s">
-        <v>262</v>
+        <v>1116</v>
+      </c>
+      <c r="C433" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A435" t="s">
-        <v>264</v>
+        <v>1118</v>
+      </c>
+      <c r="C434" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="A435" s="3" t="s">
+        <v>1123</v>
       </c>
       <c r="B435" t="s">
-        <v>265</v>
+        <v>1121</v>
       </c>
       <c r="C435" t="s">
-        <v>266</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>267</v>
+        <v>1124</v>
+      </c>
+      <c r="B436" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C436" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>268</v>
+        <v>1127</v>
       </c>
       <c r="B437" t="s">
-        <v>269</v>
+        <v>1128</v>
       </c>
       <c r="C437" t="s">
-        <v>270</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B438" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C438" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B439" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C439" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A440" t="s">
+        <v>708</v>
+      </c>
+      <c r="B440" t="s">
+        <v>723</v>
+      </c>
+      <c r="C440" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A441" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B441" t="s">
+        <v>724</v>
+      </c>
+      <c r="C441" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A442" t="s">
+        <v>711</v>
+      </c>
+      <c r="B442" t="s">
+        <v>712</v>
+      </c>
+      <c r="C442" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A443" t="s">
+        <v>714</v>
+      </c>
+      <c r="B443" t="s">
+        <v>715</v>
+      </c>
+      <c r="C443" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A444" t="s">
+        <v>717</v>
+      </c>
+      <c r="B444" t="s">
+        <v>718</v>
+      </c>
+      <c r="C444" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A445" t="s">
+        <v>720</v>
+      </c>
+      <c r="B445" t="s">
+        <v>721</v>
+      </c>
+      <c r="C445" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A446" t="s">
+        <v>725</v>
+      </c>
+      <c r="B446" t="s">
+        <v>765</v>
+      </c>
+      <c r="C446" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A447" t="s">
+        <v>727</v>
+      </c>
+      <c r="B447" t="s">
+        <v>728</v>
+      </c>
+      <c r="C447" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A448" t="s">
+        <v>730</v>
+      </c>
+      <c r="B448" t="s">
+        <v>731</v>
+      </c>
+      <c r="C448" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A449" t="s">
+        <v>733</v>
+      </c>
+      <c r="B449" t="s">
+        <v>734</v>
+      </c>
+      <c r="C449" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A450" t="s">
+        <v>736</v>
+      </c>
+      <c r="B450" t="s">
+        <v>766</v>
+      </c>
+      <c r="C450" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A451" t="s">
+        <v>738</v>
+      </c>
+      <c r="B451" t="s">
+        <v>739</v>
+      </c>
+      <c r="C451" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A452" t="s">
+        <v>741</v>
+      </c>
+      <c r="B452" t="s">
+        <v>767</v>
+      </c>
+      <c r="C452" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A453" t="s">
+        <v>743</v>
+      </c>
+      <c r="B453" t="s">
+        <v>768</v>
+      </c>
+      <c r="C453" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A454" t="s">
+        <v>745</v>
+      </c>
+      <c r="C454" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A455" t="s">
+        <v>747</v>
+      </c>
+      <c r="B455" t="s">
+        <v>748</v>
+      </c>
+      <c r="C455" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A456" t="s">
+        <v>750</v>
+      </c>
+      <c r="B456" t="s">
+        <v>751</v>
+      </c>
+      <c r="C456" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A457" t="s">
+        <v>753</v>
+      </c>
+      <c r="B457" t="s">
+        <v>754</v>
+      </c>
+      <c r="C457" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A458" t="s">
+        <v>756</v>
+      </c>
+      <c r="B458" t="s">
+        <v>757</v>
+      </c>
+      <c r="C458" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A459" t="s">
+        <v>759</v>
+      </c>
+      <c r="B459" t="s">
+        <v>760</v>
+      </c>
+      <c r="C459" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A460" t="s">
+        <v>762</v>
+      </c>
+      <c r="B460" t="s">
+        <v>763</v>
+      </c>
+      <c r="C460" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A461" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A462" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C462" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A463" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B463" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C463" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A464" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C464" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A465" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C465" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A466" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C466" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A467" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C467" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A468" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C468" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C469" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A470" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C470" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A471" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C471" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A472" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C472" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A473" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C473" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A474" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C474" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A475" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C475" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A476" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C476" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A477" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C477" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A478" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C478" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A479" t="s">
+        <v>220</v>
+      </c>
+      <c r="B479" t="s">
+        <v>221</v>
+      </c>
+      <c r="C479" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A480" t="s">
+        <v>274</v>
+      </c>
+      <c r="B480" t="s">
+        <v>275</v>
+      </c>
+      <c r="C480" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A481" t="s">
+        <v>224</v>
+      </c>
+      <c r="B481" t="s">
+        <v>276</v>
+      </c>
+      <c r="C481" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A482" t="s">
+        <v>277</v>
+      </c>
+      <c r="B482" t="s">
+        <v>278</v>
+      </c>
+      <c r="C482" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A483" t="s">
+        <v>227</v>
+      </c>
+      <c r="B483" t="s">
+        <v>279</v>
+      </c>
+      <c r="C483" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A484" t="s">
+        <v>228</v>
+      </c>
+      <c r="B484" t="s">
+        <v>281</v>
+      </c>
+      <c r="C484" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A485" t="s">
+        <v>230</v>
+      </c>
+      <c r="B485" t="s">
+        <v>231</v>
+      </c>
+      <c r="C485" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A486" t="s">
+        <v>233</v>
+      </c>
+      <c r="B486" t="s">
+        <v>234</v>
+      </c>
+      <c r="C486" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A487" t="s">
+        <v>236</v>
+      </c>
+      <c r="B487" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A488" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A489" t="s">
+        <v>239</v>
+      </c>
+      <c r="B489" t="s">
+        <v>240</v>
+      </c>
+      <c r="C489" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A490" t="s">
+        <v>242</v>
+      </c>
+      <c r="B490" t="s">
+        <v>243</v>
+      </c>
+      <c r="C490" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A491" t="s">
+        <v>245</v>
+      </c>
+      <c r="B491" t="s">
+        <v>246</v>
+      </c>
+      <c r="C491" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A492" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A493" t="s">
+        <v>249</v>
+      </c>
+      <c r="B493" t="s">
+        <v>250</v>
+      </c>
+      <c r="C493" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A494" t="s">
+        <v>252</v>
+      </c>
+      <c r="B494" t="s">
+        <v>253</v>
+      </c>
+      <c r="C494" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A495" t="s">
+        <v>255</v>
+      </c>
+      <c r="B495" t="s">
+        <v>256</v>
+      </c>
+      <c r="C495" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A496" t="s">
+        <v>258</v>
+      </c>
+      <c r="B496" t="s">
+        <v>259</v>
+      </c>
+      <c r="C496" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A497" t="s">
+        <v>261</v>
+      </c>
+      <c r="B497" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A498" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A499" t="s">
+        <v>264</v>
+      </c>
+      <c r="B499" t="s">
+        <v>265</v>
+      </c>
+      <c r="C499" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A500" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A501" t="s">
+        <v>268</v>
+      </c>
+      <c r="B501" t="s">
+        <v>269</v>
+      </c>
+      <c r="C501" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A502" t="s">
         <v>271</v>
       </c>
-      <c r="B438" t="s">
+      <c r="B502" t="s">
         <v>272</v>
       </c>
-      <c r="C438" t="s">
+      <c r="C502" t="s">
         <v>273</v>
       </c>
     </row>

--- a/00-日語文型整理.xlsx
+++ b/00-日語文型整理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://guandamachine-my.sharepoint.com/personal/ec03_gd_guandamachine_com_tw/Documents/Fly/日語/日語練習網站/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="328" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1BDFFA5-8995-4720-AC84-2B7DC64E8AD3}"/>
+  <xr:revisionPtr revIDLastSave="347" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FCFB421-6E68-4480-BC14-B69BE51EE7B0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{0F3A2E6B-B5D2-4B57-9A1E-3E6BF54CF7A6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="1377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="1441">
   <si>
     <t>わたしわ マイク・ミラーです</t>
   </si>
@@ -4475,6 +4475,199 @@
   </si>
   <si>
     <t>……我最喜歡天婦羅。</t>
+  </si>
+  <si>
+    <t>*第25課文型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>あめが ふったら、でかけません</t>
+  </si>
+  <si>
+    <t>雨が 降ったら、出かけません</t>
+  </si>
+  <si>
+    <t>如果下雨,我就不出門</t>
+  </si>
+  <si>
+    <t>あめが ふっても、でかけます</t>
+  </si>
+  <si>
+    <t>雨が 降っても、出かけます</t>
+  </si>
+  <si>
+    <t>就算下雨,我也會出門</t>
+  </si>
+  <si>
+    <t>もし 1おくえん あったら、なにを したいですか</t>
+  </si>
+  <si>
+    <t>もし 1億円 あったら、何を したいですか</t>
+  </si>
+  <si>
+    <t>如果你有1億日元,你會做什麼?</t>
+  </si>
+  <si>
+    <t>…コンピューターソフトの かいしゃを つくりたいです</t>
+  </si>
+  <si>
+    <t>…コンピューターソフトの 会社を 作りたいです</t>
+  </si>
+  <si>
+    <t>……我想開一家電腦軟體公司</t>
+  </si>
+  <si>
+    <t>やくそくの じかんに ともだちが こなかったら、どう しますか</t>
+  </si>
+  <si>
+    <t>約束の 時間に 友達が 来なかったら、どう しますか</t>
+  </si>
+  <si>
+    <t>如果你的朋友沒有依照約定時間出現,你會怎麼做?</t>
+  </si>
+  <si>
+    <t>…すぐ かえります</t>
+  </si>
+  <si>
+    <t>…すぐ 帰ります</t>
+  </si>
+  <si>
+    <t>……我會立刻回家。</t>
+  </si>
+  <si>
+    <t>あの あたらしい くつやは いい くつが たくさん ありますよ</t>
+  </si>
+  <si>
+    <t>あの 新しい 靴屋は いい 靴が たくさん ありますよ</t>
+  </si>
+  <si>
+    <t>那家新開的鞋店有很多好鞋。</t>
+  </si>
+  <si>
+    <t>…そうですか。やすかったら、かいたいです</t>
+  </si>
+  <si>
+    <t>…そうですか。安かったら、買いたいです</t>
+  </si>
+  <si>
+    <t>……真的嗎？如果價格便宜，我想買幾雙。</t>
+  </si>
+  <si>
+    <t>あしたまでに レポートを ださなければ なりませんか</t>
+  </si>
+  <si>
+    <t>あしたまでに レポートを 出さなければ なりませんか</t>
+  </si>
+  <si>
+    <t>我必須在明天之前提交報告嗎？</t>
+  </si>
+  <si>
+    <t>…いいえ。 むりだったら、きんようびに だして ください</t>
+  </si>
+  <si>
+    <t>…いいえ。 無理だったら、金曜日に 出して ください</t>
+  </si>
+  <si>
+    <t>……不用。如果您無法在明天之前提交，請在周五之前提交。</t>
+  </si>
+  <si>
+    <t>もう こどもの なまえを かんがえましたか</t>
+  </si>
+  <si>
+    <t>もう 子どもの 名前を 考えましたか</t>
+  </si>
+  <si>
+    <t>想好孩子的名字了嗎？</t>
+  </si>
+  <si>
+    <t>…ええ、おとこの こだったら、「ひかる」です</t>
+  </si>
+  <si>
+    <t>…ええ、男の 子だったら、「ひかる」です</t>
+  </si>
+  <si>
+    <t>……是的，如果是男孩，就叫「阿光」（Hikaru）。</t>
+  </si>
+  <si>
+    <t>おんなの こだったら、「あや」です</t>
+  </si>
+  <si>
+    <t>女の 子だったら、「あや」です</t>
+  </si>
+  <si>
+    <t>如果是女孩，名字就叫「Aya」。</t>
+  </si>
+  <si>
+    <t>だいがくを でたら、すぐ はたらきますか</t>
+  </si>
+  <si>
+    <t>大学を 出たら、すぐ 働きますか</t>
+  </si>
+  <si>
+    <t>你大學畢業後會馬上開始工作嗎？</t>
+  </si>
+  <si>
+    <t>…いいえ、1ねんぐらい いろいろな くにを りょこうしたいです</t>
+  </si>
+  <si>
+    <t>…いいえ、1年ぐらい いろいろな 国を 旅行したいです</t>
+  </si>
+  <si>
+    <t>……不，我想花一年左右的時間去各國旅行。</t>
+  </si>
+  <si>
+    <t>せんせい、この ことばの いみが わかりません</t>
+  </si>
+  <si>
+    <t>先生、この ことばの 意味が わかりません</t>
+  </si>
+  <si>
+    <t>老師，我不明白這個字的意思。</t>
+  </si>
+  <si>
+    <t>…じしょを みましたか</t>
+  </si>
+  <si>
+    <t>…辞書を 見ましたか</t>
+  </si>
+  <si>
+    <t>……您查過字典了嗎？</t>
+  </si>
+  <si>
+    <t>ええ。みても、わかりません</t>
+  </si>
+  <si>
+    <t>ええ。見ても、わかりません</t>
+  </si>
+  <si>
+    <t>查過了。但我還是不明白。</t>
+  </si>
+  <si>
+    <t>にほんじんは グループりょこうが すきですね</t>
+  </si>
+  <si>
+    <t>日本人は グループ旅行が 好きですね</t>
+  </si>
+  <si>
+    <t>日本人喜歡跟團遊，對吧？</t>
+  </si>
+  <si>
+    <t>…ええ、やすいですから</t>
+  </si>
+  <si>
+    <t>…ええ、安いですから</t>
+  </si>
+  <si>
+    <t>……是的，因為便宜。</t>
+  </si>
+  <si>
+    <t>いくら やすくても、わたしは グループりょこうが きらいです</t>
+  </si>
+  <si>
+    <t>いくら 安くても、わたしは グループ旅行が 嫌いです</t>
+  </si>
+  <si>
+    <t>無論價格多便宜，我都不喜歡跟團。</t>
   </si>
 </sst>
 </file>
@@ -4871,12 +5064,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B91EE72-412B-4BEC-A7E9-A97446845EE1}">
-  <dimension ref="A1:C502"/>
+  <dimension ref="A1:C524"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="57.21875" customWidth="1"/>
     <col min="2" max="2" width="45.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.109375" customWidth="1"/>
+    <col min="3" max="3" width="58.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -9825,235 +10018,471 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>220</v>
-      </c>
-      <c r="B479" t="s">
-        <v>221</v>
-      </c>
-      <c r="C479" t="s">
-        <v>222</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>274</v>
+        <v>1378</v>
       </c>
       <c r="B480" t="s">
-        <v>275</v>
+        <v>1379</v>
       </c>
       <c r="C480" t="s">
-        <v>223</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>224</v>
+        <v>1381</v>
       </c>
       <c r="B481" t="s">
-        <v>276</v>
+        <v>1382</v>
       </c>
       <c r="C481" t="s">
-        <v>225</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>277</v>
+        <v>1384</v>
       </c>
       <c r="B482" t="s">
-        <v>278</v>
+        <v>1385</v>
       </c>
       <c r="C482" t="s">
-        <v>226</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>227</v>
+        <v>1387</v>
       </c>
       <c r="B483" t="s">
-        <v>279</v>
+        <v>1388</v>
       </c>
       <c r="C483" t="s">
-        <v>280</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>228</v>
+        <v>1390</v>
       </c>
       <c r="B484" t="s">
-        <v>281</v>
+        <v>1391</v>
       </c>
       <c r="C484" t="s">
-        <v>229</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>230</v>
+        <v>1393</v>
       </c>
       <c r="B485" t="s">
-        <v>231</v>
+        <v>1394</v>
       </c>
       <c r="C485" t="s">
-        <v>232</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>233</v>
+        <v>1396</v>
       </c>
       <c r="B486" t="s">
-        <v>234</v>
+        <v>1397</v>
       </c>
       <c r="C486" t="s">
-        <v>235</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>236</v>
+        <v>1399</v>
       </c>
       <c r="B487" t="s">
-        <v>237</v>
+        <v>1400</v>
+      </c>
+      <c r="C487" t="s">
+        <v>1401</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>238</v>
+        <v>1402</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C488" t="s">
+        <v>1404</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>239</v>
+        <v>1405</v>
       </c>
       <c r="B489" t="s">
-        <v>240</v>
+        <v>1406</v>
       </c>
       <c r="C489" t="s">
-        <v>241</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>242</v>
+        <v>1408</v>
       </c>
       <c r="B490" t="s">
-        <v>243</v>
+        <v>1409</v>
       </c>
       <c r="C490" t="s">
-        <v>244</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>245</v>
+        <v>1411</v>
       </c>
       <c r="B491" t="s">
-        <v>246</v>
+        <v>1412</v>
       </c>
       <c r="C491" t="s">
-        <v>247</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>248</v>
+        <v>1414</v>
+      </c>
+      <c r="B492" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C492" t="s">
+        <v>1416</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>249</v>
+        <v>1417</v>
       </c>
       <c r="B493" t="s">
-        <v>250</v>
+        <v>1418</v>
       </c>
       <c r="C493" t="s">
-        <v>251</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>252</v>
+        <v>1420</v>
       </c>
       <c r="B494" t="s">
-        <v>253</v>
+        <v>1421</v>
       </c>
       <c r="C494" t="s">
-        <v>254</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>255</v>
+        <v>1423</v>
       </c>
       <c r="B495" t="s">
-        <v>256</v>
+        <v>1424</v>
       </c>
       <c r="C495" t="s">
-        <v>257</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>258</v>
+        <v>1426</v>
       </c>
       <c r="B496" t="s">
-        <v>259</v>
+        <v>1427</v>
       </c>
       <c r="C496" t="s">
-        <v>260</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>261</v>
+        <v>1429</v>
       </c>
       <c r="B497" t="s">
-        <v>262</v>
+        <v>1430</v>
+      </c>
+      <c r="C497" t="s">
+        <v>1431</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>263</v>
+        <v>1432</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C498" t="s">
+        <v>1434</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>264</v>
+        <v>1435</v>
       </c>
       <c r="B499" t="s">
-        <v>265</v>
+        <v>1436</v>
       </c>
       <c r="C499" t="s">
-        <v>266</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>267</v>
+        <v>1438</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C500" t="s">
+        <v>1440</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="B501" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="C501" t="s">
-        <v>270</v>
+        <v>222</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
+        <v>274</v>
+      </c>
+      <c r="B502" t="s">
+        <v>275</v>
+      </c>
+      <c r="C502" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A503" t="s">
+        <v>224</v>
+      </c>
+      <c r="B503" t="s">
+        <v>276</v>
+      </c>
+      <c r="C503" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A504" t="s">
+        <v>277</v>
+      </c>
+      <c r="B504" t="s">
+        <v>278</v>
+      </c>
+      <c r="C504" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A505" t="s">
+        <v>227</v>
+      </c>
+      <c r="B505" t="s">
+        <v>279</v>
+      </c>
+      <c r="C505" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A506" t="s">
+        <v>228</v>
+      </c>
+      <c r="B506" t="s">
+        <v>281</v>
+      </c>
+      <c r="C506" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A507" t="s">
+        <v>230</v>
+      </c>
+      <c r="B507" t="s">
+        <v>231</v>
+      </c>
+      <c r="C507" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A508" t="s">
+        <v>233</v>
+      </c>
+      <c r="B508" t="s">
+        <v>234</v>
+      </c>
+      <c r="C508" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A509" t="s">
+        <v>236</v>
+      </c>
+      <c r="B509" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A510" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A511" t="s">
+        <v>239</v>
+      </c>
+      <c r="B511" t="s">
+        <v>240</v>
+      </c>
+      <c r="C511" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A512" t="s">
+        <v>242</v>
+      </c>
+      <c r="B512" t="s">
+        <v>243</v>
+      </c>
+      <c r="C512" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A513" t="s">
+        <v>245</v>
+      </c>
+      <c r="B513" t="s">
+        <v>246</v>
+      </c>
+      <c r="C513" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A514" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A515" t="s">
+        <v>249</v>
+      </c>
+      <c r="B515" t="s">
+        <v>250</v>
+      </c>
+      <c r="C515" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A516" t="s">
+        <v>252</v>
+      </c>
+      <c r="B516" t="s">
+        <v>253</v>
+      </c>
+      <c r="C516" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A517" t="s">
+        <v>255</v>
+      </c>
+      <c r="B517" t="s">
+        <v>256</v>
+      </c>
+      <c r="C517" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A518" t="s">
+        <v>258</v>
+      </c>
+      <c r="B518" t="s">
+        <v>259</v>
+      </c>
+      <c r="C518" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A519" t="s">
+        <v>261</v>
+      </c>
+      <c r="B519" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A520" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A521" t="s">
+        <v>264</v>
+      </c>
+      <c r="B521" t="s">
+        <v>265</v>
+      </c>
+      <c r="C521" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A522" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A523" t="s">
+        <v>268</v>
+      </c>
+      <c r="B523" t="s">
+        <v>269</v>
+      </c>
+      <c r="C523" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A524" t="s">
         <v>271</v>
       </c>
-      <c r="B502" t="s">
+      <c r="B524" t="s">
         <v>272</v>
       </c>
-      <c r="C502" t="s">
+      <c r="C524" t="s">
         <v>273</v>
       </c>
     </row>

--- a/00-日語文型整理.xlsx
+++ b/00-日語文型整理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://guandamachine-my.sharepoint.com/personal/ec03_gd_guandamachine_com_tw/Documents/Fly/日語/日語練習網站/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="347" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FCFB421-6E68-4480-BC14-B69BE51EE7B0}"/>
+  <xr:revisionPtr revIDLastSave="402" documentId="14_{CE00BD51-3521-405A-8612-7683B195C2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8291CF2-AD02-4CB9-9164-99152AC54361}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{0F3A2E6B-B5D2-4B57-9A1E-3E6BF54CF7A6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="1441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="1530">
   <si>
     <t>わたしわ マイク・ミラーです</t>
   </si>
@@ -4668,6 +4668,287 @@
   </si>
   <si>
     <t>無論價格多便宜，我都不喜歡跟團。</t>
+  </si>
+  <si>
+    <t>*第14課文型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*第15課文型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*第16課文型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちょっと まって ください</t>
+  </si>
+  <si>
+    <t>ちょっと 待って ください</t>
+  </si>
+  <si>
+    <t>請稍等片刻</t>
+  </si>
+  <si>
+    <t>ミラーさんは いま でんわを かけて います</t>
+  </si>
+  <si>
+    <t>ミラーさんは 今 電話を かけて います</t>
+  </si>
+  <si>
+    <t>米勒先生正在打電話</t>
+  </si>
+  <si>
+    <t>V-て ください</t>
+  </si>
+  <si>
+    <t>請做 V 動作</t>
+  </si>
+  <si>
+    <t>V-て います</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 正在做 V 動作</t>
+  </si>
+  <si>
+    <t>ここに じゅうしょと なまえを かいて ください</t>
+  </si>
+  <si>
+    <t>ここに 住所と 名前を 書いて ください</t>
+  </si>
+  <si>
+    <t>請在這裡寫下您的地址和姓名</t>
+  </si>
+  <si>
+    <t>…はい、わかりました</t>
+  </si>
+  <si>
+    <t>……好的，我明白了</t>
+  </si>
+  <si>
+    <t>あの シャツを みせて ください</t>
+  </si>
+  <si>
+    <t>あの シャツを 見せて ください</t>
+  </si>
+  <si>
+    <t>請把那件襯衫給我看</t>
+  </si>
+  <si>
+    <t>…はい、どうぞ</t>
+  </si>
+  <si>
+    <t>……好的，給您</t>
+  </si>
+  <si>
+    <t>もう すこし おおきいのは ありませんか</t>
+  </si>
+  <si>
+    <t>もう 少し 大きいのは ありませんか</t>
+  </si>
+  <si>
+    <t>有沒有稍微大一點的？</t>
+  </si>
+  <si>
+    <t>…はい。この シャツは いかがですか</t>
+  </si>
+  <si>
+    <t>……有。這件襯衫怎麼樣？</t>
+  </si>
+  <si>
+    <t>すみませんが、この かんじの よみかたを おしえて ください</t>
+  </si>
+  <si>
+    <t>すみませんが、この 漢字の 読み方を 教えて ください</t>
+  </si>
+  <si>
+    <t>請問，這個漢字怎麼讀？</t>
+  </si>
+  <si>
+    <t>…それは 「かきとめ」 ですよ</t>
+  </si>
+  <si>
+    <t>……是「kakitome」</t>
+  </si>
+  <si>
+    <t>あついですね。 まどを あけましょうか</t>
+  </si>
+  <si>
+    <t>真熱啊，是不是？要不要我開開窗戶？</t>
+  </si>
+  <si>
+    <t>…すみません。 おねがいします。</t>
+  </si>
+  <si>
+    <t>…すみません。 お願いします。</t>
+  </si>
+  <si>
+    <t>……不好意思。好的，謝謝。</t>
+  </si>
+  <si>
+    <t>えきまで むかえに いきましょうか</t>
+  </si>
+  <si>
+    <t>駅まで 迎えに 行きましょうか</t>
+  </si>
+  <si>
+    <t>要不要我去車站接你？</t>
+  </si>
+  <si>
+    <t>…いいえ、けっこうです。 タクシーで いきますから。</t>
+  </si>
+  <si>
+    <t>…いいえ、けっこうです。 タクシーで 行きますから。</t>
+  </si>
+  <si>
+    <t>不，謝謝。我搭計程車去吧。</t>
+  </si>
+  <si>
+    <t>さとうさんは どこですか。</t>
+  </si>
+  <si>
+    <t>…いま かいぎしつで まつもとさんと はなして います。</t>
+  </si>
+  <si>
+    <t>…今 会議室で 松本さんと 話して います。</t>
+  </si>
+  <si>
+    <t>……他現在正在會議室和松本先生談話。</t>
+  </si>
+  <si>
+    <t>じゃ、また あとで きます</t>
+  </si>
+  <si>
+    <t>じゃ、また あとで 来ます</t>
+  </si>
+  <si>
+    <t>好的，我稍後再來。</t>
+  </si>
+  <si>
+    <t>暑いですね。 窓を 開けましょうか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.主動幫忙(最常見) 2.提議一起做某事</t>
+  </si>
+  <si>
+    <t>てつだい ましょうか</t>
+  </si>
+  <si>
+    <t>需要(我)幫忙嗎？</t>
+  </si>
+  <si>
+    <t>むかに いき ましょうか</t>
+  </si>
+  <si>
+    <t>迎えに いき ましょうか</t>
+  </si>
+  <si>
+    <t>(我)去接你嗎？</t>
+  </si>
+  <si>
+    <t>さとうを とり ましょうか</t>
+  </si>
+  <si>
+    <t>砂糖を とり ましょうか</t>
+  </si>
+  <si>
+    <t>(我)幫你拿砂糖好嗎？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vます→Vましょうか </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>要我幫您做V嗎/要不要一起做V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ミラーさんは いま レポートを よんで います</t>
+  </si>
+  <si>
+    <t>米勒目前正在閱讀一份報告</t>
+  </si>
+  <si>
+    <t>ミラーさんは いま ビデオを みて います</t>
+  </si>
+  <si>
+    <t>米勒目前正在觀看一段影片</t>
+  </si>
+  <si>
+    <t>ミラーさんは いま にほんごを べんきょうして います</t>
+  </si>
+  <si>
+    <t>ミラーさんは 今 日本語を 勉強して います</t>
+  </si>
+  <si>
+    <t>米勒目前正在學習日語</t>
+  </si>
+  <si>
+    <t>ミラーさんは いま なにを して いますか</t>
+  </si>
+  <si>
+    <t>ミラーさんは 今 なにを して いますか</t>
+  </si>
+  <si>
+    <t>米勒現在在做什麼？</t>
+  </si>
+  <si>
+    <t>ミラーさんは 今 レポートを 読んで います</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ミラーさんは 今 ビデオを 見て います</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>すみませんが、 しおを とって ください</t>
+  </si>
+  <si>
+    <t>すみませんが、 塩を 取って ください</t>
+  </si>
+  <si>
+    <t>打擾一下，請遞給我鹽好嗎？</t>
+  </si>
+  <si>
+    <t>すみませんが、 でんわばんごうを おしえて ください</t>
+  </si>
+  <si>
+    <t>すみませんが、 電話番号を 教えて ください</t>
+  </si>
+  <si>
+    <t>打擾一下，請問您的電話號碼是多少？</t>
+  </si>
+  <si>
+    <t>ひだりへ まがって ください</t>
+  </si>
+  <si>
+    <t>請快點</t>
+  </si>
+  <si>
+    <t>請左轉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">左へ 曲がって ください </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いそいで ください</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>急いだ ください</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佐藤さんは どこですか。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佐藤先生在哪裡？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5064,12 +5345,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B91EE72-412B-4BEC-A7E9-A97446845EE1}">
-  <dimension ref="A1:C524"/>
+  <dimension ref="A1:C586"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="57.21875" customWidth="1"/>
     <col min="2" max="2" width="45.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.109375" customWidth="1"/>
+    <col min="3" max="3" width="49.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -8073,2416 +8354,2751 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>170</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>171</v>
+        <v>1450</v>
       </c>
       <c r="C289" t="s">
-        <v>172</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>173</v>
+        <v>1444</v>
       </c>
       <c r="B290" t="s">
-        <v>174</v>
+        <v>1445</v>
       </c>
       <c r="C290" t="s">
-        <v>175</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>176</v>
+        <v>1516</v>
+      </c>
+      <c r="B291" t="s">
+        <v>1517</v>
       </c>
       <c r="C291" t="s">
-        <v>177</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>178</v>
+        <v>1519</v>
       </c>
       <c r="B292" t="s">
-        <v>179</v>
+        <v>1520</v>
       </c>
       <c r="C292" t="s">
-        <v>180</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>176</v>
+        <v>1522</v>
       </c>
       <c r="B293" t="s">
-        <v>181</v>
+        <v>1525</v>
       </c>
       <c r="C293" t="s">
-        <v>177</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>182</v>
+        <v>1526</v>
       </c>
       <c r="B294" t="s">
-        <v>183</v>
+        <v>1527</v>
       </c>
       <c r="C294" t="s">
-        <v>180</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>184</v>
+        <v>1452</v>
       </c>
       <c r="C295" t="s">
-        <v>185</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>186</v>
+        <v>1504</v>
       </c>
       <c r="B296" t="s">
-        <v>187</v>
+        <v>1514</v>
       </c>
       <c r="C296" t="s">
-        <v>188</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>189</v>
+        <v>1506</v>
       </c>
       <c r="B297" t="s">
-        <v>190</v>
+        <v>1515</v>
       </c>
       <c r="C297" t="s">
-        <v>191</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>192</v>
+        <v>1508</v>
       </c>
       <c r="B298" t="s">
-        <v>193</v>
+        <v>1509</v>
+      </c>
+      <c r="C298" t="s">
+        <v>1510</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>194</v>
+        <v>1511</v>
       </c>
       <c r="B299" t="s">
-        <v>195</v>
+        <v>1512</v>
       </c>
       <c r="C299" t="s">
-        <v>196</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>197</v>
+        <v>1447</v>
       </c>
       <c r="B300" t="s">
-        <v>198</v>
+        <v>1448</v>
       </c>
       <c r="C300" t="s">
-        <v>199</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>200</v>
+        <v>1454</v>
       </c>
       <c r="B301" t="s">
-        <v>202</v>
+        <v>1455</v>
       </c>
       <c r="C301" t="s">
-        <v>201</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>203</v>
+        <v>1457</v>
       </c>
       <c r="B302" t="s">
-        <v>204</v>
-      </c>
-      <c r="C302" t="s">
-        <v>205</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>206</v>
+        <v>1459</v>
       </c>
       <c r="B303" t="s">
-        <v>207</v>
+        <v>1460</v>
       </c>
       <c r="C303" t="s">
-        <v>208</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>209</v>
-      </c>
-      <c r="B304" t="s">
-        <v>210</v>
+        <v>1462</v>
       </c>
       <c r="C304" t="s">
-        <v>211</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>212</v>
+        <v>1464</v>
       </c>
       <c r="B305" t="s">
-        <v>213</v>
+        <v>1465</v>
       </c>
       <c r="C305" t="s">
-        <v>214</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>215</v>
-      </c>
-      <c r="B306" t="s">
-        <v>216</v>
+        <v>1467</v>
       </c>
       <c r="C306" t="s">
-        <v>217</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>218</v>
+        <v>1469</v>
       </c>
       <c r="B307" t="s">
-        <v>219</v>
+        <v>1470</v>
+      </c>
+      <c r="C307" t="s">
+        <v>1471</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>353</v>
+        <v>1472</v>
+      </c>
+      <c r="C308" t="s">
+        <v>1473</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>408</v>
+        <v>1502</v>
+      </c>
+      <c r="B309" t="s">
+        <v>1503</v>
       </c>
       <c r="C309" t="s">
-        <v>370</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>409</v>
-      </c>
-      <c r="B310" t="s">
-        <v>405</v>
+        <v>1494</v>
       </c>
       <c r="C310" t="s">
-        <v>370</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>406</v>
+        <v>1496</v>
+      </c>
+      <c r="B311" t="s">
+        <v>1497</v>
       </c>
       <c r="C311" t="s">
-        <v>407</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>369</v>
+        <v>1499</v>
       </c>
       <c r="B312" t="s">
-        <v>354</v>
+        <v>1500</v>
       </c>
       <c r="C312" t="s">
-        <v>355</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>410</v>
+        <v>1474</v>
+      </c>
+      <c r="B313" t="s">
+        <v>1492</v>
       </c>
       <c r="C313" t="s">
-        <v>411</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>425</v>
+        <v>1476</v>
       </c>
       <c r="B314" t="s">
-        <v>424</v>
+        <v>1477</v>
       </c>
       <c r="C314" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>426</v>
+        <v>1479</v>
       </c>
       <c r="B315" t="s">
-        <v>423</v>
+        <v>1480</v>
       </c>
       <c r="C315" t="s">
-        <v>427</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>416</v>
+        <v>1482</v>
       </c>
       <c r="B316" t="s">
-        <v>417</v>
+        <v>1483</v>
       </c>
       <c r="C316" t="s">
-        <v>412</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>357</v>
+        <v>1485</v>
       </c>
       <c r="B317" t="s">
-        <v>358</v>
+        <v>1528</v>
       </c>
       <c r="C317" t="s">
-        <v>428</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>414</v>
+        <v>1486</v>
       </c>
       <c r="B318" t="s">
-        <v>413</v>
+        <v>1487</v>
       </c>
       <c r="C318" t="s">
-        <v>415</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>419</v>
+        <v>1489</v>
       </c>
       <c r="B319" t="s">
-        <v>418</v>
+        <v>1490</v>
       </c>
       <c r="C319" t="s">
-        <v>420</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>429</v>
-      </c>
-      <c r="B320" t="s">
-        <v>430</v>
-      </c>
-      <c r="C320" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A321" t="s">
-        <v>422</v>
-      </c>
-      <c r="B321" t="s">
-        <v>421</v>
-      </c>
-      <c r="C321" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A322" t="s">
-        <v>359</v>
-      </c>
-      <c r="C322" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A323" t="s">
-        <v>361</v>
-      </c>
-      <c r="B323" t="s">
-        <v>362</v>
-      </c>
-      <c r="C323" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A324" t="s">
-        <v>364</v>
-      </c>
-      <c r="B324" t="s">
-        <v>365</v>
-      </c>
-      <c r="C324" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>367</v>
-      </c>
-      <c r="C325" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A326" t="s">
-        <v>371</v>
-      </c>
-      <c r="B326" t="s">
-        <v>372</v>
-      </c>
-      <c r="C326" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A327" t="s">
-        <v>374</v>
-      </c>
-      <c r="B327" t="s">
-        <v>375</v>
-      </c>
-      <c r="C327" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A328" t="s">
-        <v>377</v>
-      </c>
-      <c r="B328" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A329" t="s">
-        <v>402</v>
-      </c>
-      <c r="B329" t="s">
-        <v>403</v>
-      </c>
-      <c r="C329" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A330" t="s">
-        <v>379</v>
-      </c>
-      <c r="B330" t="s">
-        <v>380</v>
-      </c>
-      <c r="C330" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A331" t="s">
-        <v>382</v>
-      </c>
-      <c r="B331" t="s">
-        <v>383</v>
-      </c>
-      <c r="C331" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A332" t="s">
-        <v>385</v>
-      </c>
-      <c r="B332" t="s">
-        <v>404</v>
-      </c>
-      <c r="C332" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A333" t="s">
-        <v>386</v>
-      </c>
-      <c r="B333" t="s">
-        <v>387</v>
-      </c>
-      <c r="C333" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A334" t="s">
-        <v>389</v>
-      </c>
-      <c r="B334" t="s">
-        <v>390</v>
-      </c>
-      <c r="C334" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A335" t="s">
-        <v>392</v>
-      </c>
-      <c r="C335" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A336" t="s">
-        <v>394</v>
-      </c>
-      <c r="B336" t="s">
-        <v>395</v>
-      </c>
-      <c r="C336" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A337" t="s">
-        <v>397</v>
-      </c>
-      <c r="B337" t="s">
-        <v>398</v>
-      </c>
-      <c r="C337" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A338" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A339" t="s">
-        <v>483</v>
-      </c>
-      <c r="B339" t="s">
-        <v>434</v>
-      </c>
-      <c r="C339" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A340" t="s">
-        <v>487</v>
-      </c>
-      <c r="B340" t="s">
-        <v>484</v>
-      </c>
-      <c r="C340" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A341" t="s">
-        <v>440</v>
-      </c>
-      <c r="B341" t="s">
-        <v>441</v>
-      </c>
-      <c r="C341" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A342" t="s">
-        <v>489</v>
-      </c>
-      <c r="B342" t="s">
-        <v>488</v>
-      </c>
-      <c r="C342" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A343" t="s">
-        <v>437</v>
-      </c>
-      <c r="B343" t="s">
-        <v>438</v>
-      </c>
-      <c r="C343" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A344" t="s">
-        <v>442</v>
-      </c>
-      <c r="B344" t="s">
-        <v>443</v>
-      </c>
-      <c r="C344" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A345" t="s">
-        <v>445</v>
-      </c>
-      <c r="B345" t="s">
-        <v>446</v>
-      </c>
-      <c r="C345" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A346" t="s">
-        <v>448</v>
-      </c>
-      <c r="B346" t="s">
-        <v>449</v>
-      </c>
-      <c r="C346" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A347" t="s">
-        <v>451</v>
-      </c>
-      <c r="B347" t="s">
-        <v>452</v>
-      </c>
-      <c r="C347" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A348" t="s">
-        <v>454</v>
-      </c>
-      <c r="B348" t="s">
-        <v>455</v>
-      </c>
-      <c r="C348" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A349" t="s">
-        <v>459</v>
-      </c>
-      <c r="B349" t="s">
-        <v>457</v>
-      </c>
-      <c r="C349" t="s">
-        <v>458</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>460</v>
-      </c>
-      <c r="B350" t="s">
-        <v>461</v>
-      </c>
-      <c r="C350" t="s">
-        <v>462</v>
+        <v>170</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>463</v>
-      </c>
-      <c r="B351" t="s">
-        <v>464</v>
+        <v>171</v>
       </c>
       <c r="C351" t="s">
-        <v>465</v>
+        <v>172</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>466</v>
+        <v>173</v>
       </c>
       <c r="B352" t="s">
-        <v>467</v>
+        <v>174</v>
       </c>
       <c r="C352" t="s">
-        <v>468</v>
+        <v>175</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>469</v>
+        <v>176</v>
       </c>
       <c r="C353" t="s">
-        <v>470</v>
+        <v>177</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>471</v>
+        <v>178</v>
       </c>
       <c r="B354" t="s">
-        <v>472</v>
+        <v>179</v>
       </c>
       <c r="C354" t="s">
-        <v>473</v>
+        <v>180</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>474</v>
+        <v>176</v>
       </c>
       <c r="B355" t="s">
-        <v>475</v>
+        <v>181</v>
       </c>
       <c r="C355" t="s">
-        <v>476</v>
+        <v>177</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>477</v>
+        <v>182</v>
       </c>
       <c r="B356" t="s">
-        <v>478</v>
+        <v>183</v>
       </c>
       <c r="C356" t="s">
-        <v>479</v>
+        <v>180</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>481</v>
-      </c>
-      <c r="B357" t="s">
-        <v>482</v>
+        <v>184</v>
       </c>
       <c r="C357" t="s">
-        <v>480</v>
+        <v>185</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>546</v>
+        <v>186</v>
+      </c>
+      <c r="B358" t="s">
+        <v>187</v>
+      </c>
+      <c r="C358" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>548</v>
+        <v>189</v>
       </c>
       <c r="B359" t="s">
-        <v>549</v>
+        <v>190</v>
       </c>
       <c r="C359" t="s">
-        <v>550</v>
+        <v>191</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>551</v>
+        <v>192</v>
       </c>
       <c r="B360" t="s">
-        <v>552</v>
-      </c>
-      <c r="C360" t="s">
-        <v>553</v>
+        <v>193</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>554</v>
+        <v>194</v>
       </c>
       <c r="B361" t="s">
-        <v>555</v>
+        <v>195</v>
       </c>
       <c r="C361" t="s">
-        <v>556</v>
+        <v>196</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>557</v>
+        <v>197</v>
       </c>
       <c r="B362" t="s">
-        <v>558</v>
+        <v>198</v>
       </c>
       <c r="C362" t="s">
-        <v>559</v>
+        <v>199</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>560</v>
+        <v>200</v>
       </c>
       <c r="B363" t="s">
-        <v>561</v>
+        <v>202</v>
       </c>
       <c r="C363" t="s">
-        <v>562</v>
+        <v>201</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>563</v>
+        <v>203</v>
+      </c>
+      <c r="B364" t="s">
+        <v>204</v>
       </c>
       <c r="C364" t="s">
-        <v>564</v>
+        <v>205</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>565</v>
+        <v>206</v>
+      </c>
+      <c r="B365" t="s">
+        <v>207</v>
       </c>
       <c r="C365" t="s">
-        <v>566</v>
+        <v>208</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>567</v>
+        <v>209</v>
+      </c>
+      <c r="B366" t="s">
+        <v>210</v>
       </c>
       <c r="C366" t="s">
-        <v>568</v>
+        <v>211</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>569</v>
+        <v>212</v>
       </c>
       <c r="B367" t="s">
-        <v>570</v>
+        <v>213</v>
       </c>
       <c r="C367" t="s">
-        <v>571</v>
+        <v>214</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>572</v>
+        <v>215</v>
       </c>
       <c r="B368" t="s">
-        <v>573</v>
+        <v>216</v>
       </c>
       <c r="C368" t="s">
-        <v>574</v>
+        <v>217</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>575</v>
+        <v>218</v>
       </c>
       <c r="B369" t="s">
-        <v>576</v>
-      </c>
-      <c r="C369" t="s">
-        <v>577</v>
+        <v>219</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>578</v>
-      </c>
-      <c r="C370" t="s">
-        <v>579</v>
+        <v>353</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>580</v>
+        <v>408</v>
       </c>
       <c r="C371" t="s">
-        <v>581</v>
+        <v>370</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>582</v>
+        <v>409</v>
       </c>
       <c r="B372" t="s">
-        <v>583</v>
+        <v>405</v>
       </c>
       <c r="C372" t="s">
-        <v>584</v>
+        <v>370</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>585</v>
-      </c>
-      <c r="B373" t="s">
-        <v>586</v>
+        <v>406</v>
       </c>
       <c r="C373" t="s">
-        <v>587</v>
+        <v>407</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>588</v>
+        <v>369</v>
       </c>
       <c r="B374" t="s">
-        <v>596</v>
+        <v>354</v>
       </c>
       <c r="C374" t="s">
-        <v>589</v>
+        <v>355</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>590</v>
-      </c>
-      <c r="B375" t="s">
-        <v>597</v>
+        <v>410</v>
       </c>
       <c r="C375" t="s">
-        <v>598</v>
+        <v>411</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>591</v>
+        <v>425</v>
       </c>
       <c r="B376" t="s">
-        <v>592</v>
+        <v>424</v>
       </c>
       <c r="C376" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>593</v>
+        <v>426</v>
       </c>
       <c r="B377" t="s">
-        <v>594</v>
+        <v>423</v>
       </c>
       <c r="C377" t="s">
-        <v>595</v>
+        <v>427</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>547</v>
+        <v>416</v>
+      </c>
+      <c r="B378" t="s">
+        <v>417</v>
+      </c>
+      <c r="C378" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>600</v>
+        <v>357</v>
       </c>
       <c r="B379" t="s">
-        <v>601</v>
+        <v>358</v>
       </c>
       <c r="C379" t="s">
-        <v>602</v>
+        <v>428</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>603</v>
+        <v>414</v>
       </c>
       <c r="B380" t="s">
-        <v>605</v>
+        <v>413</v>
       </c>
       <c r="C380" t="s">
-        <v>604</v>
+        <v>415</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>606</v>
+        <v>419</v>
       </c>
       <c r="B381" t="s">
-        <v>617</v>
+        <v>418</v>
       </c>
       <c r="C381" t="s">
-        <v>607</v>
+        <v>420</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>608</v>
+        <v>429</v>
       </c>
       <c r="B382" t="s">
-        <v>609</v>
+        <v>430</v>
       </c>
       <c r="C382" t="s">
-        <v>610</v>
+        <v>431</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>611</v>
+        <v>422</v>
       </c>
       <c r="B383" t="s">
-        <v>612</v>
+        <v>421</v>
       </c>
       <c r="C383" t="s">
-        <v>613</v>
+        <v>432</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>614</v>
-      </c>
-      <c r="B384" t="s">
-        <v>615</v>
+        <v>359</v>
       </c>
       <c r="C384" t="s">
-        <v>616</v>
+        <v>360</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>618</v>
+        <v>361</v>
+      </c>
+      <c r="B385" t="s">
+        <v>362</v>
       </c>
       <c r="C385" t="s">
-        <v>619</v>
+        <v>363</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>620</v>
+        <v>364</v>
       </c>
       <c r="B386" t="s">
-        <v>621</v>
+        <v>365</v>
       </c>
       <c r="C386" t="s">
-        <v>622</v>
+        <v>366</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>623</v>
-      </c>
-      <c r="B387" t="s">
-        <v>624</v>
+        <v>367</v>
       </c>
       <c r="C387" t="s">
-        <v>625</v>
+        <v>368</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>631</v>
+        <v>371</v>
       </c>
       <c r="B388" t="s">
-        <v>626</v>
+        <v>372</v>
       </c>
       <c r="C388" t="s">
-        <v>627</v>
+        <v>373</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>628</v>
+        <v>374</v>
       </c>
       <c r="B389" t="s">
-        <v>629</v>
+        <v>375</v>
       </c>
       <c r="C389" t="s">
-        <v>630</v>
+        <v>376</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>632</v>
+        <v>377</v>
       </c>
       <c r="B390" t="s">
-        <v>633</v>
-      </c>
-      <c r="C390" t="s">
-        <v>634</v>
+        <v>378</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>637</v>
+        <v>402</v>
       </c>
       <c r="B391" t="s">
-        <v>635</v>
+        <v>403</v>
       </c>
       <c r="C391" t="s">
-        <v>636</v>
+        <v>401</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>638</v>
+        <v>379</v>
       </c>
       <c r="B392" t="s">
-        <v>639</v>
+        <v>380</v>
       </c>
       <c r="C392" t="s">
-        <v>640</v>
+        <v>381</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>641</v>
+        <v>382</v>
       </c>
       <c r="B393" t="s">
-        <v>642</v>
+        <v>383</v>
       </c>
       <c r="C393" t="s">
-        <v>643</v>
+        <v>384</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>644</v>
+        <v>385</v>
       </c>
       <c r="B394" t="s">
-        <v>645</v>
+        <v>404</v>
       </c>
       <c r="C394" t="s">
-        <v>646</v>
+        <v>400</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>647</v>
+        <v>386</v>
       </c>
       <c r="B395" t="s">
-        <v>648</v>
+        <v>387</v>
       </c>
       <c r="C395" t="s">
-        <v>649</v>
+        <v>388</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>654</v>
+        <v>389</v>
       </c>
       <c r="B396" t="s">
-        <v>650</v>
+        <v>390</v>
       </c>
       <c r="C396" t="s">
-        <v>651</v>
+        <v>391</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>652</v>
+        <v>392</v>
       </c>
       <c r="C397" t="s">
-        <v>653</v>
+        <v>393</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>490</v>
+        <v>394</v>
+      </c>
+      <c r="B398" t="s">
+        <v>395</v>
+      </c>
+      <c r="C398" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>491</v>
+        <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>492</v>
+        <v>398</v>
       </c>
       <c r="C399" t="s">
-        <v>493</v>
+        <v>399</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>494</v>
-      </c>
-      <c r="B400" t="s">
-        <v>495</v>
-      </c>
-      <c r="C400" t="s">
-        <v>496</v>
+        <v>433</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="B401" t="s">
-        <v>498</v>
+        <v>434</v>
       </c>
       <c r="C401" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="B402" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="C402" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>503</v>
+        <v>440</v>
       </c>
       <c r="B403" t="s">
-        <v>504</v>
+        <v>441</v>
       </c>
       <c r="C403" t="s">
-        <v>505</v>
+        <v>436</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>506</v>
+        <v>489</v>
+      </c>
+      <c r="B404" t="s">
+        <v>488</v>
       </c>
       <c r="C404" t="s">
-        <v>507</v>
+        <v>486</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>508</v>
+        <v>437</v>
       </c>
       <c r="B405" t="s">
-        <v>509</v>
+        <v>438</v>
       </c>
       <c r="C405" t="s">
-        <v>510</v>
+        <v>439</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>511</v>
+        <v>442</v>
       </c>
       <c r="B406" t="s">
-        <v>512</v>
+        <v>443</v>
       </c>
       <c r="C406" t="s">
-        <v>513</v>
+        <v>444</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>514</v>
+        <v>445</v>
       </c>
       <c r="B407" t="s">
-        <v>515</v>
+        <v>446</v>
       </c>
       <c r="C407" t="s">
-        <v>516</v>
+        <v>447</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>517</v>
+        <v>448</v>
       </c>
       <c r="B408" t="s">
-        <v>518</v>
+        <v>449</v>
       </c>
       <c r="C408" t="s">
-        <v>519</v>
+        <v>450</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>520</v>
+        <v>451</v>
       </c>
       <c r="B409" t="s">
-        <v>521</v>
+        <v>452</v>
       </c>
       <c r="C409" t="s">
-        <v>522</v>
+        <v>453</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>523</v>
+        <v>454</v>
       </c>
       <c r="B410" t="s">
-        <v>524</v>
+        <v>455</v>
       </c>
       <c r="C410" t="s">
-        <v>525</v>
+        <v>456</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>526</v>
+        <v>459</v>
       </c>
       <c r="B411" t="s">
-        <v>535</v>
+        <v>457</v>
       </c>
       <c r="C411" t="s">
-        <v>527</v>
+        <v>458</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>528</v>
+        <v>460</v>
+      </c>
+      <c r="B412" t="s">
+        <v>461</v>
       </c>
       <c r="C412" t="s">
-        <v>529</v>
+        <v>462</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>530</v>
+        <v>463</v>
+      </c>
+      <c r="B413" t="s">
+        <v>464</v>
       </c>
       <c r="C413" t="s">
-        <v>531</v>
+        <v>465</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="B414" t="s">
-        <v>533</v>
+        <v>467</v>
       </c>
       <c r="C414" t="s">
-        <v>534</v>
+        <v>468</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>536</v>
-      </c>
-      <c r="B415" t="s">
-        <v>537</v>
+        <v>469</v>
       </c>
       <c r="C415" t="s">
-        <v>538</v>
+        <v>470</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>539</v>
+        <v>471</v>
       </c>
       <c r="B416" t="s">
-        <v>545</v>
+        <v>472</v>
       </c>
       <c r="C416" t="s">
-        <v>540</v>
+        <v>473</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>197</v>
+        <v>474</v>
       </c>
       <c r="B417" t="s">
-        <v>198</v>
+        <v>475</v>
       </c>
       <c r="C417" t="s">
-        <v>541</v>
+        <v>476</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>542</v>
+        <v>477</v>
       </c>
       <c r="B418" t="s">
-        <v>543</v>
+        <v>478</v>
       </c>
       <c r="C418" t="s">
-        <v>544</v>
+        <v>479</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>707</v>
+        <v>481</v>
+      </c>
+      <c r="B419" t="s">
+        <v>482</v>
+      </c>
+      <c r="C419" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>1086</v>
-      </c>
-      <c r="B420" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C420" t="s">
-        <v>1088</v>
+        <v>546</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>1111</v>
+        <v>548</v>
       </c>
       <c r="B421" t="s">
-        <v>1110</v>
+        <v>549</v>
       </c>
       <c r="C421" t="s">
-        <v>1089</v>
+        <v>550</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>1090</v>
+        <v>551</v>
+      </c>
+      <c r="B422" t="s">
+        <v>552</v>
       </c>
       <c r="C422" t="s">
-        <v>1091</v>
+        <v>553</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>1092</v>
+        <v>554</v>
       </c>
       <c r="B423" t="s">
-        <v>1093</v>
+        <v>555</v>
       </c>
       <c r="C423" t="s">
-        <v>1094</v>
+        <v>556</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>1095</v>
+        <v>557</v>
       </c>
       <c r="B424" t="s">
-        <v>1096</v>
+        <v>558</v>
       </c>
       <c r="C424" t="s">
-        <v>1097</v>
+        <v>559</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>1098</v>
+        <v>560</v>
       </c>
       <c r="B425" t="s">
-        <v>1099</v>
+        <v>561</v>
+      </c>
+      <c r="C425" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>1100</v>
+        <v>563</v>
       </c>
       <c r="C426" t="s">
-        <v>1101</v>
+        <v>564</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>1102</v>
-      </c>
-      <c r="B427" t="s">
-        <v>1103</v>
+        <v>565</v>
+      </c>
+      <c r="C427" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>1104</v>
+        <v>567</v>
       </c>
       <c r="C428" t="s">
-        <v>1105</v>
+        <v>568</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>1106</v>
+        <v>569</v>
       </c>
       <c r="B429" t="s">
-        <v>1107</v>
+        <v>570</v>
+      </c>
+      <c r="C429" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>1108</v>
+        <v>572</v>
+      </c>
+      <c r="B430" t="s">
+        <v>573</v>
       </c>
       <c r="C430" t="s">
-        <v>1109</v>
+        <v>574</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>1112</v>
+        <v>575</v>
+      </c>
+      <c r="B431" t="s">
+        <v>576</v>
       </c>
       <c r="C431" t="s">
-        <v>1113</v>
+        <v>577</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>1114</v>
+        <v>578</v>
       </c>
       <c r="C432" t="s">
-        <v>1115</v>
+        <v>579</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>1116</v>
+        <v>580</v>
       </c>
       <c r="C433" t="s">
-        <v>1117</v>
+        <v>581</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>1118</v>
+        <v>582</v>
+      </c>
+      <c r="B434" t="s">
+        <v>583</v>
       </c>
       <c r="C434" t="s">
-        <v>1119</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A435" s="3" t="s">
-        <v>1123</v>
+        <v>584</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>585</v>
       </c>
       <c r="B435" t="s">
-        <v>1121</v>
+        <v>586</v>
       </c>
       <c r="C435" t="s">
-        <v>1122</v>
+        <v>587</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>1124</v>
+        <v>588</v>
       </c>
       <c r="B436" t="s">
-        <v>1125</v>
+        <v>596</v>
       </c>
       <c r="C436" t="s">
-        <v>1126</v>
+        <v>589</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>1127</v>
+        <v>590</v>
       </c>
       <c r="B437" t="s">
-        <v>1128</v>
+        <v>597</v>
       </c>
       <c r="C437" t="s">
-        <v>1129</v>
+        <v>598</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>1130</v>
+        <v>591</v>
       </c>
       <c r="B438" t="s">
-        <v>1131</v>
+        <v>592</v>
       </c>
       <c r="C438" t="s">
-        <v>1132</v>
+        <v>599</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>1133</v>
+        <v>593</v>
       </c>
       <c r="B439" t="s">
-        <v>1134</v>
+        <v>594</v>
       </c>
       <c r="C439" t="s">
-        <v>1135</v>
+        <v>595</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>708</v>
-      </c>
-      <c r="B440" t="s">
-        <v>723</v>
-      </c>
-      <c r="C440" t="s">
-        <v>709</v>
+        <v>547</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>1120</v>
+        <v>600</v>
       </c>
       <c r="B441" t="s">
-        <v>724</v>
+        <v>601</v>
       </c>
       <c r="C441" t="s">
-        <v>710</v>
+        <v>602</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>711</v>
+        <v>603</v>
       </c>
       <c r="B442" t="s">
-        <v>712</v>
+        <v>605</v>
       </c>
       <c r="C442" t="s">
-        <v>713</v>
+        <v>604</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>714</v>
+        <v>606</v>
       </c>
       <c r="B443" t="s">
-        <v>715</v>
+        <v>617</v>
       </c>
       <c r="C443" t="s">
-        <v>716</v>
+        <v>607</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>717</v>
+        <v>608</v>
       </c>
       <c r="B444" t="s">
-        <v>718</v>
+        <v>609</v>
       </c>
       <c r="C444" t="s">
-        <v>719</v>
+        <v>610</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>720</v>
+        <v>611</v>
       </c>
       <c r="B445" t="s">
-        <v>721</v>
+        <v>612</v>
       </c>
       <c r="C445" t="s">
-        <v>722</v>
+        <v>613</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>725</v>
+        <v>614</v>
       </c>
       <c r="B446" t="s">
-        <v>765</v>
+        <v>615</v>
       </c>
       <c r="C446" t="s">
-        <v>726</v>
+        <v>616</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>727</v>
-      </c>
-      <c r="B447" t="s">
-        <v>728</v>
+        <v>618</v>
       </c>
       <c r="C447" t="s">
-        <v>729</v>
+        <v>619</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>730</v>
+        <v>620</v>
       </c>
       <c r="B448" t="s">
-        <v>731</v>
+        <v>621</v>
       </c>
       <c r="C448" t="s">
-        <v>732</v>
+        <v>622</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>733</v>
+        <v>623</v>
       </c>
       <c r="B449" t="s">
-        <v>734</v>
+        <v>624</v>
       </c>
       <c r="C449" t="s">
-        <v>735</v>
+        <v>625</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>736</v>
+        <v>631</v>
       </c>
       <c r="B450" t="s">
-        <v>766</v>
+        <v>626</v>
       </c>
       <c r="C450" t="s">
-        <v>737</v>
+        <v>627</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>738</v>
+        <v>628</v>
       </c>
       <c r="B451" t="s">
-        <v>739</v>
+        <v>629</v>
       </c>
       <c r="C451" t="s">
-        <v>740</v>
+        <v>630</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>741</v>
+        <v>632</v>
       </c>
       <c r="B452" t="s">
-        <v>767</v>
+        <v>633</v>
       </c>
       <c r="C452" t="s">
-        <v>742</v>
+        <v>634</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>743</v>
+        <v>637</v>
       </c>
       <c r="B453" t="s">
-        <v>768</v>
+        <v>635</v>
       </c>
       <c r="C453" t="s">
-        <v>744</v>
+        <v>636</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>745</v>
+        <v>638</v>
+      </c>
+      <c r="B454" t="s">
+        <v>639</v>
       </c>
       <c r="C454" t="s">
-        <v>746</v>
+        <v>640</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>747</v>
+        <v>641</v>
       </c>
       <c r="B455" t="s">
-        <v>748</v>
+        <v>642</v>
       </c>
       <c r="C455" t="s">
-        <v>749</v>
+        <v>643</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>750</v>
+        <v>644</v>
       </c>
       <c r="B456" t="s">
-        <v>751</v>
+        <v>645</v>
       </c>
       <c r="C456" t="s">
-        <v>752</v>
+        <v>646</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>753</v>
+        <v>647</v>
       </c>
       <c r="B457" t="s">
-        <v>754</v>
+        <v>648</v>
       </c>
       <c r="C457" t="s">
-        <v>755</v>
+        <v>649</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>756</v>
+        <v>654</v>
       </c>
       <c r="B458" t="s">
-        <v>757</v>
+        <v>650</v>
       </c>
       <c r="C458" t="s">
-        <v>758</v>
+        <v>651</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>759</v>
-      </c>
-      <c r="B459" t="s">
-        <v>760</v>
+        <v>652</v>
       </c>
       <c r="C459" t="s">
-        <v>761</v>
+        <v>653</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>762</v>
-      </c>
-      <c r="B460" t="s">
-        <v>763</v>
-      </c>
-      <c r="C460" t="s">
-        <v>764</v>
+        <v>490</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>1136</v>
+        <v>491</v>
+      </c>
+      <c r="B461" t="s">
+        <v>492</v>
+      </c>
+      <c r="C461" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>1149</v>
+        <v>494</v>
       </c>
       <c r="B462" t="s">
-        <v>1150</v>
+        <v>495</v>
       </c>
       <c r="C462" t="s">
-        <v>1155</v>
+        <v>496</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>1151</v>
+        <v>497</v>
       </c>
       <c r="B463" t="s">
-        <v>1152</v>
+        <v>498</v>
       </c>
       <c r="C463" t="s">
-        <v>1156</v>
+        <v>499</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>1153</v>
+        <v>500</v>
       </c>
       <c r="B464" t="s">
-        <v>1154</v>
+        <v>501</v>
       </c>
       <c r="C464" t="s">
-        <v>1157</v>
+        <v>502</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>1137</v>
+        <v>503</v>
       </c>
       <c r="B465" t="s">
-        <v>1138</v>
+        <v>504</v>
       </c>
       <c r="C465" t="s">
-        <v>1139</v>
+        <v>505</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B466" t="s">
-        <v>1141</v>
+        <v>506</v>
       </c>
       <c r="C466" t="s">
-        <v>1142</v>
+        <v>507</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>1143</v>
+        <v>508</v>
       </c>
       <c r="B467" t="s">
-        <v>1144</v>
+        <v>509</v>
       </c>
       <c r="C467" t="s">
-        <v>1145</v>
+        <v>510</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>1146</v>
+        <v>511</v>
       </c>
       <c r="B468" t="s">
-        <v>1147</v>
+        <v>512</v>
       </c>
       <c r="C468" t="s">
-        <v>1148</v>
+        <v>513</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>1158</v>
+        <v>514</v>
       </c>
       <c r="B469" t="s">
-        <v>1159</v>
+        <v>515</v>
       </c>
       <c r="C469" t="s">
-        <v>1160</v>
+        <v>516</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>1161</v>
+        <v>517</v>
       </c>
       <c r="B470" t="s">
-        <v>1172</v>
+        <v>518</v>
       </c>
       <c r="C470" t="s">
-        <v>1162</v>
+        <v>519</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>1163</v>
+        <v>520</v>
+      </c>
+      <c r="B471" t="s">
+        <v>521</v>
       </c>
       <c r="C471" t="s">
-        <v>1164</v>
+        <v>522</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>1165</v>
+        <v>523</v>
       </c>
       <c r="B472" t="s">
-        <v>1173</v>
+        <v>524</v>
       </c>
       <c r="C472" t="s">
-        <v>1166</v>
+        <v>525</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>1174</v>
+        <v>526</v>
       </c>
       <c r="B473" t="s">
-        <v>1167</v>
+        <v>535</v>
       </c>
       <c r="C473" t="s">
-        <v>1168</v>
+        <v>527</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>1169</v>
-      </c>
-      <c r="B474" t="s">
-        <v>1170</v>
+        <v>528</v>
       </c>
       <c r="C474" t="s">
-        <v>1171</v>
+        <v>529</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>1175</v>
-      </c>
-      <c r="B475" t="s">
-        <v>1176</v>
+        <v>530</v>
       </c>
       <c r="C475" t="s">
-        <v>1177</v>
+        <v>531</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>1178</v>
+        <v>532</v>
       </c>
       <c r="B476" t="s">
-        <v>1179</v>
+        <v>533</v>
       </c>
       <c r="C476" t="s">
-        <v>1180</v>
+        <v>534</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>1181</v>
+        <v>536</v>
       </c>
       <c r="B477" t="s">
-        <v>1182</v>
+        <v>537</v>
       </c>
       <c r="C477" t="s">
-        <v>1183</v>
+        <v>538</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>1184</v>
+        <v>539</v>
       </c>
       <c r="B478" t="s">
-        <v>1185</v>
+        <v>545</v>
       </c>
       <c r="C478" t="s">
-        <v>1186</v>
+        <v>540</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>1377</v>
+        <v>197</v>
+      </c>
+      <c r="B479" t="s">
+        <v>198</v>
+      </c>
+      <c r="C479" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>1378</v>
+        <v>542</v>
       </c>
       <c r="B480" t="s">
-        <v>1379</v>
+        <v>543</v>
       </c>
       <c r="C480" t="s">
-        <v>1380</v>
+        <v>544</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>1381</v>
-      </c>
-      <c r="B481" t="s">
-        <v>1382</v>
-      </c>
-      <c r="C481" t="s">
-        <v>1383</v>
+        <v>707</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>1384</v>
+        <v>1086</v>
       </c>
       <c r="B482" t="s">
-        <v>1385</v>
+        <v>1087</v>
       </c>
       <c r="C482" t="s">
-        <v>1386</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>1387</v>
+        <v>1111</v>
       </c>
       <c r="B483" t="s">
-        <v>1388</v>
+        <v>1110</v>
       </c>
       <c r="C483" t="s">
-        <v>1389</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>1390</v>
-      </c>
-      <c r="B484" t="s">
-        <v>1391</v>
+        <v>1090</v>
       </c>
       <c r="C484" t="s">
-        <v>1392</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>1393</v>
+        <v>1092</v>
       </c>
       <c r="B485" t="s">
-        <v>1394</v>
+        <v>1093</v>
       </c>
       <c r="C485" t="s">
-        <v>1395</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>1396</v>
+        <v>1095</v>
       </c>
       <c r="B486" t="s">
-        <v>1397</v>
+        <v>1096</v>
       </c>
       <c r="C486" t="s">
-        <v>1398</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>1399</v>
+        <v>1098</v>
       </c>
       <c r="B487" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C487" t="s">
-        <v>1401</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>1402</v>
-      </c>
-      <c r="B488" t="s">
-        <v>1403</v>
+        <v>1100</v>
       </c>
       <c r="C488" t="s">
-        <v>1404</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>1405</v>
+        <v>1102</v>
       </c>
       <c r="B489" t="s">
-        <v>1406</v>
-      </c>
-      <c r="C489" t="s">
-        <v>1407</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>1408</v>
-      </c>
-      <c r="B490" t="s">
-        <v>1409</v>
+        <v>1104</v>
       </c>
       <c r="C490" t="s">
-        <v>1410</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>1411</v>
+        <v>1106</v>
       </c>
       <c r="B491" t="s">
-        <v>1412</v>
-      </c>
-      <c r="C491" t="s">
-        <v>1413</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>1414</v>
-      </c>
-      <c r="B492" t="s">
-        <v>1415</v>
+        <v>1108</v>
       </c>
       <c r="C492" t="s">
-        <v>1416</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>1417</v>
-      </c>
-      <c r="B493" t="s">
-        <v>1418</v>
+        <v>1112</v>
       </c>
       <c r="C493" t="s">
-        <v>1419</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>1420</v>
-      </c>
-      <c r="B494" t="s">
-        <v>1421</v>
+        <v>1114</v>
       </c>
       <c r="C494" t="s">
-        <v>1422</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>1423</v>
-      </c>
-      <c r="B495" t="s">
-        <v>1424</v>
+        <v>1116</v>
       </c>
       <c r="C495" t="s">
-        <v>1425</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>1426</v>
-      </c>
-      <c r="B496" t="s">
-        <v>1427</v>
+        <v>1118</v>
       </c>
       <c r="C496" t="s">
-        <v>1428</v>
-      </c>
-    </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A497" t="s">
-        <v>1429</v>
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="A497" s="3" t="s">
+        <v>1123</v>
       </c>
       <c r="B497" t="s">
-        <v>1430</v>
+        <v>1121</v>
       </c>
       <c r="C497" t="s">
-        <v>1431</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>1432</v>
+        <v>1124</v>
       </c>
       <c r="B498" t="s">
-        <v>1433</v>
+        <v>1125</v>
       </c>
       <c r="C498" t="s">
-        <v>1434</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>1435</v>
+        <v>1127</v>
       </c>
       <c r="B499" t="s">
-        <v>1436</v>
+        <v>1128</v>
       </c>
       <c r="C499" t="s">
-        <v>1437</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>1438</v>
+        <v>1130</v>
       </c>
       <c r="B500" t="s">
-        <v>1439</v>
+        <v>1131</v>
       </c>
       <c r="C500" t="s">
-        <v>1440</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>220</v>
+        <v>1133</v>
       </c>
       <c r="B501" t="s">
-        <v>221</v>
+        <v>1134</v>
       </c>
       <c r="C501" t="s">
-        <v>222</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>274</v>
+        <v>708</v>
       </c>
       <c r="B502" t="s">
-        <v>275</v>
+        <v>723</v>
       </c>
       <c r="C502" t="s">
-        <v>223</v>
+        <v>709</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>224</v>
+        <v>1120</v>
       </c>
       <c r="B503" t="s">
-        <v>276</v>
+        <v>724</v>
       </c>
       <c r="C503" t="s">
-        <v>225</v>
+        <v>710</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>277</v>
+        <v>711</v>
       </c>
       <c r="B504" t="s">
-        <v>278</v>
+        <v>712</v>
       </c>
       <c r="C504" t="s">
-        <v>226</v>
+        <v>713</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>227</v>
+        <v>714</v>
       </c>
       <c r="B505" t="s">
-        <v>279</v>
+        <v>715</v>
       </c>
       <c r="C505" t="s">
-        <v>280</v>
+        <v>716</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>228</v>
+        <v>717</v>
       </c>
       <c r="B506" t="s">
-        <v>281</v>
+        <v>718</v>
       </c>
       <c r="C506" t="s">
-        <v>229</v>
+        <v>719</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>230</v>
+        <v>720</v>
       </c>
       <c r="B507" t="s">
-        <v>231</v>
+        <v>721</v>
       </c>
       <c r="C507" t="s">
-        <v>232</v>
+        <v>722</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>233</v>
+        <v>725</v>
       </c>
       <c r="B508" t="s">
-        <v>234</v>
+        <v>765</v>
       </c>
       <c r="C508" t="s">
-        <v>235</v>
+        <v>726</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>236</v>
+        <v>727</v>
       </c>
       <c r="B509" t="s">
-        <v>237</v>
+        <v>728</v>
+      </c>
+      <c r="C509" t="s">
+        <v>729</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>238</v>
+        <v>730</v>
+      </c>
+      <c r="B510" t="s">
+        <v>731</v>
+      </c>
+      <c r="C510" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>239</v>
+        <v>733</v>
       </c>
       <c r="B511" t="s">
-        <v>240</v>
+        <v>734</v>
       </c>
       <c r="C511" t="s">
-        <v>241</v>
+        <v>735</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>242</v>
+        <v>736</v>
       </c>
       <c r="B512" t="s">
-        <v>243</v>
+        <v>766</v>
       </c>
       <c r="C512" t="s">
-        <v>244</v>
+        <v>737</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>245</v>
+        <v>738</v>
       </c>
       <c r="B513" t="s">
-        <v>246</v>
+        <v>739</v>
       </c>
       <c r="C513" t="s">
-        <v>247</v>
+        <v>740</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>248</v>
+        <v>741</v>
+      </c>
+      <c r="B514" t="s">
+        <v>767</v>
+      </c>
+      <c r="C514" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
-        <v>249</v>
+        <v>743</v>
       </c>
       <c r="B515" t="s">
-        <v>250</v>
+        <v>768</v>
       </c>
       <c r="C515" t="s">
-        <v>251</v>
+        <v>744</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>252</v>
-      </c>
-      <c r="B516" t="s">
-        <v>253</v>
+        <v>745</v>
       </c>
       <c r="C516" t="s">
-        <v>254</v>
+        <v>746</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>255</v>
+        <v>747</v>
       </c>
       <c r="B517" t="s">
-        <v>256</v>
+        <v>748</v>
       </c>
       <c r="C517" t="s">
-        <v>257</v>
+        <v>749</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>258</v>
+        <v>750</v>
       </c>
       <c r="B518" t="s">
-        <v>259</v>
+        <v>751</v>
       </c>
       <c r="C518" t="s">
-        <v>260</v>
+        <v>752</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>261</v>
+        <v>753</v>
       </c>
       <c r="B519" t="s">
-        <v>262</v>
+        <v>754</v>
+      </c>
+      <c r="C519" t="s">
+        <v>755</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>263</v>
+        <v>756</v>
+      </c>
+      <c r="B520" t="s">
+        <v>757</v>
+      </c>
+      <c r="C520" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>264</v>
+        <v>759</v>
       </c>
       <c r="B521" t="s">
-        <v>265</v>
+        <v>760</v>
       </c>
       <c r="C521" t="s">
-        <v>266</v>
+        <v>761</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>267</v>
+        <v>762</v>
+      </c>
+      <c r="B522" t="s">
+        <v>763</v>
+      </c>
+      <c r="C522" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>268</v>
-      </c>
-      <c r="B523" t="s">
-        <v>269</v>
-      </c>
-      <c r="C523" t="s">
-        <v>270</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C524" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A525" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C525" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A526" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C526" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A527" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C527" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A528" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C528" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A529" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C529" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A530" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C530" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A531" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C531" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A532" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C532" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A533" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C533" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A534" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C534" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A535" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C535" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A536" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C536" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A537" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C537" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A538" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C538" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A539" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C539" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A540" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C540" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A541" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A542" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C542" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A543" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C543" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A544" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C544" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A545" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C545" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A546" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C546" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A547" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C547" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A548" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C548" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A549" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C549" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A550" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C550" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A551" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C551" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A552" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C552" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A553" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C553" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A554" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C554" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A555" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C555" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A556" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C556" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A557" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C557" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A558" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C558" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A559" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C559" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A560" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C560" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A561" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C561" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A562" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C562" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A563" t="s">
+        <v>220</v>
+      </c>
+      <c r="B563" t="s">
+        <v>221</v>
+      </c>
+      <c r="C563" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A564" t="s">
+        <v>274</v>
+      </c>
+      <c r="B564" t="s">
+        <v>275</v>
+      </c>
+      <c r="C564" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A565" t="s">
+        <v>224</v>
+      </c>
+      <c r="B565" t="s">
+        <v>276</v>
+      </c>
+      <c r="C565" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A566" t="s">
+        <v>277</v>
+      </c>
+      <c r="B566" t="s">
+        <v>278</v>
+      </c>
+      <c r="C566" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A567" t="s">
+        <v>227</v>
+      </c>
+      <c r="B567" t="s">
+        <v>279</v>
+      </c>
+      <c r="C567" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A568" t="s">
+        <v>228</v>
+      </c>
+      <c r="B568" t="s">
+        <v>281</v>
+      </c>
+      <c r="C568" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A569" t="s">
+        <v>230</v>
+      </c>
+      <c r="B569" t="s">
+        <v>231</v>
+      </c>
+      <c r="C569" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A570" t="s">
+        <v>233</v>
+      </c>
+      <c r="B570" t="s">
+        <v>234</v>
+      </c>
+      <c r="C570" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A571" t="s">
+        <v>236</v>
+      </c>
+      <c r="B571" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A572" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A573" t="s">
+        <v>239</v>
+      </c>
+      <c r="B573" t="s">
+        <v>240</v>
+      </c>
+      <c r="C573" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A574" t="s">
+        <v>242</v>
+      </c>
+      <c r="B574" t="s">
+        <v>243</v>
+      </c>
+      <c r="C574" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A575" t="s">
+        <v>245</v>
+      </c>
+      <c r="B575" t="s">
+        <v>246</v>
+      </c>
+      <c r="C575" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A576" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A577" t="s">
+        <v>249</v>
+      </c>
+      <c r="B577" t="s">
+        <v>250</v>
+      </c>
+      <c r="C577" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A578" t="s">
+        <v>252</v>
+      </c>
+      <c r="B578" t="s">
+        <v>253</v>
+      </c>
+      <c r="C578" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A579" t="s">
+        <v>255</v>
+      </c>
+      <c r="B579" t="s">
+        <v>256</v>
+      </c>
+      <c r="C579" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A580" t="s">
+        <v>258</v>
+      </c>
+      <c r="B580" t="s">
+        <v>259</v>
+      </c>
+      <c r="C580" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A581" t="s">
+        <v>261</v>
+      </c>
+      <c r="B581" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A582" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A583" t="s">
+        <v>264</v>
+      </c>
+      <c r="B583" t="s">
+        <v>265</v>
+      </c>
+      <c r="C583" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A584" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A585" t="s">
+        <v>268</v>
+      </c>
+      <c r="B585" t="s">
+        <v>269</v>
+      </c>
+      <c r="C585" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A586" t="s">
         <v>271</v>
       </c>
-      <c r="B524" t="s">
+      <c r="B586" t="s">
         <v>272</v>
       </c>
-      <c r="C524" t="s">
+      <c r="C586" t="s">
         <v>273</v>
       </c>
     </row>
